--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F588"/>
+  <dimension ref="A1:F611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18186,6 +18186,698 @@
         <v>1</v>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>PreferencesWin</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>game_mode_section_header</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Windows Options page: Game Mode section header above the draw-mode/suit-count/deck-count picker</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Game Mode</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Modo de Juego</t>
+        </is>
+      </c>
+      <c r="F589" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>PreferencesWin</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>saved_themes_header</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Windows Options page: Themes sub-panel sidebar header</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Saved Themes</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Temas Guardados</t>
+        </is>
+      </c>
+      <c r="F590" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>PreferencesWin</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>double_click_card_or_background_tooltip</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Windows Options page: hero preview tooltip (combined card+background, unlike Mac which has separate tooltips)</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Double-click the card or the background to adjust it</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Haz doble clic en la carta o el fondo para ajustarlo</t>
+        </is>
+      </c>
+      <c r="F591" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>PreferencesWin</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>delete_background_confirm_body</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Windows Options page: Delete Background confirmation dialog body</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Are you sure you want to delete this custom background? This cannot be undone.</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>¿Seguro que quieres eliminar este fondo personalizado? Esto no se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="F592" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>PreferencesWin</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>save_new_theme_title</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Windows Options page: Save New Theme dialog title (distinct from the button which has an ellipsis)</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Save New Theme</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Guardar Nuevo Tema</t>
+        </is>
+      </c>
+      <c r="F593" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>PreferencesWin</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>enter_theme_name_prompt</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Windows Options page: Save New Theme dialog prompt text</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Enter a name for this theme:</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Introduce un nombre para este tema:</t>
+        </is>
+      </c>
+      <c r="F594" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>PreferencesWin</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>tap_tile_upload_art_hint</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Windows Options page: Face Cards sub-panel instructional hint</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Tap a tile to upload art. Tap again to adjust.</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Toca un mosaico para subir arte. Toca de nuevo para ajustar.</t>
+        </is>
+      </c>
+      <c r="F595" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>suit_name_spades_plain</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list, e.g. "Ascension: Spades, Hearts"</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Spades</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Picas</t>
+        </is>
+      </c>
+      <c r="F596" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>suit_name_hearts_plain</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Hearts</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Corazones</t>
+        </is>
+      </c>
+      <c r="F597" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>suit_name_diamonds_plain</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Diamonds</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Diamantes</t>
+        </is>
+      </c>
+      <c r="F598" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>suit_name_clubs_plain</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Clubs</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Tréboles</t>
+        </is>
+      </c>
+      <c r="F599" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>AboutWin</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>about_downloading_update</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Windows About window: update download in progress</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Downloading update…</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Descargando actualización…</t>
+        </is>
+      </c>
+      <c r="F600" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>AboutWin</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>about_downloading_update_pct_fmt</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Windows About window: update download progress with percentage</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Downloading update… %d%%</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Descargando actualización… %d%%</t>
+        </is>
+      </c>
+      <c r="F601" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>AboutWin</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>about_update_download_failed</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Windows About window: update download failure message</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Failed to download the update.</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>No se pudo descargar la actualización.</t>
+        </is>
+      </c>
+      <c r="F602" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>AboutWin</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>install_and_restart</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Windows About window: button to install a downloaded update and restart</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Install &amp; Restart</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Instalar y Reiniciar</t>
+        </is>
+      </c>
+      <c r="F603" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>BackgroundEditorWin</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>add_background_title</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Windows Background editor window title when adding a new background</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Add Background</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Añadir Fondo</t>
+        </is>
+      </c>
+      <c r="F604" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>BackgroundEditorWin</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>edit_background_title</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Windows Background editor window title when editing an existing background</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Edit Background</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Editar Fondo</t>
+        </is>
+      </c>
+      <c r="F605" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>CardBackEditorWin</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>card_back_fill_note</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Windows Card Back editor: note shown instead of position sliders for fill-type card backs</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>This card back fills the card automatically
+and doesn't use position adjustments.</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Este reverso de carta llena la carta automáticamente
+y no usa ajustes de posición.</t>
+        </is>
+      </c>
+      <c r="F606" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>VideoPokerWin</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>btn_deal_d_hotkey</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Windows Video Poker Deal/Draw toggle button, Deal state (D hotkey)</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Deal  [D]</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Repartir  [D]</t>
+        </is>
+      </c>
+      <c r="F607" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>VideoPokerWin</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>btn_draw_d_hotkey</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Windows Video Poker Deal/Draw toggle button, Draw state (D hotkey)</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Draw  [D]</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Robar  [D]</t>
+        </is>
+      </c>
+      <c r="F608" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>DeckBuilderWin</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>remove_from_deck_context_menu</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Windows Deck Builder: right-click context menu item on a deck card</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Remove from deck?</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>¿Quitar del mazo?</t>
+        </is>
+      </c>
+      <c r="F609" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>ManageDecksWin</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>star_count_filter_fmt</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Windows Manage Decks: star-count filter dropdown item, e.g. "1 Star"/"3 Stars"</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>%d Star%@</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>%d Estrella%@</t>
+        </is>
+      </c>
+      <c r="F610" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>ManageDecksWin</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>no_cards_match_filter</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Windows Manage Decks: empty state when the current filter selection matches no cards</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>No cards match this filter.</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Ninguna carta coincide con este filtro.</t>
+        </is>
+      </c>
+      <c r="F611" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F611"/>
+  <dimension ref="A1:F620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18878,6 +18878,276 @@
         <v>1</v>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>you_lose</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Match-result overlay title on a loss (Honeycomb)</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>You Lose</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Perdiste</t>
+        </is>
+      </c>
+      <c r="F612" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>draw_sudden_death_fmt</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Match-result overlay title when a tied match enters Sudden Death; %@ is the localized Sudden Death rule name</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Draw - %@!</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>¡Empate - %@!</t>
+        </is>
+      </c>
+      <c r="F613" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>result_dealer_wins</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Result summary label, single-hand loss (iOS visible text)</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Dealer Wins</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Gana el Repartidor</t>
+        </is>
+      </c>
+      <c r="F614" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>result_hand_win_fmt</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Result summary label, multi-hand (split) win — %d is the hand number</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Hand %d: Win</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Mano %d: Gana</t>
+        </is>
+      </c>
+      <c r="F615" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>result_hand_loss_fmt</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Result summary label, multi-hand (split) loss — %d is the hand number</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Hand %d: Loss</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Mano %d: Pierde</t>
+        </is>
+      </c>
+      <c r="F616" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>result_hand_push_fmt</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Result summary label, multi-hand (split) push — %d is the hand number</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Hand %d: Push</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Mano %d: Empate</t>
+        </is>
+      </c>
+      <c r="F617" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>result_hand_bust_fmt</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Result summary label, multi-hand (split) bust — %d is the hand number</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Hand %d: Bust</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Mano %d: Se pasó</t>
+        </is>
+      </c>
+      <c r="F618" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>new_match_confirm_title</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Confirmation dialog when starting a new match mid-match</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Start a new match? Your current match will end.</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>¿Empezar un nuevo partido? Tu partido actual terminará.</t>
+        </is>
+      </c>
+      <c r="F619" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>rematch_confirm_title</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Confirmation dialog when requesting a rematch mid-match</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Rematch? Your current match will end.</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>¿Revancha? Tu partido actual terminará.</t>
+        </is>
+      </c>
+      <c r="F620" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F620"/>
+  <dimension ref="A1:F662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19148,6 +19148,1268 @@
         <v>1</v>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>menu_tab_game_selection</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu segmented tab</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Game Selection</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Selección de Juego</t>
+        </is>
+      </c>
+      <c r="F621" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>menu_header_title</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu header title</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Menú</t>
+        </is>
+      </c>
+      <c r="F622" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>close_menu_a11y</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu close-button accessibility label</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Close menu</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Cerrar menú</t>
+        </is>
+      </c>
+      <c r="F623" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>menu_section_game</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu Game Selection tab section header</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Juego</t>
+        </is>
+      </c>
+      <c r="F624" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>menu_section_theme</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu Themes tab felt-color section header</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="F625" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>menu_section_card_back</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu Themes tab card-back section header</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Card Back</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Reverso de Carta</t>
+        </is>
+      </c>
+      <c r="F626" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>menu_section_background</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu Themes tab background section header</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Background</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="F627" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>background_none_option</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu: clears the custom background back to felt color</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="F628" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>remove_card_back_alert_title</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu: confirm removing a custom card back</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Remove Card Back?</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>¿Quitar Reverso de Carta?</t>
+        </is>
+      </c>
+      <c r="F629" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>remove_background_alert_title</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu: confirm removing a custom background</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Remove Background?</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>¿Quitar Fondo?</t>
+        </is>
+      </c>
+      <c r="F630" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>remove_imported_image_body</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>This removes the imported image. It can't be undone.</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="F631" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>statistics_nav_row</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu: Statistics destination row</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Statistics</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Estadísticas</t>
+        </is>
+      </c>
+      <c r="F632" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>how_to_play_nav_row</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu: Help destination row</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>How to Play</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Cómo Jugar</t>
+        </is>
+      </c>
+      <c r="F633" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>SlideDownMenuIOS</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>face_card_art_nav_row</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>iOS slide-down menu: Face Card Art destination row</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Face Card Art</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Arte de Carta</t>
+        </is>
+      </c>
+      <c r="F634" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>touch_new_deal_label</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="F635" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>touch_undo_last_move_label</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Undo Last Move</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Deshacer Última Jugada</t>
+        </is>
+      </c>
+      <c r="F636" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>touch_deal_a11y</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>iOS Spider touch view: stock pile accessibility label</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Repartir</t>
+        </is>
+      </c>
+      <c r="F637" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>touch_completed_runs_a11y</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Completed runs</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Series completadas</t>
+        </is>
+      </c>
+      <c r="F638" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>touch_decks_picker_label</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>iOS Beecell touch view: deck-count Picker label</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Decks</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Mazos</t>
+        </is>
+      </c>
+      <c r="F639" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>touch_single_deck_option</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>iOS Beecell touch view: deck-count Picker option</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Single Deck</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Mazo Sencillo</t>
+        </is>
+      </c>
+      <c r="F640" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>touch_double_deck_option</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>iOS Beecell touch view: deck-count Picker option</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Double Deck</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Doble Mazo</t>
+        </is>
+      </c>
+      <c r="F641" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>touch_suits_picker_label</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Palos</t>
+        </is>
+      </c>
+      <c r="F642" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>touch_bet_max_button</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>iOS Video Poker touch view: Max bet button</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Máx</t>
+        </is>
+      </c>
+      <c r="F643" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>touch_settings_unlock_between_hands</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Settings unlock between hands.</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>La configuración se desbloquea entre manos.</t>
+        </is>
+      </c>
+      <c r="F644" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>touch_settings_unlock_hand_ends</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Settings unlock when the hand ends.</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>La configuración se desbloquea cuando termina la mano.</t>
+        </is>
+      </c>
+      <c r="F645" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>touch_hands_dealt_stat</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Hands Dealt</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Manos Repartidas</t>
+        </is>
+      </c>
+      <c r="F646" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>touch_session_credits_stat</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Session Credits</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Créditos de Sesión</t>
+        </is>
+      </c>
+      <c r="F647" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>touch_hand_label_fmt</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>HAND %d</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>MANO %d</t>
+        </is>
+      </c>
+      <c r="F648" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>touch_you_label</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>TÚ</t>
+        </is>
+      </c>
+      <c r="F649" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>touch_bust_suffix</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BUST</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SE PASÓ</t>
+        </is>
+      </c>
+      <c r="F650" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>touch_result_win</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>GANA</t>
+        </is>
+      </c>
+      <c r="F651" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>touch_result_loss</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>PIERDE</t>
+        </is>
+      </c>
+      <c r="F652" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>touch_result_push</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>PUSH</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>EMPATE</t>
+        </is>
+      </c>
+      <c r="F653" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>touch_result_blackjack</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>BLACKJACK!</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>¡BLACKJACK!</t>
+        </is>
+      </c>
+      <c r="F654" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>touch_result_bust</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>BUST</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>SE PASÓ</t>
+        </is>
+      </c>
+      <c r="F655" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>touch_action_hit</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: action button</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Pedir</t>
+        </is>
+      </c>
+      <c r="F656" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>touch_action_stand</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: action button</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Plantarse</t>
+        </is>
+      </c>
+      <c r="F657" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>touch_action_double</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: action button</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Doblar</t>
+        </is>
+      </c>
+      <c r="F658" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>touch_action_split</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>iOS Blackjack touch view: action button</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Dividir</t>
+        </is>
+      </c>
+      <c r="F659" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>touch_reset_position_button</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: Reset Position button</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Reset Position</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Restablecer Posición</t>
+        </is>
+      </c>
+      <c r="F660" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>touch_add_card_back_title</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>iOS custom card-back import sheet nav title</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Add Card Back</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Añadir Reverso de Carta</t>
+        </is>
+      </c>
+      <c r="F661" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>steal_instruction_tap</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Steal-mode instructional hint, iOS (touch wording — Mac/Windows use the click-based steal_instruction key)</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Double-tap a captured opponent's card
+on the board to steal it.</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Toca dos veces la carta capturada de un oponente
+en el tablero para robarla.</t>
+        </is>
+      </c>
+      <c r="F662" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F662"/>
+  <dimension ref="A1:F664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>hand_four_of_a_kind</t>
+          <t>hand_flush</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -13022,12 +13022,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Four of a Kind</t>
+          <t>Flush</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Póker</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="F420" t="b">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>hand_full_house</t>
+          <t>hand_straight</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -13052,16 +13052,16 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Full House</t>
+          <t>Straight</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Full House</t>
+          <t>Escalera</t>
         </is>
       </c>
       <c r="F421" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422">
@@ -13072,22 +13072,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>hand_five_of_a_kind</t>
+          <t>hand_four_of_a_kind</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Pay table row / result banner (Deuces Wild)</t>
+          <t>Pay table row / result banner</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Five of a Kind</t>
+          <t>Four of a Kind</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Repóker</t>
+          <t>Póker</t>
         </is>
       </c>
       <c r="F422" t="b">
@@ -13102,26 +13102,26 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>hand_four_aces</t>
+          <t>hand_full_house</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Pay table row (Bonus Poker)</t>
+          <t>Pay table row / result banner</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Four Aces</t>
+          <t>Full House</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Cuatro Ases</t>
+          <t>Full House</t>
         </is>
       </c>
       <c r="F423" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -13132,22 +13132,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>hand_four_2s_4s</t>
+          <t>hand_five_of_a_kind</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Pay table row (Bonus Poker)</t>
+          <t>Pay table row / result banner (Deuces Wild)</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Four 2s–4s</t>
+          <t>Five of a Kind</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Cuatro 2s-4s</t>
+          <t>Repóker</t>
         </is>
       </c>
       <c r="F424" t="b">
@@ -13162,22 +13162,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>hand_four_deuces</t>
+          <t>hand_four_aces</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Pay table row (Deuces Wild)</t>
+          <t>Pay table row (Bonus Poker)</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Four Deuces</t>
+          <t>Four Aces</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Cuatro Doses</t>
+          <t>Cuatro Ases</t>
         </is>
       </c>
       <c r="F425" t="b">
@@ -13192,22 +13192,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>hand_natural_royal_flush</t>
+          <t>hand_four_2s_4s</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Pay table row (Deuces Wild)</t>
+          <t>Pay table row (Bonus Poker)</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Natural Royal Flush</t>
+          <t>Four 2s–4s</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Escalera Real Natural</t>
+          <t>Cuatro 2s-4s</t>
         </is>
       </c>
       <c r="F426" t="b">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>hand_wild_royal_flush</t>
+          <t>hand_four_deuces</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Wild Royal Flush</t>
+          <t>Four Deuces</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Escalera Real Comodín</t>
+          <t>Cuatro Doses</t>
         </is>
       </c>
       <c r="F427" t="b">
@@ -13252,22 +13252,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>hand_no_win</t>
+          <t>hand_natural_royal_flush</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Result banner when hand doesn't qualify, VideoPokerViewModel.swift evaluateHand()/lastHandName (display-only)</t>
+          <t>Pay table row (Deuces Wild)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>No Win</t>
+          <t>Natural Royal Flush</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Sin Premio</t>
+          <t>Escalera Real Natural</t>
         </is>
       </c>
       <c r="F428" t="b">
@@ -13277,27 +13277,27 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>HoneycombRules</t>
+          <t>PokerHands</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>difficulty_ultra_hard_rawvalue</t>
+          <t>hand_wild_royal_flush</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>HoneycombDifficulty.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Killer Bee" is shown); kept for reference/future use, no wiring needed today</t>
+          <t>Pay table row (Deuces Wild)</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Ultra Hard</t>
+          <t>Wild Royal Flush</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Ultra Difícil</t>
+          <t>Escalera Real Comodín</t>
         </is>
       </c>
       <c r="F429" t="b">
@@ -13307,27 +13307,27 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>HoneycombRules</t>
+          <t>PokerHands</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>rule_name_capped_brood</t>
+          <t>hand_no_win</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>HoneycombRule.bombShelter.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>Result banner when hand doesn't qualify, VideoPokerViewModel.swift evaluateHand()/lastHandName (display-only)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Capped Brood</t>
+          <t>No Win</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Cría Sellada</t>
+          <t>Sin Premio</t>
         </is>
       </c>
       <c r="F430" t="b">
@@ -13342,22 +13342,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>rule_name_nectar_exchange</t>
+          <t>difficulty_ultra_hard_rawvalue</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>HoneycombRule.swap.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombDifficulty.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Killer Bee" is shown); kept for reference/future use, no wiring needed today</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Nectar Exchange</t>
+          <t>Ultra Hard</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Intercambio de Néctar</t>
+          <t>Ultra Difícil</t>
         </is>
       </c>
       <c r="F431" t="b">
@@ -13372,22 +13372,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>rule_name_scouting_party</t>
+          <t>rule_name_capped_brood</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>HoneycombRule.threeOpen.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.bombShelter.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Scouting Party</t>
+          <t>Capped Brood</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Grupo de Exploración</t>
+          <t>Cría Sellada</t>
         </is>
       </c>
       <c r="F432" t="b">
@@ -13402,22 +13402,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>rule_name_swarm_to_the_death</t>
+          <t>rule_name_nectar_exchange</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>HoneycombRule.suddenDeath.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.swap.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Swarm to the Death</t>
+          <t>Nectar Exchange</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Enjambre a Muerte</t>
+          <t>Intercambio de Néctar</t>
         </is>
       </c>
       <c r="F433" t="b">
@@ -13432,22 +13432,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>rule_explanation_chaos</t>
+          <t>rule_name_scouting_party</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>HoneycombRule.chaos.explanation(), HoneycombBoard.swift — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.threeOpen.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Randomly mandates which card must be played each turn.</t>
+          <t>Scouting Party</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Obliga aleatoriamente qué carta se debe jugar en cada turno.</t>
+          <t>Grupo de Exploración</t>
         </is>
       </c>
       <c r="F434" t="b">
@@ -13462,22 +13462,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>rule_explanation_reverse</t>
+          <t>rule_name_swarm_to_the_death</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>HoneycombRule.reverse.explanation(), HoneycombBoard.swift — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.suddenDeath.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Inverts all comparisons—lower stats beat higher stats.</t>
+          <t>Swarm to the Death</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Invierte todas las comparaciones—las estadísticas más bajas vencen a las más altas.</t>
+          <t>Enjambre a Muerte</t>
         </is>
       </c>
       <c r="F435" t="b">
@@ -13492,22 +13492,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>normal_mode_ban_list_tooltip</t>
+          <t>rule_explanation_chaos</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Ban-list Normal Mode row tooltip fallback, HoneycombView.swift:1416</t>
+          <t>HoneycombRule.chaos.explanation(), HoneycombBoard.swift — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Forces a match with no active rules, skipping roulette.</t>
+          <t>Randomly mandates which card must be played each turn.</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Fuerza una partida sin reglas activas, saltándose la ruleta.</t>
+          <t>Obliga aleatoriamente qué carta se debe jugar en cada turno.</t>
         </is>
       </c>
       <c r="F436" t="b">
@@ -13517,61 +13517,61 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>GameModes</t>
+          <t>HoneycombRules</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>gamemode_klondike_display</t>
+          <t>rule_explanation_reverse</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>GameMode.klondike.displayName — rawValue "Klondike Solitaire" stays untouched (persisted)</t>
+          <t>HoneycombRule.reverse.explanation(), HoneycombBoard.swift — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Klondike Solibee</t>
+          <t>Inverts all comparisons—lower stats beat higher stats.</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Klondike Solibee</t>
+          <t>Invierte todas las comparaciones—las estadísticas más bajas vencen a las más altas.</t>
         </is>
       </c>
       <c r="F437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>GameModes</t>
+          <t>HoneycombRules</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>gamemode_spider_display</t>
+          <t>normal_mode_ban_list_tooltip</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>GameMode.spider.displayName — rawValue "Spider Solitaire" stays untouched (persisted)</t>
+          <t>Ban-list Normal Mode row tooltip fallback, HoneycombView.swift:1416</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Spider Solibee</t>
+          <t>Forces a match with no active rules, skipping roulette.</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Spider Solibee</t>
+          <t>Fuerza una partida sin reglas activas, saltándose la ruleta.</t>
         </is>
       </c>
       <c r="F438" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -13582,26 +13582,26 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>playmode_single</t>
+          <t>gamemode_klondike_display</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>VideoPokerPlayMode.single.rawValue (Options picker) — display-only translation</t>
+          <t>GameMode.klondike.displayName — rawValue "Klondike Solitaire" stays untouched (persisted)</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Single Play</t>
+          <t>Klondike Solibee</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Partida Única</t>
+          <t>Klondike Solibee</t>
         </is>
       </c>
       <c r="F439" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -13612,26 +13612,26 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>playmode_triple</t>
+          <t>gamemode_spider_display</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>VideoPokerPlayMode.triple.rawValue (Options picker, currently hidden/tripleEnabled=false) — display-only translation</t>
+          <t>GameMode.spider.displayName — rawValue "Spider Solitaire" stays untouched (persisted)</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Triple Play</t>
+          <t>Spider Solibee</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Partida Triple</t>
+          <t>Spider Solibee</t>
         </is>
       </c>
       <c r="F440" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -13642,22 +13642,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>game_selection_label</t>
+          <t>playmode_single</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Section label, GameUIStyles.swift:263</t>
+          <t>VideoPokerPlayMode.single.rawValue (Options picker) — display-only translation</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Game Selection</t>
+          <t>Single Play</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Selección de Juego</t>
+          <t>Partida Única</t>
         </is>
       </c>
       <c r="F441" t="b">
@@ -13672,22 +13672,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>hint_recycle_waste_to_stock</t>
+          <t>playmode_triple</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Hint-move description, GameViewModel.swift:1057</t>
+          <t>VideoPokerPlayMode.triple.rawValue (Options picker, currently hidden/tripleEnabled=false) — display-only translation</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Recycle Waste pile to Stock.</t>
+          <t>Triple Play</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Reciclar pila de descarte al mazo.</t>
+          <t>Partida Triple</t>
         </is>
       </c>
       <c r="F442" t="b">
@@ -13697,27 +13697,27 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Themes</t>
+          <t>GameModes</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>theme_name_field_placeholder</t>
+          <t>game_selection_label</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>TextField placeholder, ThemesSectionView.swift (new + rename)</t>
+          <t>Section label, GameUIStyles.swift:263</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Theme name</t>
+          <t>Game Selection</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Nombre del tema</t>
+          <t>Selección de Juego</t>
         </is>
       </c>
       <c r="F443" t="b">
@@ -13727,27 +13727,27 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Themes</t>
+          <t>GameModes</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>theme_name_empty_error</t>
+          <t>hint_recycle_waste_to_stock</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Validation error, ThemesSectionView.swift</t>
+          <t>Hint-move description, GameViewModel.swift:1057</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Theme name can't be empty.</t>
+          <t>Recycle Waste pile to Stock.</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>El nombre del tema no puede estar vacío.</t>
+          <t>Reciclar pila de descarte al mazo.</t>
         </is>
       </c>
       <c r="F444" t="b">
@@ -13762,22 +13762,22 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>theme_name_exists_error_fmt</t>
+          <t>theme_name_field_placeholder</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Validation error, ThemesSectionView.swift, %@ = theme name</t>
+          <t>TextField placeholder, ThemesSectionView.swift (new + rename)</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>A theme named "%@" already exists.</t>
+          <t>Theme name</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Ya existe un tema llamado "%@".</t>
+          <t>Nombre del tema</t>
         </is>
       </c>
       <c r="F445" t="b">
@@ -13792,22 +13792,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>rename_theme_title</t>
+          <t>theme_name_empty_error</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Alert title, ThemesSectionView.swift</t>
+          <t>Validation error, ThemesSectionView.swift</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Rename Theme</t>
+          <t>Theme name can't be empty.</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Renombrar Tema</t>
+          <t>El nombre del tema no puede estar vacío.</t>
         </is>
       </c>
       <c r="F446" t="b">
@@ -13822,22 +13822,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>save_as_new_theme</t>
+          <t>theme_name_exists_error_fmt</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Button, ThemesSectionView.swift</t>
+          <t>Validation error, ThemesSectionView.swift, %@ = theme name</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Save as New Theme</t>
+          <t>A theme named "%@" already exists.</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Guardar como Nuevo Tema</t>
+          <t>Ya existe un tema llamado "%@".</t>
         </is>
       </c>
       <c r="F447" t="b">
@@ -13852,22 +13852,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>no_saved_themes_yet</t>
+          <t>rename_theme_title</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Empty-state text, ThemesSectionView.swift</t>
+          <t>Alert title, ThemesSectionView.swift</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>No saved themes yet.</t>
+          <t>Rename Theme</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Aún no hay temas guardados.</t>
+          <t>Renombrar Tema</t>
         </is>
       </c>
       <c r="F448" t="b">
@@ -13882,22 +13882,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>delete_theme_title</t>
+          <t>save_as_new_theme</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Alert title, ThemesSectionView.swift</t>
+          <t>Button, ThemesSectionView.swift</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Delete Theme</t>
+          <t>Save as New Theme</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Eliminar Tema</t>
+          <t>Guardar como Nuevo Tema</t>
         </is>
       </c>
       <c r="F449" t="b">
@@ -13912,22 +13912,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>apply_theme_button</t>
+          <t>no_saved_themes_yet</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Button, ThemesSectionView.swift</t>
+          <t>Empty-state text, ThemesSectionView.swift</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>No saved themes yet.</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Aplicar</t>
+          <t>Aún no hay temas guardados.</t>
         </is>
       </c>
       <c r="F450" t="b">
@@ -13942,22 +13942,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>delete_theme_confirm_fmt</t>
+          <t>delete_theme_title</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Alert body, ThemesSectionView.swift, %@ = theme name</t>
+          <t>Alert title, ThemesSectionView.swift</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Delete "%@"? This cannot be undone.</t>
+          <t>Delete Theme</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>¿Eliminar "%@"? Esta acción no se puede deshacer.</t>
+          <t>Eliminar Tema</t>
         </is>
       </c>
       <c r="F451" t="b">
@@ -13967,27 +13967,27 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>Themes</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>help_honeycomb_subtitle</t>
+          <t>apply_theme_button</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>HoneycombHelpView subtitle, HelpGuideView.swift</t>
+          <t>Button, ThemesSectionView.swift</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>A tactical 3×3 grid card battle inspired by Triple Triad.</t>
+          <t>Apply</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Una batalla táctica de cartas en cuadrícula de 3×3 inspirada en Triple Triad.</t>
+          <t>Aplicar</t>
         </is>
       </c>
       <c r="F452" t="b">
@@ -13997,27 +13997,27 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>Themes</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>help_core_gameplay_mechanics_title</t>
+          <t>delete_theme_confirm_fmt</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>RuleSection title, Honeycomb only</t>
+          <t>Alert body, ThemesSectionView.swift, %@ = theme name</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>🎮 Core Gameplay &amp; Mechanics</t>
+          <t>Delete "%@"? This cannot be undone.</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>🎮 Jugabilidad Principal y Mecánicas</t>
+          <t>¿Eliminar "%@"? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F453" t="b">
@@ -14032,22 +14032,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>help_how_to_play_variants_title</t>
+          <t>help_honeycomb_subtitle</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>RuleSection title, Video Poker only</t>
+          <t>HoneycombHelpView subtitle, HelpGuideView.swift</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>🎮 How to Play &amp; Variants</t>
+          <t>A tactical 3×3 grid card battle inspired by Triple Triad.</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>🎮 Cómo Jugar y Variantes</t>
+          <t>Una batalla táctica de cartas en cuadrícula de 3×3 inspirada en Triple Triad.</t>
         </is>
       </c>
       <c r="F454" t="b">
@@ -14062,22 +14062,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>help_strategy_pro_tips_title</t>
+          <t>help_core_gameplay_mechanics_title</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>RuleSection title, shared across Klondike/Beecell/Spider/VideoPoker/Blackjack</t>
+          <t>RuleSection title, Honeycomb only</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>💡 Strategy &amp; Pro Tips</t>
+          <t>🎮 Core Gameplay &amp; Mechanics</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>💡 Estrategia y Consejos Pro</t>
+          <t>🎮 Jugabilidad Principal y Mecánicas</t>
         </is>
       </c>
       <c r="F455" t="b">
@@ -14092,22 +14092,22 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>help_overview_objective_title</t>
+          <t>help_how_to_play_variants_title</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>RuleSection title, shared across all 7 Help views</t>
+          <t>RuleSection title, Video Poker only</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>📌 Overview &amp; Objective</t>
+          <t>🎮 How to Play &amp; Variants</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>📌 Resumen y Objetivo</t>
+          <t>🎮 Cómo Jugar y Variantes</t>
         </is>
       </c>
       <c r="F456" t="b">
@@ -14122,22 +14122,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>help_controls_shortcuts_title</t>
+          <t>help_strategy_pro_tips_title</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Section header, shared across all 7 Help views</t>
+          <t>RuleSection title, shared across Klondike/Beecell/Spider/VideoPoker/Blackjack</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>⌨️ Controls &amp; Shortcuts</t>
+          <t>💡 Strategy &amp; Pro Tips</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>⌨️ Controles y Atajos</t>
+          <t>💡 Estrategia y Consejos Pro</t>
         </is>
       </c>
       <c r="F457" t="b">
@@ -14152,22 +14152,22 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>help_shortcut_click_drag_tap</t>
+          <t>help_overview_objective_title</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Honeycomb only</t>
+          <t>RuleSection title, shared across all 7 Help views</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Click &amp; Drag or Tap Card → Tap Cell</t>
+          <t>📌 Overview &amp; Objective</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Haz clic y arrastra o Toca Carta → Toca Celda</t>
+          <t>📌 Resumen y Objetivo</t>
         </is>
       </c>
       <c r="F458" t="b">
@@ -14182,22 +14182,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>help_shortcut_navigate_select</t>
+          <t>help_controls_shortcuts_title</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Beecell only</t>
+          <t>Section header, shared across all 7 Help views</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Navigate / Select</t>
+          <t>⌨️ Controls &amp; Shortcuts</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Navegar / Seleccionar</t>
+          <t>⌨️ Controles y Atajos</t>
         </is>
       </c>
       <c r="F459" t="b">
@@ -14212,22 +14212,22 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>help_shortcut_select_place_card</t>
+          <t>help_shortcut_click_drag_tap</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>ShortcutRow action, shared Klondike + Honeycomb</t>
+          <t>ShortcutRow action, Honeycomb only</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Select / Place Card</t>
+          <t>Click &amp; Drag or Tap Card → Tap Cell</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Seleccionar / Colocar Carta</t>
+          <t>Haz clic y arrastra o Toca Carta → Toca Celda</t>
         </is>
       </c>
       <c r="F460" t="b">
@@ -14242,22 +14242,22 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>help_shortcut_select_place_sequence</t>
+          <t>help_shortcut_navigate_select</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Spider only</t>
+          <t>ShortcutRow action, Beecell only</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Select / Place Sequence</t>
+          <t>Navigate / Select</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Seleccionar / Colocar Secuencia</t>
+          <t>Navegar / Seleccionar</t>
         </is>
       </c>
       <c r="F461" t="b">
@@ -14272,22 +14272,22 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>help_shortcut_show_best_ai_move</t>
+          <t>help_shortcut_select_place_card</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Honeycomb only</t>
+          <t>ShortcutRow action, shared Klondike + Honeycomb</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Show Best AI Move</t>
+          <t>Select / Place Card</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Mostrar Mejor Movimiento de la IA</t>
+          <t>Seleccionar / Colocar Carta</t>
         </is>
       </c>
       <c r="F462" t="b">
@@ -14302,22 +14302,22 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>help_shortcut_split_pairs</t>
+          <t>help_shortcut_select_place_sequence</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Blackjack only</t>
+          <t>ShortcutRow action, Spider only</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Split Pairs</t>
+          <t>Select / Place Sequence</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Dividir Pares</t>
+          <t>Seleccionar / Colocar Secuencia</t>
         </is>
       </c>
       <c r="F463" t="b">
@@ -14332,22 +14332,22 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>help_shortcut_arrow_keys</t>
+          <t>help_shortcut_show_best_ai_move</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, Klondike only (standalone; Beecell/Spider use a compound form not covered by this pass)</t>
+          <t>ShortcutRow action, Honeycomb only</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Arrow Keys</t>
+          <t>Show Best AI Move</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Teclas de Flecha</t>
+          <t>Mostrar Mejor Movimiento de la IA</t>
         </is>
       </c>
       <c r="F464" t="b">
@@ -14362,26 +14362,26 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>help_shortcut_c_q</t>
+          <t>help_shortcut_split_pairs</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, Video Poker only</t>
+          <t>ShortcutRow action, Blackjack only</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>C / Q</t>
+          <t>Split Pairs</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>C / Q</t>
+          <t>Dividir Pares</t>
         </is>
       </c>
       <c r="F465" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
@@ -14392,22 +14392,22 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>help_shortcut_space_enter</t>
+          <t>help_shortcut_arrow_keys</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, reused Klondike/Spider/VideoPoker</t>
+          <t>ShortcutRow shortcut value, Klondike only (standalone; Beecell/Spider use a compound form not covered by this pass)</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Space / Enter</t>
+          <t>Arrow Keys</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Espacio / Intro</t>
+          <t>Teclas de Flecha</t>
         </is>
       </c>
       <c r="F466" t="b">
@@ -14422,22 +14422,22 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>help_shortcut_cmd_n_r</t>
+          <t>help_shortcut_c_q</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, reused Klondike/Beecell</t>
+          <t>ShortcutRow shortcut value, Video Poker only</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>⌘N / ⌘R</t>
+          <t>C / Q</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>⌘N / ⌘R</t>
+          <t>C / Q</t>
         </is>
       </c>
       <c r="F467" t="b">
@@ -14452,26 +14452,26 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>help_shortcut_cmd_z</t>
+          <t>help_shortcut_space_enter</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, reused Klondike/Beecell/Spider</t>
+          <t>ShortcutRow shortcut value, reused Klondike/Spider/VideoPoker</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>⌘Z</t>
+          <t>Space / Enter</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>⌘Z</t>
+          <t>Espacio / Intro</t>
         </is>
       </c>
       <c r="F468" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -14482,22 +14482,22 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>help_beecell_title</t>
+          <t>help_shortcut_cmd_n_r</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>HelpShell title for BeecellHelpView — proper noun, kept as-is</t>
+          <t>ShortcutRow shortcut value, reused Klondike/Beecell</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Freecell (Beecell)</t>
+          <t>⌘N / ⌘R</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Freecell (Beecell)</t>
+          <t>⌘N / ⌘R</t>
         </is>
       </c>
       <c r="F469" t="b">
@@ -14507,50 +14507,110 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>HelpGuideKlondike</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>help_klondike_objective</t>
+          <t>help_shortcut_cmd_z</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Overview RuleSection body</t>
+          <t>ShortcutRow shortcut value, reused Klondike/Beecell/Spider</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Move all 52 cards to the four Foundation piles, organized by suit from Ace (lowest) to King (highest).</t>
+          <t>⌘Z</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Mueve las 52 cartas a las cuatro pilas de la Fundación, organizadas por palo desde el As (el más bajo) hasta el Rey (el más alto).</t>
+          <t>⌘Z</t>
         </is>
       </c>
       <c r="F470" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
+          <t>HelpGuideCommon</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>help_beecell_title</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>HelpShell title for BeecellHelpView — proper noun, kept as-is</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Freecell (Beecell)</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Freecell (Beecell)</t>
+        </is>
+      </c>
+      <c r="F471" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
           <t>HelpGuideKlondike</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>help_klondike_objective</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Overview RuleSection body</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Move all 52 cards to the four Foundation piles, organized by suit from Ace (lowest) to King (highest).</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Mueve las 52 cartas a las cuatro pilas de la Fundación, organizadas por palo desde el As (el más bajo) hasta el Rey (el más alto).</t>
+        </is>
+      </c>
+      <c r="F472" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>HelpGuideKlondike</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
         <is>
           <t>help_klondike_layout</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr">
+      <c r="C473" t="inlineStr">
         <is>
           <t>Setup &amp; Layout RuleSection body</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr">
+      <c r="D473" t="inlineStr">
         <is>
           <t>• Tableau (7 Columns): Dealt from left to right with 1 to 7 cards respectively. Only the top card in each column is face-up.
 • Stock Pile (Top-Left): Contains the remaining 24 face-down cards.
@@ -14558,7 +14618,7 @@
 • Foundations (Top-Right): Four empty slots reserved for completing each suit.</t>
         </is>
       </c>
-      <c r="E471" t="inlineStr">
+      <c r="E473" t="inlineStr">
         <is>
           <t>• Tablero (7 Columnas): Repartidas de izquierda a derecha con 1 a 7 cartas respectivamente. Solo la carta superior de cada columna está boca arriba.
 • Pila (Arriba a la Izquierda): Contiene las 24 cartas restantes boca abajo.
@@ -14566,27 +14626,27 @@
 • Fundaciones (Arriba a la Derecha): Cuatro espacios vacíos reservados para completar cada palo.</t>
         </is>
       </c>
-      <c r="F471" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
+      <c r="F473" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
         <is>
           <t>HelpGuideKlondike</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
+      <c r="B474" t="inlineStr">
         <is>
           <t>help_klondike_rules</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr">
+      <c r="C474" t="inlineStr">
         <is>
           <t>Rules &amp; How to Play RuleSection body</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr">
+      <c r="D474" t="inlineStr">
         <is>
           <t>• Tableau Building: Stack cards in descending rank with alternating colors (e.g., a red 6 on a black 7). You may move a single card or an entire face-up sequence to another column.
 • Empty Columns: Only a King (or a sequence starting with a King) may be placed in an empty tableau column.
@@ -14598,7 +14658,7 @@
   – Vegas: Start with a debt of −$52. Earn +$5 for every card moved to a foundation. Draw 1 permits only 1 pass through the stock; Draw 3 allows 3 passes (2 redeals).</t>
         </is>
       </c>
-      <c r="E472" t="inlineStr">
+      <c r="E474" t="inlineStr">
         <is>
           <t>• Construcción del Tablero: Apila cartas en rango descendente alternando colores (ej., un 6 rojo sobre un 7 negro). Puedes mover una sola carta o una secuencia entera boca arriba a otra columna.
 • Columnas Vacías: Solo un Rey (o una secuencia que empiece con un Rey) puede colocarse en una columna vacía del tablero.
@@ -14610,100 +14670,40 @@
   – Vegas: Empiezas con una deuda de −$52. Gana +$5 por cada carta movida a la fundación. Robar 1 permite solo 1 pasada por la pila; Robar 3 permite 3 pasadas (2 repartos extra).</t>
         </is>
       </c>
-      <c r="F472" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
+      <c r="F474" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
         <is>
           <t>HelpGuideKlondike</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
+      <c r="B475" t="inlineStr">
         <is>
           <t>help_klondike_strategy</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr">
+      <c r="C475" t="inlineStr">
         <is>
           <t>Strategy &amp; Pro Tips RuleSection body</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr">
+      <c r="D475" t="inlineStr">
         <is>
           <t>1. Prioritize Face-Down Cards: Always prioritize moves that reveal hidden cards in the longest tableau columns.
 2. Keep Columns Open: Don't clear a tableau column unless you already have a King ready to occupy it.
 3. Delay Foundation Moves: Avoid rushing cards into the foundation early if those cards might be needed to build lower sequences in the tableau.</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr">
+      <c r="E475" t="inlineStr">
         <is>
           <t>1. Prioriza Cartas Boca Abajo: Siempre prioriza movimientos que revelen cartas ocultas en las columnas más largas del tablero.
 2. Mantén Columnas Abiertas: No vacíes una columna del tablero a menos que ya tengas un Rey listo para ocuparla.
 3. Retrasa Movimientos a la Fundación: Evita apresurar cartas a la fundación temprano si podrían necesitarse para construir secuencias más bajas en el tablero.</t>
         </is>
       </c>
-      <c r="F473" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>HelpGuideKlondike</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>help_klondike_no_stress</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>No Stress Mode RuleSection body (identical text also used by Beecell/Spider — separate row per file grouping, exact duplicate)</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>Enabling No Stress Mode in Options disables the game timer completely.</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>Activar el Modo Sin Estrés en Opciones desactiva el temporizador de la partida por completo.</t>
-        </is>
-      </c>
-      <c r="F474" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>HelpGuideBeecell</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>help_beecell_objective</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>Overview RuleSection body</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>Move all 52 cards to the four Foundation piles, built up by suit from Ace to King.</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>Mueve las 52 cartas a las cuatro pilas de la Fundación, construyéndolas por palo desde el As hasta el Rey.</t>
-        </is>
-      </c>
       <c r="F475" t="b">
         <v>1</v>
       </c>
@@ -14711,54 +14711,114 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
+          <t>HelpGuideKlondike</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>help_klondike_no_stress</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>No Stress Mode RuleSection body (identical text also used by Beecell/Spider — separate row per file grouping, exact duplicate)</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Enabling No Stress Mode in Options disables the game timer completely.</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Activar el Modo Sin Estrés en Opciones desactiva el temporizador de la partida por completo.</t>
+        </is>
+      </c>
+      <c r="F476" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
           <t>HelpGuideBeecell</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>help_beecell_objective</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Overview RuleSection body</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Move all 52 cards to the four Foundation piles, built up by suit from Ace to King.</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Mueve las 52 cartas a las cuatro pilas de la Fundación, construyéndolas por palo desde el As hasta el Rey.</t>
+        </is>
+      </c>
+      <c r="F477" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>HelpGuideBeecell</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
         <is>
           <t>help_beecell_layout</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr">
+      <c r="C478" t="inlineStr">
         <is>
           <t>Setup &amp; Layout RuleSection body</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr">
+      <c r="D478" t="inlineStr">
         <is>
           <t>• Tableau (8 Columns): All 52 cards are dealt face-up at the start (4 columns of 7 cards, 4 columns of 6 cards).
 • Free Cells (Top-Left): Four temporary storage slots.
 • Foundations (Top-Right): Four suit build-up piles.</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr">
+      <c r="E478" t="inlineStr">
         <is>
           <t>• Tablero (8 Columnas): Las 52 cartas se reparten boca arriba al inicio (4 columnas de 7 cartas, 4 columnas de 6 cartas).
 • Celdas Libres (Arriba a la Izquierda): Cuatro espacios de almacenamiento temporal.
 • Fundaciones (Arriba a la Derecha): Cuatro pilas de construcción por palo.</t>
         </is>
       </c>
-      <c r="F476" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
+      <c r="F478" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
         <is>
           <t>HelpGuideBeecell</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
+      <c r="B479" t="inlineStr">
         <is>
           <t>help_beecell_rules</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr">
+      <c r="C479" t="inlineStr">
         <is>
           <t>Rules &amp; How to Play RuleSection body</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr">
+      <c r="D479" t="inlineStr">
         <is>
           <t>• Tableau Building: Stack cards in descending rank and alternating colors.
 • Free Cell Storage: Each free cell can hold exactly 1 card at a time.
@@ -14766,7 +14826,7 @@
 • Empty Columns: Any single card or valid sequence can be moved into an empty tableau column.</t>
         </is>
       </c>
-      <c r="E477" t="inlineStr">
+      <c r="E479" t="inlineStr">
         <is>
           <t>• Construcción del Tablero: Apila cartas en rango descendente y colores alternos.
 • Almacenamiento en Celdas Libres: Cada celda libre puede contener exactamente 1 carta a la vez.
@@ -14774,123 +14834,123 @@
 • Columnas Vacías: Cualquier carta individual o secuencia válida se puede mover a una columna vacía en el tablero.</t>
         </is>
       </c>
-      <c r="F477" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+      <c r="F479" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t>HelpGuideBeecell</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>help_beecell_strategy</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr">
+      <c r="C480" t="inlineStr">
         <is>
           <t>Strategy &amp; Pro Tips RuleSection body</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
+      <c r="D480" t="inlineStr">
         <is>
           <t>1. Protect Your Free Cells: Treat free cells as temporary maneuvering space. Avoid filling all four free cells simultaneously, as it drastically reduces your sequence-moving capacity.
 2. Uncover Low Cards Early: Focus on freeing up Aces and 2s buried at the bottom of columns.
 3. Empty Columns are Gold: An empty column doubles your movement capacity and acts as an unrestricted free cell.</t>
         </is>
       </c>
-      <c r="E478" t="inlineStr">
+      <c r="E480" t="inlineStr">
         <is>
           <t>1. Protege Tus Celdas Libres: Trata las celdas libres como espacio de maniobra temporal. Evita llenar las cuatro celdas libres simultáneamente, ya que reduce drásticamente tu capacidad de mover secuencias.
 2. Descubre Cartas Bajas Temprano: Concéntrate en liberar Ases y Doses enterrados al fondo de las columnas.
 3. Las Columnas Vacías son Oro: Una columna vacía duplica tu capacidad de movimiento y actúa como una celda libre sin restricciones.</t>
         </is>
       </c>
-      <c r="F478" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+      <c r="F480" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t>HelpGuideSpider</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B481" t="inlineStr">
         <is>
           <t>help_spider_objective</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
+      <c r="C481" t="inlineStr">
         <is>
           <t>Overview RuleSection body</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
+      <c r="D481" t="inlineStr">
         <is>
           <t>Assemble eight complete same-suit sequences from King down to Ace within the tableau. Each completed 13-card sequence is automatically removed to the foundation.</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr">
+      <c r="E481" t="inlineStr">
         <is>
           <t>Arma ocho secuencias completas del mismo palo desde el Rey hasta el As dentro del tablero. Cada secuencia completa de 13 cartas se elimina automáticamente a la fundación.</t>
         </is>
       </c>
-      <c r="F479" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
+      <c r="F481" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t>HelpGuideSpider</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
+      <c r="B482" t="inlineStr">
         <is>
           <t>help_spider_layout</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr">
+      <c r="C482" t="inlineStr">
         <is>
           <t>Setup &amp; Layout RuleSection body</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr">
+      <c r="D482" t="inlineStr">
         <is>
           <t>• Tableau (10 Columns): 54 cards dealt across 10 columns (first 4 get 6 cards; last 6 get 5 cards). Only the top card of each column is face-up.
 • Stock (Bottom/Top): 50 remaining cards arranged in 5 extra deals of 10 cards each.</t>
         </is>
       </c>
-      <c r="E480" t="inlineStr">
+      <c r="E482" t="inlineStr">
         <is>
           <t>• Tablero (10 Columnas): 54 cartas repartidas en 10 columnas (las primeras 4 tienen 6 cartas; las últimas 6 tienen 5 cartas). Solo la carta superior de cada columna está boca arriba.
 • Pila (Abajo/Arriba): Las 50 cartas restantes organizadas en 5 repartos extra de 10 cartas cada uno.</t>
         </is>
       </c>
-      <c r="F480" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
+      <c r="F482" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
         <is>
           <t>HelpGuideSpider</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B483" t="inlineStr">
         <is>
           <t>help_spider_rules</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
+      <c r="C483" t="inlineStr">
         <is>
           <t>Rules &amp; How to Play RuleSection body</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr">
+      <c r="D483" t="inlineStr">
         <is>
           <t>• Difficulty Modes:
   – 1-Suit (Easy): All 104 cards are Spades.
@@ -14900,7 +14960,7 @@
 • Stock Deals: Click the stock to deal 1 card onto every tableau column. Requirement: Every column must contain at least 1 card before you can deal from the stock.</t>
         </is>
       </c>
-      <c r="E481" t="inlineStr">
+      <c r="E483" t="inlineStr">
         <is>
           <t>• Modos de Dificultad:
   – 1 Palo (Fácil): Las 104 cartas son Picas.
@@ -14910,91 +14970,91 @@
 • Repartos desde la Pila: Haz clic en la pila para repartir 1 carta en cada columna del tablero. Requisito: Cada columna debe contener al menos 1 carta antes de que puedas repartir desde la pila.</t>
         </is>
       </c>
-      <c r="F481" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
+      <c r="F483" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
         <is>
           <t>HelpGuideSpider</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
+      <c r="B484" t="inlineStr">
         <is>
           <t>help_spider_strategy</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr">
+      <c r="C484" t="inlineStr">
         <is>
           <t>Strategy &amp; Pro Tips RuleSection body</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr">
+      <c r="D484" t="inlineStr">
         <is>
           <t>1. Same-Suit Over Mixed-Suit: Always prefer building same-suit runs. Mixed-suit stacks lock up your cards and cannot be moved together.
 2. Empty Columns First: Empty columns allow you to isolate mixed-suit stacks and re-organize them into clean same-suit runs.
 3. Delay Dealing: Exhaust every possible move on the board before clicking the stock.</t>
         </is>
       </c>
-      <c r="E482" t="inlineStr">
+      <c r="E484" t="inlineStr">
         <is>
           <t>1. Mismo Palo Antes que Palos Mixtos: Siempre prefiere construir rachas del mismo palo. Las pilas de palos mixtos bloquean tus cartas y no pueden moverse juntas.
 2. Columnas Vacías Primero: Las columnas vacías te permiten aislar pilas de palos mixtos y reorganizarlas en limpias rachas del mismo palo.
 3. Retrasa el Reparto: Agota cada movimiento posible en el tablero antes de hacer clic en la pila.</t>
         </is>
       </c>
-      <c r="F482" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
+      <c r="F484" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
         <is>
           <t>HelpGuideVideoPoker</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>help_videopoker_objective</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr">
+      <c r="C485" t="inlineStr">
         <is>
           <t>Overview RuleSection body</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr">
+      <c r="D485" t="inlineStr">
         <is>
           <t>Draw a 5-card hand that matches a qualifying entry on the pay table to earn credit multipliers.</t>
         </is>
       </c>
-      <c r="E483" t="inlineStr">
+      <c r="E485" t="inlineStr">
         <is>
           <t>Roba una mano de 5 cartas que coincida con una entrada válida en la tabla de pagos para ganar multiplicadores de créditos.</t>
         </is>
       </c>
-      <c r="F483" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
+      <c r="F485" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t>HelpGuideVideoPoker</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t>help_videopoker_how_to_play</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
+      <c r="C486" t="inlineStr">
         <is>
           <t>How to Play &amp; Variants RuleSection body</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr">
+      <c r="D486" t="inlineStr">
         <is>
           <t>1. Betting: Select 1 to 5 coins. Press Bet Max (M) to bet 5 coins and immediately deal. (Note: The 800× Royal Flush jackpot is only awarded on a 5-coin bet).
 2. Deal &amp; Hold: Press Deal (Space). Click cards or press 1–5 to toggle HOLD on cards you wish to keep.
@@ -15005,7 +15065,7 @@
 • Bonus Poker: Enhanced payouts for Four of a Kind (Four Aces pays 80×; Four 2s/3s/4s pays 40×).</t>
         </is>
       </c>
-      <c r="E484" t="inlineStr">
+      <c r="E486" t="inlineStr">
         <is>
           <t>1. Apuestas: Selecciona 1 a 5 monedas. Presiona Apuesta Máxima (M) para apostar 5 monedas y repartir de inmediato. (Nota: El premio de 800× por la Escalera Real solo se otorga con una apuesta de 5 monedas).
 2. Repartir y Retener: Presiona Repartir (Espacio). Haz clic en las cartas o presiona 1–5 para alternar RETENER (HOLD) en las cartas que desees guardar.
@@ -15016,100 +15076,40 @@
 • Bonus Poker: Pagos mejorados por Póker (Cuatro Ases paga 80×; Cuatro 2s/3s/4s paga 40×).</t>
         </is>
       </c>
-      <c r="F484" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
+      <c r="F486" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
         <is>
           <t>HelpGuideVideoPoker</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B487" t="inlineStr">
         <is>
           <t>help_videopoker_strategy</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
+      <c r="C487" t="inlineStr">
         <is>
           <t>Strategy &amp; Pro Tips RuleSection body</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr">
+      <c r="D487" t="inlineStr">
         <is>
           <t>1. Always Bet Max (5 Coins): The Royal Flush payout jumps from 250× to 800× only at 5 coins.
 2. Never Break a Made Hand (Except for 4-to-a-Royal): Only break a Straight or Flush if you are 1 card away from a Royal Flush.
 3. In Deuces Wild, Never Discard a 2: Deuces are wild—always hold every 2 dealt to you!</t>
         </is>
       </c>
-      <c r="E485" t="inlineStr">
+      <c r="E487" t="inlineStr">
         <is>
           <t>1. Siempre Haz Apuesta Máxima (5 Monedas): El pago por la Escalera Real salta de 250× a 800× solo con 5 monedas.
 2. Nunca Rompas una Mano Armada (Excepto por 4-para-Escalera Real): Solo rompe una Escalera o Color si estás a 1 carta de una Escalera Real.
 3. En Deuces Wild, Nunca Descartes un 2: Los dos son comodines—¡siempre retén cada 2 que te repartan!</t>
         </is>
       </c>
-      <c r="F485" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>HelpGuideVideoPoker</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>help_videopoker_no_stress</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>No Stress Mode RuleSection body</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Enabling No Stress Mode in Options switches the game into Free Play—hiding bets, credits, and pay tables so you can play risk-free without wagers.</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>Activar el Modo Sin Estrés en Opciones cambia el juego a Juego Libre—ocultando apuestas, créditos y tablas de pagos para que puedas jugar sin riesgos ni apuestas.</t>
-        </is>
-      </c>
-      <c r="F486" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>HelpGuideBlackjack</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>help_blackjack_objective</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Overview RuleSection body</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Outscore the dealer's hand total without exceeding 21. Face cards = 10, Aces = 1 or 11, Number cards = face value.</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>Supera el total de la mano del repartidor sin pasarte de 21. Cartas de Figura = 10, Ases = 1 u 11, Cartas Numéricas = valor nominal.</t>
-        </is>
-      </c>
       <c r="F487" t="b">
         <v>1</v>
       </c>
@@ -15117,20 +15117,80 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
+          <t>HelpGuideVideoPoker</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>help_videopoker_no_stress</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>No Stress Mode RuleSection body</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Enabling No Stress Mode in Options switches the game into Free Play—hiding bets, credits, and pay tables so you can play risk-free without wagers.</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Activar el Modo Sin Estrés en Opciones cambia el juego a Juego Libre—ocultando apuestas, créditos y tablas de pagos para que puedas jugar sin riesgos ni apuestas.</t>
+        </is>
+      </c>
+      <c r="F488" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
           <t>HelpGuideBlackjack</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>help_blackjack_objective</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Overview RuleSection body</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Outscore the dealer's hand total without exceeding 21. Face cards = 10, Aces = 1 or 11, Number cards = face value.</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Supera el total de la mano del repartidor sin pasarte de 21. Cartas de Figura = 10, Ases = 1 u 11, Cartas Numéricas = valor nominal.</t>
+        </is>
+      </c>
+      <c r="F489" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>HelpGuideBlackjack</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
         <is>
           <t>help_blackjack_rules</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr">
+      <c r="C490" t="inlineStr">
         <is>
           <t>Rules &amp; Options RuleSection body</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr">
+      <c r="D490" t="inlineStr">
         <is>
           <t>1. Place Bet &amp; Deal: Select your chip wager (1, 5, 10, 25) or press Bet Max (M), then press Deal (Space).
 2. Your Turn:
@@ -15145,7 +15205,7 @@
 • Push (Tie): Bet is returned.</t>
         </is>
       </c>
-      <c r="E488" t="inlineStr">
+      <c r="E490" t="inlineStr">
         <is>
           <t>1. Haz Apuesta y Reparte: Selecciona tu apuesta en fichas (1, 5, 10, 25) o presiona Apuesta Máxima (M), luego presiona Repartir (Espacio).
 2. Tu Turno:
@@ -15160,100 +15220,40 @@
 • Empate (Push): Se devuelve la apuesta.</t>
         </is>
       </c>
-      <c r="F488" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
+      <c r="F490" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
         <is>
           <t>HelpGuideBlackjack</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
+      <c r="B491" t="inlineStr">
         <is>
           <t>help_blackjack_strategy</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
+      <c r="C491" t="inlineStr">
         <is>
           <t>Strategy &amp; Pro Tips RuleSection body</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr">
+      <c r="D491" t="inlineStr">
         <is>
           <t>1. Always Split Aces and 8s: Never split 10s or 5s.
 2. Double Down on 11: Always Double Down when your starting hand totals 11 against a dealer 2 through 10.
 3. Watch the Dealer's Upcard: If the dealer shows a 2 through 6, they have a high chance of busting—stand on hard 12 or higher and let the dealer draw.</t>
         </is>
       </c>
-      <c r="E489" t="inlineStr">
+      <c r="E491" t="inlineStr">
         <is>
           <t>1. Siempre Divide Ases y 8s: Nunca dividas 10s o 5s.
 2. Dobla con 11: Siempre Dobla cuando tu mano inicial sume 11 contra un repartidor del 2 al 10.
 3. Observa la Carta Abierta del Repartidor: Si el repartidor muestra del 2 al 6, tiene una alta probabilidad de pasarse—plántate con 12 duro o más y deja que el repartidor robe.</t>
         </is>
       </c>
-      <c r="F489" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>HelpGuideBlackjack</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>help_blackjack_no_stress</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>No Stress Mode RuleSection body</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>Enabling No Stress Mode in Options switches the game into Free Play—hiding bets and credits so you can play risk-free without wagers.</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>Activar el Modo Sin Estrés en Opciones cambia el juego a Juego Libre—ocultando apuestas y créditos para que puedas jugar sin riesgos ni apuestas.</t>
-        </is>
-      </c>
-      <c r="F490" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>HelpGuideHoneycomb</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>help_honeycomb_objective</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>Overview RuleSection body</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>Battle an AI opponent on a 3×3 grid using a 5-card deck. Each card features 4 directional stats (Top, Right, Bottom, Left). Place cards strategically to flip enemy cards to your color. Whoever controls the majority of the 9 grid cells at the end wins!</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr">
-        <is>
-          <t>Lucha contra un oponente de la IA en una cuadrícula de 3×3 usando un mazo de 5 cartas. Cada carta cuenta con 4 estadísticas direccionales (Arriba, Derecha, Abajo, Izquierda). Coloca las cartas estratégicamente para voltear las cartas enemigas a tu color. ¡Quien controle la mayoría de las 9 celdas al final gana!</t>
-        </is>
-      </c>
       <c r="F491" t="b">
         <v>1</v>
       </c>
@@ -15261,52 +15261,112 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
+          <t>HelpGuideBlackjack</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>help_blackjack_no_stress</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>No Stress Mode RuleSection body</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Enabling No Stress Mode in Options switches the game into Free Play—hiding bets and credits so you can play risk-free without wagers.</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Activar el Modo Sin Estrés en Opciones cambia el juego a Juego Libre—ocultando apuestas y créditos para que puedas jugar sin riesgos ni apuestas.</t>
+        </is>
+      </c>
+      <c r="F492" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
           <t>HelpGuideHoneycomb</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>help_honeycomb_objective</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Overview RuleSection body</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Battle an AI opponent on a 3×3 grid using a 5-card deck. Each card features 4 directional stats (Top, Right, Bottom, Left). Place cards strategically to flip enemy cards to your color. Whoever controls the majority of the 9 grid cells at the end wins!</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Lucha contra un oponente de la IA en una cuadrícula de 3×3 usando un mazo de 5 cartas. Cada carta cuenta con 4 estadísticas direccionales (Arriba, Derecha, Abajo, Izquierda). Coloca las cartas estratégicamente para voltear las cartas enemigas a tu color. ¡Quien controle la mayoría de las 9 celdas al final gana!</t>
+        </is>
+      </c>
+      <c r="F493" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>HelpGuideHoneycomb</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
         <is>
           <t>help_honeycomb_mechanics</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
+      <c r="C494" t="inlineStr">
         <is>
           <t>Core Gameplay &amp; Mechanics RuleSection body</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr">
+      <c r="D494" t="inlineStr">
         <is>
           <t>• Capturing: When you place a card adjacent to an opponent's card, your facing stat is compared against their opposite facing stat. If your stat is higher, the enemy card is captured (flipped to your color). Stat 10 is rendered as "A".
 • Hive Minds: A card captured during a turn immediately checks its own adjacent neighbors, triggering a chain-reaction capture sequence!</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr">
+      <c r="E494" t="inlineStr">
         <is>
           <t>• Capturas: Cuando colocas una carta adyacente a la de un oponente, tu estadística de cara se compara con su estadística de cara opuesta. Si tu estadística es mayor, la carta enemiga es capturada (volteada a tu color). La estadística 10 se representa como "A".
 • Mentes Colmena: ¡Una carta capturada durante un turno revisa de inmediato a sus propios vecinos adyacentes, desencadenando una secuencia de captura en reacción en cadena!</t>
         </is>
       </c>
-      <c r="F492" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
+      <c r="F494" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
         <is>
           <t>HelpGuideHoneycomb</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B495" t="inlineStr">
         <is>
           <t>help_honeycomb_card_bank</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
+      <c r="C495" t="inlineStr">
         <is>
           <t>Card Bank &amp; Stealing RuleSection body</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr">
+      <c r="D495" t="inlineStr">
         <is>
           <t>• Steal Mechanics: After winning a match, double-click an eligible dealer card to permanently steal it into your Card Bank! Only one steal is allowed per match.
 • Deck Rarity Caps: Custom decks are limited to: at most one 5★ card, and at most one 4★ card if a 5★ is present (or up to two 4★ cards without a 5★).
@@ -15314,7 +15374,7 @@
 • Steal Protection: Stuck in a Rematch chain against an opponent whose cards you just can't seem to capture? Win two Rematches in a row against the same opponent with nothing eligible to steal, and any not-yet-unlocked card left on the board becomes stealable on that second win — captured or not. Once triggered, it stays active for the rest of that Rematch chain, so every future win keeps offering a steal — you won't have to re-earn it. Starting a fresh New Game (a new opponent) is what turns it back off.</t>
         </is>
       </c>
-      <c r="E493" t="inlineStr">
+      <c r="E495" t="inlineStr">
         <is>
           <t>• Mecánica de Robo: Después de ganar una partida, ¡haz doble clic en una carta elegible del repartidor para robarla permanentemente hacia tu Banco de Cartas! Solo se permite un robo por partida.
 • Límites de Rareza de Mazo: Los mazos personalizados están limitados a: como máximo una carta de 5★, y como máximo una carta de 4★ si hay una de 5★ presente (o hasta dos cartas de 4★ sin una de 5★).
@@ -15322,57 +15382,57 @@
 • Protección Anti-Robo: ¿Atrapado en una cadena de Revanchas contra un oponente cuyas cartas parece que no puedes capturar? Gana dos Revanchas seguidas contra el mismo oponente sin que haya nada elegible para robar, y cualquier carta aún no desbloqueada que quede en el tablero se vuelve robable en esa segunda victoria — capturada o no. Una vez activada, se mantiene activa para el resto de esa cadena de Revanchas, para que cada victoria futura siga ofreciendo un robo — no tendrás que volver a ganarlo. Comenzar una Nueva Partida (un nuevo oponente) es lo que la desactiva.</t>
         </is>
       </c>
-      <c r="F493" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
+      <c r="F495" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
         <is>
           <t>HelpGuideHoneycomb</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B496" t="inlineStr">
         <is>
           <t>help_honeycomb_no_stress</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
+      <c r="C496" t="inlineStr">
         <is>
           <t>No Stress Mode RuleSection body</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr">
+      <c r="D496" t="inlineStr">
         <is>
           <t>Enabling No Stress Mode in Options supplies you with a fixed strong deck every match and hides the Card Steal mechanics.</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr">
+      <c r="E496" t="inlineStr">
         <is>
           <t>Activar el Modo Sin Estrés en Opciones te proporciona un mazo fuerte fijo en cada partida y oculta las mecánicas de Robo de Cartas.</t>
         </is>
       </c>
-      <c r="F494" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
+      <c r="F496" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
         <is>
           <t>HelpGuideCustomization</t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
+      <c r="B497" t="inlineStr">
         <is>
           <t>help_customization_themes</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
+      <c r="C497" t="inlineStr">
         <is>
           <t>Themes &amp; Customization RuleSection body, ThemesHelpView</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr">
+      <c r="D497" t="inlineStr">
         <is>
           <t>• Felt Table: Choose from 5 preset felt colors (Green, Crimson, Royal Blue, Charcoal, Desert) or set a Custom Color via picker. Toggle edge vignette on/off.
 • Card Backs: Select built-in designs or upload custom .jpg/.png/.gif files.
@@ -15380,7 +15440,7 @@
 • Saved Themes: Snapshot your custom felt, card backs, and face art into named custom themes to apply anytime in one click!</t>
         </is>
       </c>
-      <c r="E495" t="inlineStr">
+      <c r="E497" t="inlineStr">
         <is>
           <t>• Mesa de Fieltro: Elige entre 5 colores de fieltro preestablecidos (Verde, Carmesí, Azul Real, Carbón, Desierto) o establece un Color Personalizado. Activa/desactiva la viñeta de los bordes.
 • Reversos de Cartas: Selecciona diseños incorporados o sube archivos .jpg/.png/.gif personalizados.
@@ -15388,100 +15448,40 @@
 • Temas Guardados: ¡Guarda un instante de tu fieltro, reversos de cartas y arte de figuras en temas personalizados con nombre para aplicarlos en cualquier momento con un solo clic!</t>
         </is>
       </c>
-      <c r="F495" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
+      <c r="F497" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
         <is>
           <t>HelpGuideCustomization</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
+      <c r="B498" t="inlineStr">
         <is>
           <t>help_customization_options</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
+      <c r="C498" t="inlineStr">
         <is>
           <t>Options RuleSection body, ThemesHelpView</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr">
+      <c r="D498" t="inlineStr">
         <is>
           <t>• Honey Mode (Flavor): Global toggle across all 6 games — controls the "+N"/"-N" score popups and whether flavor/ambiance banners appear. Turn it off for a quieter, more minimal play experience.
 • Stay on Top: Keeps the game window pinned above your other windows (View menu).
 • Sound Effects, Vegas Scoring, and Hide Hint Button are also available here per-game.</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr">
+      <c r="E498" t="inlineStr">
         <is>
           <t>• Modo Miel (Sabor): Interruptor global en los 6 juegos — controla las ventanas emergentes de puntuación "+N"/"-N" y si aparecen los carteles de sabor/ambiente. Desactívalo para una experiencia de juego más silenciosa y minimalista.
 • Siempre Encima: Mantiene la ventana del juego anclada sobre tus otras ventanas (Menú Vista).
 • Efectos de Sonido, Puntuación Vegas, y Ocultar Botón de Pistas también están disponibles aquí por juego.</t>
         </is>
       </c>
-      <c r="F496" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>HelpGuideCommon</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>help_klondike_title</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>HelpShell title, KlondikeHelpView</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>Klondike Solitaire</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>Solitario Klondike</t>
-        </is>
-      </c>
-      <c r="F497" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>HelpGuideKlondike</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>help_klondike_subtitle</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>HelpShell subtitle, KlondikeHelpView</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Classic single-deck solitaire with Draw 1, Draw 3, and Vegas scoring options.</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>Clásico solitario de un mazo con opciones de Robar 1, Robar 3 y puntuación Vegas.</t>
-        </is>
-      </c>
       <c r="F498" t="b">
         <v>1</v>
       </c>
@@ -15489,27 +15489,27 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>HelpGuideBeecell</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>help_beecell_subtitle</t>
+          <t>help_klondike_title</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>HelpShell subtitle, BeecellHelpView</t>
+          <t>HelpShell title, KlondikeHelpView</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>The ultimate strategic solitaire game—99.9% of all deals are solvable.</t>
+          <t>Klondike Solitaire</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>El juego de solitario estratégico definitivo: el 99.9% de los repartos tienen solución.</t>
+          <t>Solitario Klondike</t>
         </is>
       </c>
       <c r="F499" t="b">
@@ -15519,27 +15519,27 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>HelpGuideKlondike</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>help_spider_title</t>
+          <t>help_klondike_subtitle</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>HelpShell title, SpiderHelpView</t>
+          <t>HelpShell subtitle, KlondikeHelpView</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Spider Solitaire</t>
+          <t>Classic single-deck solitaire with Draw 1, Draw 3, and Vegas scoring options.</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Solitario Spider</t>
+          <t>Clásico solitario de un mazo con opciones de Robar 1, Robar 3 y puntuación Vegas.</t>
         </is>
       </c>
       <c r="F500" t="b">
@@ -15549,27 +15549,27 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>HelpGuideSpider</t>
+          <t>HelpGuideBeecell</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>help_spider_subtitle</t>
+          <t>help_beecell_subtitle</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>HelpShell subtitle, SpiderHelpView</t>
+          <t>HelpShell subtitle, BeecellHelpView</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>A deep, two-deck game of sequence building across 1, 2, or 4 suits.</t>
+          <t>The ultimate strategic solitaire game—99.9% of all deals are solvable.</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Un juego profundo de dos mazos sobre construcción de secuencias con 1, 2 o 4 palos.</t>
+          <t>El juego de solitario estratégico definitivo: el 99.9% de los repartos tienen solución.</t>
         </is>
       </c>
       <c r="F501" t="b">
@@ -15584,22 +15584,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>help_videopoker_title</t>
+          <t>help_spider_title</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>HelpShell title, VideoPokerHelpView (identical text to gamemode_videopoker_display — kept as separate key since one is Help chrome, one is a game-mode label)</t>
+          <t>HelpShell title, SpiderHelpView</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Video Poker</t>
+          <t>Spider Solitaire</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Video Póker</t>
+          <t>Solitario Spider</t>
         </is>
       </c>
       <c r="F502" t="b">
@@ -15609,27 +15609,27 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>HelpGuideVideoPoker</t>
+          <t>HelpGuideSpider</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>help_videopoker_subtitle</t>
+          <t>help_spider_subtitle</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>HelpShell subtitle, VideoPokerHelpView</t>
+          <t>HelpShell subtitle, SpiderHelpView</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Classic casino poker with Jacks or Better, Deuces Wild, and Bonus Poker pay tables.</t>
+          <t>A deep, two-deck game of sequence building across 1, 2, or 4 suits.</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Póker clásico de casino con tablas de pagos de Jacks or Better, Deuces Wild y Bonus Poker.</t>
+          <t>Un juego profundo de dos mazos sobre construcción de secuencias con 1, 2 o 4 palos.</t>
         </is>
       </c>
       <c r="F503" t="b">
@@ -15644,52 +15644,52 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>help_blackjack_title</t>
+          <t>help_videopoker_title</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>HelpShell title, BlackjackHelpView</t>
+          <t>HelpShell title, VideoPokerHelpView (identical text to gamemode_videopoker_display — kept as separate key since one is Help chrome, one is a game-mode label)</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Video Blackjack</t>
+          <t>Video Poker</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Video Blackjack</t>
+          <t>Video Póker</t>
         </is>
       </c>
       <c r="F504" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>HelpGuideBlackjack</t>
+          <t>HelpGuideVideoPoker</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>help_blackjack_subtitle</t>
+          <t>help_videopoker_subtitle</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>HelpShell subtitle, BlackjackHelpView</t>
+          <t>HelpShell subtitle, VideoPokerHelpView</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Beat the dealer by getting closer to 21 without going over.</t>
+          <t>Classic casino poker with Jacks or Better, Deuces Wild, and Bonus Poker pay tables.</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Vence al repartidor acercándote más a 21 sin pasarte.</t>
+          <t>Póker clásico de casino con tablas de pagos de Jacks or Better, Deuces Wild y Bonus Poker.</t>
         </is>
       </c>
       <c r="F505" t="b">
@@ -15704,52 +15704,52 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>help_themes_title</t>
+          <t>help_blackjack_title</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>HelpShell title, ThemesHelpView</t>
+          <t>HelpShell title, BlackjackHelpView</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Themes &amp; Global Settings</t>
+          <t>Video Blackjack</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Temas y Configuración Global</t>
+          <t>Video Blackjack</t>
         </is>
       </c>
       <c r="F506" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>HelpGuideCustomization</t>
+          <t>HelpGuideBlackjack</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>help_themes_subtitle</t>
+          <t>help_blackjack_subtitle</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>HelpShell subtitle, ThemesHelpView</t>
+          <t>HelpShell subtitle, BlackjackHelpView</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Customize the look of every game and adjust global modes.</t>
+          <t>Beat the dealer by getting closer to 21 without going over.</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Personaliza la apariencia de cada juego y ajusta los modos globales.</t>
+          <t>Vence al repartidor acercándote más a 21 sin pasarte.</t>
         </is>
       </c>
       <c r="F507" t="b">
@@ -15764,22 +15764,22 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>help_setup_layout_title</t>
+          <t>help_themes_title</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>RuleSection title, shared Klondike/Beecell/Spider</t>
+          <t>HelpShell title, ThemesHelpView</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>🃏 Setup &amp; Layout</t>
+          <t>Themes &amp; Global Settings</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>🃏 Preparación y Disposición</t>
+          <t>Temas y Configuración Global</t>
         </is>
       </c>
       <c r="F508" t="b">
@@ -15789,27 +15789,27 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>HelpGuideCustomization</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>help_rules_how_to_play_title</t>
+          <t>help_themes_subtitle</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>RuleSection title, shared Klondike/Beecell/Spider</t>
+          <t>HelpShell subtitle, ThemesHelpView</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>🎮 Rules &amp; How to Play</t>
+          <t>Customize the look of every game and adjust global modes.</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>🎮 Reglas y Cómo Jugar</t>
+          <t>Personaliza la apariencia de cada juego y ajusta los modos globales.</t>
         </is>
       </c>
       <c r="F509" t="b">
@@ -15819,27 +15819,27 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>HelpGuideBlackjack</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>help_rules_options_title</t>
+          <t>help_setup_layout_title</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>RuleSection title, Blackjack</t>
+          <t>RuleSection title, shared Klondike/Beecell/Spider</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>🎮 Rules &amp; Options</t>
+          <t>🃏 Setup &amp; Layout</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>🎮 Reglas y Opciones</t>
+          <t>🃏 Preparación y Disposición</t>
         </is>
       </c>
       <c r="F510" t="b">
@@ -15849,27 +15849,27 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>HelpGuideHoneycomb</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>help_match_modifiers_title</t>
+          <t>help_rules_how_to_play_title</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>RuleSection title, Honeycomb</t>
+          <t>RuleSection title, shared Klondike/Beecell/Spider</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>🎲 Match Modifiers &amp; Special Rules</t>
+          <t>🎮 Rules &amp; How to Play</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>🎲 Modificadores de Partida y Reglas Especiales</t>
+          <t>🎮 Reglas y Cómo Jugar</t>
         </is>
       </c>
       <c r="F511" t="b">
@@ -15879,27 +15879,27 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>HelpGuideHoneycomb</t>
+          <t>HelpGuideBlackjack</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>help_card_bank_stealing_title</t>
+          <t>help_rules_options_title</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>RuleSection title, Honeycomb</t>
+          <t>RuleSection title, Blackjack</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>🏆 Card Bank &amp; Stealing</t>
+          <t>🎮 Rules &amp; Options</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>🏆 Banco de Cartas y Robos</t>
+          <t>🎮 Reglas y Opciones</t>
         </is>
       </c>
       <c r="F512" t="b">
@@ -15909,27 +15909,27 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>HelpGuideCustomization</t>
+          <t>HelpGuideHoneycomb</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>help_themes_customization_title</t>
+          <t>help_match_modifiers_title</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>RuleSection title, ThemesHelpView</t>
+          <t>RuleSection title, Honeycomb</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>🎨 Themes &amp; Customization</t>
+          <t>🎲 Match Modifiers &amp; Special Rules</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>🎨 Temas y Personalización</t>
+          <t>🎲 Modificadores de Partida y Reglas Especiales</t>
         </is>
       </c>
       <c r="F513" t="b">
@@ -15939,27 +15939,27 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>HelpGuideCustomization</t>
+          <t>HelpGuideHoneycomb</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>help_options_title</t>
+          <t>help_card_bank_stealing_title</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>RuleSection title, ThemesHelpView</t>
+          <t>RuleSection title, Honeycomb</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>⚙️ Options</t>
+          <t>🏆 Card Bank &amp; Stealing</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>⚙️ Opciones</t>
+          <t>🏆 Banco de Cartas y Robos</t>
         </is>
       </c>
       <c r="F514" t="b">
@@ -15969,27 +15969,27 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>HelpGuideCustomization</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>help_shortcut_navigate_board_cursor</t>
+          <t>help_themes_customization_title</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Klondike</t>
+          <t>RuleSection title, ThemesHelpView</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Navigate Board Cursor</t>
+          <t>🎨 Themes &amp; Customization</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Navegar Cursor del Tablero</t>
+          <t>🎨 Temas y Personalización</t>
         </is>
       </c>
       <c r="F515" t="b">
@@ -15999,27 +15999,27 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>HelpGuideCustomization</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>help_shortcut_clear_selection</t>
+          <t>help_options_title</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Klondike</t>
+          <t>RuleSection title, ThemesHelpView</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Clear Selection</t>
+          <t>⚙️ Options</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Borrar Selección</t>
+          <t>⚙️ Opciones</t>
         </is>
       </c>
       <c r="F516" t="b">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>help_shortcut_draw_cards</t>
+          <t>help_shortcut_navigate_board_cursor</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -16044,12 +16044,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Draw Card(s)</t>
+          <t>Navigate Board Cursor</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Robar Carta(s)</t>
+          <t>Navegar Cursor del Tablero</t>
         </is>
       </c>
       <c r="F517" t="b">
@@ -16064,22 +16064,22 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>help_shortcut_auto_move_foundation</t>
+          <t>help_shortcut_clear_selection</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>ShortcutRow action, shared Klondike/Beecell</t>
+          <t>ShortcutRow action, Klondike</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Auto-Move to Foundation</t>
+          <t>Clear Selection</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Mover Automáticamente a la Fundación</t>
+          <t>Borrar Selección</t>
         </is>
       </c>
       <c r="F518" t="b">
@@ -16094,22 +16094,22 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>help_shortcut_new_game_restart_deal</t>
+          <t>help_shortcut_draw_cards</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>ShortcutRow action, shared Klondike/Beecell</t>
+          <t>ShortcutRow action, Klondike</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>New Game / Restart Deal</t>
+          <t>Draw Card(s)</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Nueva Partida / Reiniciar Reparto</t>
+          <t>Robar Carta(s)</t>
         </is>
       </c>
       <c r="F519" t="b">
@@ -16124,22 +16124,22 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>help_shortcut_undo_move</t>
+          <t>help_shortcut_auto_move_foundation</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>ShortcutRow action, shared Klondike/Beecell/Spider</t>
+          <t>ShortcutRow action, shared Klondike/Beecell</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Undo Move</t>
+          <t>Auto-Move to Foundation</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Deshacer Movimiento</t>
+          <t>Mover Automáticamente a la Fundación</t>
         </is>
       </c>
       <c r="F520" t="b">
@@ -16149,27 +16149,27 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>HelpGuideKlondike</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>help_shortcut_toggle_draw</t>
+          <t>help_shortcut_new_game_restart_deal</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut label — actually this row's English is the ACTION text, not the ⌥⌘ shortcut value; Klondike only</t>
+          <t>ShortcutRow action, shared Klondike/Beecell</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Toggle Draw 1 / Draw 3</t>
+          <t>New Game / Restart Deal</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Alternar Robar 1 / Robar 3</t>
+          <t>Nueva Partida / Reiniciar Reparto</t>
         </is>
       </c>
       <c r="F521" t="b">
@@ -16179,27 +16179,27 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>HelpGuideKlondike</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>help_shortcut_cycle_hints</t>
+          <t>help_shortcut_undo_move</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Klondike</t>
+          <t>ShortcutRow action, shared Klondike/Beecell/Spider</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Cycle Available Hints</t>
+          <t>Undo Move</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Alternar Pistas Disponibles</t>
+          <t>Deshacer Movimiento</t>
         </is>
       </c>
       <c r="F522" t="b">
@@ -16209,27 +16209,27 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>HelpGuideKlondike</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>help_shortcut_hint_button</t>
+          <t>help_shortcut_toggle_draw</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, shared Klondike/Beecell/Honeycomb</t>
+          <t>ShortcutRow shortcut label — actually this row's English is the ACTION text, not the ⌥⌘ shortcut value; Klondike only</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Hint button</t>
+          <t>Toggle Draw 1 / Draw 3</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Botón de Pista</t>
+          <t>Alternar Robar 1 / Robar 3</t>
         </is>
       </c>
       <c r="F523" t="b">
@@ -16239,27 +16239,27 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>HelpGuideBeecell</t>
+          <t>HelpGuideKlondike</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>help_shortcut_auto_park_free_cell</t>
+          <t>help_shortcut_cycle_hints</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Beecell</t>
+          <t>ShortcutRow action, Klondike</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Auto-Park to Free Cell</t>
+          <t>Cycle Available Hints</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Aparcar Automáticamente en Celda Libre</t>
+          <t>Alternar Pistas Disponibles</t>
         </is>
       </c>
       <c r="F524" t="b">
@@ -16269,27 +16269,27 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>HelpGuideBeecell</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>help_shortcut_arrow_space_enter</t>
+          <t>help_shortcut_hint_button</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, Beecell (compound form)</t>
+          <t>ShortcutRow shortcut value, shared Klondike/Beecell/Honeycomb</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Arrow Keys + Space / Enter</t>
+          <t>Hint button</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Teclas de Flecha + Espacio / Intro</t>
+          <t>Botón de Pista</t>
         </is>
       </c>
       <c r="F525" t="b">
@@ -16299,27 +16299,27 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>HelpGuideSpider</t>
+          <t>HelpGuideBeecell</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>help_shortcut_deal_10_cards</t>
+          <t>help_shortcut_auto_park_free_cell</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Spider</t>
+          <t>ShortcutRow action, Beecell</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Deal 10 Cards from Stock</t>
+          <t>Auto-Park to Free Cell</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Repartir 10 Cartas de la Pila</t>
+          <t>Aparcar Automáticamente en Celda Libre</t>
         </is>
       </c>
       <c r="F526" t="b">
@@ -16329,27 +16329,27 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>HelpGuideSpider</t>
+          <t>HelpGuideBeecell</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>help_shortcut_1suit_2suit_mode</t>
+          <t>help_shortcut_arrow_space_enter</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Spider</t>
+          <t>ShortcutRow shortcut value, Beecell (compound form)</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>1-Suit / 2-Suit Mode</t>
+          <t>Arrow Keys + Space / Enter</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Modo de 1 Palo / 2 Palos</t>
+          <t>Teclas de Flecha + Espacio / Intro</t>
         </is>
       </c>
       <c r="F527" t="b">
@@ -16359,27 +16359,27 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>HelpGuideSpider</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>help_shortcut_autocomplete</t>
+          <t>help_shortcut_deal_10_cards</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>ShortcutRow action, shared Spider/(short form)</t>
+          <t>ShortcutRow action, Spider</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Autocomplete</t>
+          <t>Deal 10 Cards from Stock</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Autocompletar</t>
+          <t>Repartir 10 Cartas de la Pila</t>
         </is>
       </c>
       <c r="F528" t="b">
@@ -16389,27 +16389,27 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>HelpGuideVideoPoker</t>
+          <t>HelpGuideSpider</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>help_shortcut_deal_draw</t>
+          <t>help_shortcut_1suit_2suit_mode</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Video Poker</t>
+          <t>ShortcutRow action, Spider</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Deal / Draw</t>
+          <t>1-Suit / 2-Suit Mode</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Repartir / Robar</t>
+          <t>Modo de 1 Palo / 2 Palos</t>
         </is>
       </c>
       <c r="F529" t="b">
@@ -16419,27 +16419,27 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>HelpGuideVideoPoker</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>help_shortcut_hold_card_12345</t>
+          <t>help_shortcut_autocomplete</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Video Poker</t>
+          <t>ShortcutRow action, shared Spider/(short form)</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Hold Card 1, 2, 3, 4, 5</t>
+          <t>Autocomplete</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Retener Carta 1, 2, 3, 4, 5</t>
+          <t>Autocompletar</t>
         </is>
       </c>
       <c r="F530" t="b">
@@ -16454,26 +16454,26 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>help_shortcut_12345</t>
+          <t>help_shortcut_deal_draw</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>ShortcutRow shortcut value, Video Poker</t>
+          <t>ShortcutRow action, Video Poker</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>1, 2, 3, 4, 5</t>
+          <t>Deal / Draw</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>1, 2, 3, 4, 5</t>
+          <t>Repartir / Robar</t>
         </is>
       </c>
       <c r="F531" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>help_shortcut_hold_all_cards</t>
+          <t>help_shortcut_hold_card_12345</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -16494,12 +16494,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Hold All Cards</t>
+          <t>Hold Card 1, 2, 3, 4, 5</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Retener Todas las Cartas</t>
+          <t>Retener Carta 1, 2, 3, 4, 5</t>
         </is>
       </c>
       <c r="F532" t="b">
@@ -16509,57 +16509,57 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>HelpGuideVideoPoker</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>help_shortcut_bet_max_deal</t>
+          <t>help_shortcut_12345</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>ShortcutRow action, shared VideoPoker/Blackjack</t>
+          <t>ShortcutRow shortcut value, Video Poker</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Bet Max &amp; Deal</t>
+          <t>1, 2, 3, 4, 5</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Apuesta Máxima y Repartir</t>
+          <t>1, 2, 3, 4, 5</t>
         </is>
       </c>
       <c r="F533" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>HelpGuideBlackjack</t>
+          <t>HelpGuideVideoPoker</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>help_shortcut_deal_buy_in</t>
+          <t>help_shortcut_hold_all_cards</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Blackjack</t>
+          <t>ShortcutRow action, Video Poker</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Deal / Buy In</t>
+          <t>Hold All Cards</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Repartir / Comprar Fichas</t>
+          <t>Retener Todas las Cartas</t>
         </is>
       </c>
       <c r="F534" t="b">
@@ -16569,27 +16569,27 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>HelpGuideBlackjack</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>help_shortcut_hit</t>
+          <t>help_shortcut_bet_max_deal</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Blackjack</t>
+          <t>ShortcutRow action, shared VideoPoker/Blackjack</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Bet Max &amp; Deal</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Pedir</t>
+          <t>Apuesta Máxima y Repartir</t>
         </is>
       </c>
       <c r="F535" t="b">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>help_shortcut_stand</t>
+          <t>help_shortcut_deal_buy_in</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -16614,12 +16614,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Deal / Buy In</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Plantarse</t>
+          <t>Repartir / Comprar Fichas</t>
         </is>
       </c>
       <c r="F536" t="b">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>help_shortcut_double_down</t>
+          <t>help_shortcut_hit</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -16644,12 +16644,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Double Down</t>
+          <t>Hit</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Doblar</t>
+          <t>Pedir</t>
         </is>
       </c>
       <c r="F537" t="b">
@@ -16659,27 +16659,27 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>HoneycombRules</t>
+          <t>HelpGuideBlackjack</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>rule_name_pollination</t>
+          <t>help_shortcut_stand</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>HoneycombRule.ascension.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>ShortcutRow action, Blackjack</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>Pollination</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Polinización</t>
+          <t>Plantarse</t>
         </is>
       </c>
       <c r="F538" t="b">
@@ -16689,27 +16689,27 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>HoneycombRules</t>
+          <t>HelpGuideBlackjack</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>rule_name_smoked_out</t>
+          <t>help_shortcut_double_down</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>HoneycombRule.descension.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>ShortcutRow action, Blackjack</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Smoked Out</t>
+          <t>Double Down</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Ahumado</t>
+          <t>Doblar</t>
         </is>
       </c>
       <c r="F539" t="b">
@@ -16724,22 +16724,22 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>rule_name_symmetry</t>
+          <t>rule_name_pollination</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>HoneycombRule.same.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.ascension.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Symmetry</t>
+          <t>Pollination</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Simetría</t>
+          <t>Polinización</t>
         </is>
       </c>
       <c r="F540" t="b">
@@ -16754,22 +16754,22 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>rule_name_math_bee</t>
+          <t>rule_name_smoked_out</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>HoneycombRule.plus.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.descension.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Math Bee</t>
+          <t>Smoked Out</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Abeja Matemática</t>
+          <t>Ahumado</t>
         </is>
       </c>
       <c r="F541" t="b">
@@ -16784,22 +16784,22 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>rule_name_queens_fall</t>
+          <t>rule_name_symmetry</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>HoneycombRule.fallenAce.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.same.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Queen's Fall</t>
+          <t>Symmetry</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Caída de la Reina</t>
+          <t>Simetría</t>
         </is>
       </c>
       <c r="F542" t="b">
@@ -16814,22 +16814,22 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>rule_name_inversion</t>
+          <t>rule_name_math_bee</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>HoneycombRule.reverse.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.plus.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Inversion</t>
+          <t>Math Bee</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Inversión</t>
+          <t>Abeja Matemática</t>
         </is>
       </c>
       <c r="F543" t="b">
@@ -16844,22 +16844,22 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>rule_name_clear_skies</t>
+          <t>rule_name_queens_fall</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>HoneycombRule.allOpen.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.fallenAce.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Clear Skies</t>
+          <t>Queen's Fall</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Cielos Despejados</t>
+          <t>Caída de la Reina</t>
         </is>
       </c>
       <c r="F544" t="b">
@@ -16874,22 +16874,22 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>rule_name_hierarchy</t>
+          <t>rule_name_inversion</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>HoneycombRule.order.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.reverse.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Hierarchy</t>
+          <t>Inversion</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Jerarquía</t>
+          <t>Inversión</t>
         </is>
       </c>
       <c r="F545" t="b">
@@ -16904,22 +16904,22 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>rule_name_frenzy</t>
+          <t>rule_name_clear_skies</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>HoneycombRule.chaos.rawValue — display-only translation, rawValue itself stays English</t>
+          <t>HoneycombRule.allOpen.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Frenzy</t>
+          <t>Clear Skies</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Frenesí</t>
+          <t>Cielos Despejados</t>
         </is>
       </c>
       <c r="F546" t="b">
@@ -16934,22 +16934,22 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>rule_explanation_same</t>
+          <t>rule_name_hierarchy</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>HoneycombRule.same.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.order.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>If 2+ touching neighbor stats match your card's facing stats, all matching neighbors are captured simultaneously.</t>
+          <t>Hierarchy</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Si 2+ estadísticas de vecinos en contacto coinciden con las estadísticas de cara de tu carta, todos los vecinos coincidentes se capturan simultáneamente.</t>
+          <t>Jerarquía</t>
         </is>
       </c>
       <c r="F547" t="b">
@@ -16964,22 +16964,22 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>rule_explanation_plus</t>
+          <t>rule_name_frenzy</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>HoneycombRule.plus.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.chaos.rawValue — display-only translation, rawValue itself stays English</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>If the sum of (your stat + neighbor's stat) equals the same total across 2+ neighbors, all involved cards are captured.</t>
+          <t>Frenzy</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Si la suma de (tu estadística + la estadística del vecino) iguala el mismo total en 2+ vecinos, todas las cartas involucradas son capturadas.</t>
+          <t>Frenesí</t>
         </is>
       </c>
       <c r="F548" t="b">
@@ -16994,22 +16994,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>rule_explanation_fallen_ace</t>
+          <t>rule_explanation_same</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>HoneycombRule.fallenAce.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.same.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>A card with a stat of 1 attacking a 10 ("A") always captures it! If Inversion is also active, this flips: a 10 ("A") captures a 1 instead.</t>
+          <t>If 2+ touching neighbor stats match your card's facing stats, all matching neighbors are captured simultaneously.</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>¡Una carta con una estadística de 1 atacando a un 10 ("A") siempre lo captura! Si Inversión también está activa, esto se voltea: un 10 ("A") captura a un 1 en su lugar.</t>
+          <t>Si 2+ estadísticas de vecinos en contacto coinciden con las estadísticas de cara de tu carta, todos los vecinos coincidentes se capturan simultáneamente.</t>
         </is>
       </c>
       <c r="F549" t="b">
@@ -17024,22 +17024,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>rule_explanation_ascension_generic</t>
+          <t>rule_explanation_plus</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>HoneycombRule.ascension.explanation() generic (no suits yet selected) variant — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.plus.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Grants +1 to stats for all cards matching randomly selected suits as more of that suit enter the board.</t>
+          <t>If the sum of (your stat + neighbor's stat) equals the same total across 2+ neighbors, all involved cards are captured.</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Otorga +1 a las estadísticas de todas las cartas que coincidan con palos seleccionados aleatoriamente a medida que entren más de ese palo en el tablero.</t>
+          <t>Si la suma de (tu estadística + la estadística del vecino) iguala el mismo total en 2+ vecinos, todas las cartas involucradas son capturadas.</t>
         </is>
       </c>
       <c r="F550" t="b">
@@ -17054,22 +17054,22 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>rule_explanation_descension_generic</t>
+          <t>rule_explanation_fallen_ace</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>HoneycombRule.descension.explanation() generic (no suits yet selected) variant — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.fallenAce.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Inflicts -1 to stats for all cards matching randomly selected suits as more of that suit enter the board.</t>
+          <t>A card with a stat of 1 attacking a 10 ("A") always captures it! If Inversion is also active, this flips: a 10 ("A") captures a 1 instead.</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Inflige -1 a las estadísticas de todas las cartas que coincidan con palos seleccionados aleatoriamente a medida que entren más de ese palo en el tablero.</t>
+          <t>¡Una carta con una estadística de 1 atacando a un 10 ("A") siempre lo captura! Si Inversión también está activa, esto se voltea: un 10 ("A") captura a un 1 en su lugar.</t>
         </is>
       </c>
       <c r="F551" t="b">
@@ -17084,22 +17084,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>rule_explanation_order</t>
+          <t>rule_explanation_ascension_generic</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>HoneycombRule.order.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.ascension.explanation() generic (no suits yet selected) variant — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Forces you to play cards in exact deck sequence.</t>
+          <t>Grants +1 to stats for all cards matching randomly selected suits as more of that suit enter the board.</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Te obliga a jugar las cartas en la secuencia exacta del mazo.</t>
+          <t>Otorga +1 a las estadísticas de todas las cartas que coincidan con palos seleccionados aleatoriamente a medida que entren más de ese palo en el tablero.</t>
         </is>
       </c>
       <c r="F552" t="b">
@@ -17114,22 +17114,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>rule_explanation_all_open</t>
+          <t>rule_explanation_descension_generic</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>HoneycombRule.allOpen.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.descension.explanation() generic (no suits yet selected) variant — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>Both players' hands are completely visible.</t>
+          <t>Inflicts -1 to stats for all cards matching randomly selected suits as more of that suit enter the board.</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Las manos de ambos jugadores son completamente visibles.</t>
+          <t>Inflige -1 a las estadísticas de todas las cartas que coincidan con palos seleccionados aleatoriamente a medida que entren más de ese palo en el tablero.</t>
         </is>
       </c>
       <c r="F553" t="b">
@@ -17144,22 +17144,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>rule_explanation_three_open</t>
+          <t>rule_explanation_order</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>HoneycombRule.threeOpen.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.order.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Three randomly selected cards from each player's hand are visible.</t>
+          <t>Forces you to play cards in exact deck sequence.</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>Tres cartas seleccionadas al azar de la mano de cada jugador son visibles.</t>
+          <t>Te obliga a jugar las cartas en la secuencia exacta del mazo.</t>
         </is>
       </c>
       <c r="F554" t="b">
@@ -17174,22 +17174,22 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>rule_explanation_bomb_shelter</t>
+          <t>rule_explanation_all_open</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>HoneycombRule.bombShelter.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.allOpen.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Each player's first card played remains face-down for 3 turns before flipping automatically.</t>
+          <t>Both players' hands are completely visible.</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>La primera carta jugada de cada jugador permanece boca abajo durante 3 turnos antes de voltearse automáticamente.</t>
+          <t>Las manos de ambos jugadores son completamente visibles.</t>
         </is>
       </c>
       <c r="F555" t="b">
@@ -17204,22 +17204,22 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>rule_explanation_sudden_death</t>
+          <t>rule_explanation_three_open</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>HoneycombRule.suddenDeath.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.threeOpen.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>If the match ends in a draw, a rematch begins immediately.</t>
+          <t>Three randomly selected cards from each player's hand are visible.</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>Si la partida termina en empate, comienza una revancha inmediatamente.</t>
+          <t>Tres cartas seleccionadas al azar de la mano de cada jugador son visibles.</t>
         </is>
       </c>
       <c r="F556" t="b">
@@ -17234,22 +17234,22 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>rule_explanation_swap</t>
+          <t>rule_explanation_bomb_shelter</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>HoneycombRule.swap.explanation() — display-only translation, explanation() source stays English</t>
+          <t>HoneycombRule.bombShelter.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Before the match, one card from your hand is randomly swapped with one of the opponent's.</t>
+          <t>Each player's first card played remains face-down for 3 turns before flipping automatically.</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Antes de la partida, una carta de tu mano se intercambia aleatoriamente con una del oponente.</t>
+          <t>La primera carta jugada de cada jugador permanece boca abajo durante 3 turnos antes de voltearse automáticamente.</t>
         </is>
       </c>
       <c r="F557" t="b">
@@ -17264,22 +17264,22 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>difficulty_easy_rawvalue</t>
+          <t>rule_explanation_sudden_death</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>HoneycombDifficulty.easy.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Baby Bee" is shown); kept for reference/future use, no wiring needed today</t>
+          <t>HoneycombRule.suddenDeath.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>If the match ends in a draw, a rematch begins immediately.</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Si la partida termina en empate, comienza una revancha inmediatamente.</t>
         </is>
       </c>
       <c r="F558" t="b">
@@ -17294,22 +17294,22 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>difficulty_medium_rawvalue</t>
+          <t>rule_explanation_swap</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>HoneycombDifficulty.medium.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Honey Bee" is shown); kept for reference/future use, no wiring needed today</t>
+          <t>HoneycombRule.swap.explanation() — display-only translation, explanation() source stays English</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Before the match, one card from your hand is randomly swapped with one of the opponent's.</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>Antes de la partida, una carta de tu mano se intercambia aleatoriamente con una del oponente.</t>
         </is>
       </c>
       <c r="F559" t="b">
@@ -17324,22 +17324,22 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>difficulty_hard_rawvalue</t>
+          <t>difficulty_easy_rawvalue</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>HoneycombDifficulty.hard.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Queen Bee" is shown); kept for reference/future use, no wiring needed today</t>
+          <t>HoneycombDifficulty.easy.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Baby Bee" is shown); kept for reference/future use, no wiring needed today</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F560" t="b">
@@ -17349,57 +17349,57 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>GameModes</t>
+          <t>HoneycombRules</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>gamemode_beecell_display</t>
+          <t>difficulty_medium_rawvalue</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>GameMode.beecell.displayName — rawValue "Freecell" stays untouched (persisted); translator kept proper noun as-is</t>
+          <t>HoneycombDifficulty.medium.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Honey Bee" is shown); kept for reference/future use, no wiring needed today</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Beecell</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Beecell</t>
+          <t>Medio</t>
         </is>
       </c>
       <c r="F561" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HoneycombRules</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>roulette_colon_prefix</t>
+          <t>difficulty_hard_rawvalue</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>RuleExplanationPopover.swift label prefix, %@ = Roulette translation not needed, plain concat</t>
+          <t>HoneycombDifficulty.hard.rawValue (persisted identifier) — NOT currently rendered anywhere as raw text (only .displayName "Queen Bee" is shown); kept for reference/future use, no wiring needed today</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roulette: </t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ruleta: </t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F562" t="b">
@@ -17409,31 +17409,31 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>GameModes</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>rules_randomized_at_start</t>
+          <t>gamemode_beecell_display</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>RuleExplanationPopover.swift roulette body text</t>
+          <t>GameMode.beecell.displayName — rawValue "Freecell" stays untouched (persisted); translator kept proper noun as-is</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Rules are randomized at the start of the match.</t>
+          <t>Beecell</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Las reglas se seleccionan al azar al inicio de la partida.</t>
+          <t>Beecell</t>
         </is>
       </c>
       <c r="F563" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="564">
@@ -17444,52 +17444,52 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>rule_name_colon_fmt</t>
+          <t>roulette_colon_prefix</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>RuleExplanationPopover.swift rule-name label, %@ = translated rule name</t>
+          <t>RuleExplanationPopover.swift label prefix, %@ = Roulette translation not needed, plain concat</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t xml:space="preserve">%@: </t>
+          <t xml:space="preserve">Roulette: </t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t xml:space="preserve">%@: </t>
+          <t xml:space="preserve">Ruleta: </t>
         </is>
       </c>
       <c r="F564" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>HoneycombRules</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>ban_column_header</t>
+          <t>rules_randomized_at_start</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Column header, HoneycombRulesView.axaml (Windows)</t>
+          <t>RuleExplanationPopover.swift roulette body text</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Ban?</t>
+          <t>Rules are randomized at the start of the match.</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>¿Vetar?</t>
+          <t>Las reglas se seleccionan al azar al inicio de la partida.</t>
         </is>
       </c>
       <c r="F565" t="b">
@@ -17499,31 +17499,31 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>HoneycombRules</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>play_column_header</t>
+          <t>rule_name_colon_fmt</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Column header, HoneycombRulesView.axaml (Windows)</t>
+          <t>RuleExplanationPopover.swift rule-name label, %@ = translated rule name</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t xml:space="preserve">%@: </t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Jugar</t>
+          <t xml:space="preserve">%@: </t>
         </is>
       </c>
       <c r="F566" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567">
@@ -17534,22 +17534,22 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>match_rules_hint_win</t>
+          <t>ban_column_header</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Helper text, HoneycombRulesView.axaml (Windows) — near-identical to matchRulesHint, kept separate since wording differs (match's vs match)</t>
+          <t>Column header, HoneycombRulesView.axaml (Windows)</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Select up to 4 rules. Leave empty to let roulette decide each match's rules.</t>
+          <t>Ban?</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Selecciona hasta 4 reglas. Déjalo vacío para que la ruleta decida las reglas de cada partida.</t>
+          <t>¿Vetar?</t>
         </is>
       </c>
       <c r="F567" t="b">
@@ -17564,22 +17564,22 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>ban_removes_rule_hint</t>
+          <t>play_column_header</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Helper text, HoneycombRulesView.axaml (Windows)</t>
+          <t>Column header, HoneycombRulesView.axaml (Windows)</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Ban removes a rule from the roulette pool entirely.</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Vetar elimina una regla por completo del grupo de la ruleta.</t>
+          <t>Jugar</t>
         </is>
       </c>
       <c r="F568" t="b">
@@ -17594,22 +17594,22 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>opponent_label_colon</t>
+          <t>match_rules_hint_win</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Label, HoneycombRulesView.axaml (Windows) — colon variant of opponentPickerLabel</t>
+          <t>Helper text, HoneycombRulesView.axaml (Windows) — near-identical to matchRulesHint, kept separate since wording differs (match's vs match)</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Opponent:</t>
+          <t>Select up to 4 rules. Leave empty to let roulette decide each match's rules.</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Oponente:</t>
+          <t>Selecciona hasta 4 reglas. Déjalo vacío para que la ruleta decida las reglas de cada partida.</t>
         </is>
       </c>
       <c r="F569" t="b">
@@ -17619,27 +17619,27 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>PreferencesThemes</t>
+          <t>HoneycombRules</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>save_new_theme_ellipsis_win</t>
+          <t>ban_removes_rule_hint</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Button, PreferencesView.axaml (Windows) — different wording from Mac's "Save as New Theme"</t>
+          <t>Helper text, HoneycombRulesView.axaml (Windows)</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Save New Theme…</t>
+          <t>Ban removes a rule from the roulette pool entirely.</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Guardar Nuevo Tema…</t>
+          <t>Vetar elimina una regla por completo del grupo de la ruleta.</t>
         </is>
       </c>
       <c r="F570" t="b">
@@ -17649,27 +17649,27 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HoneycombRules</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>first_move_player</t>
+          <t>opponent_label_colon</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Match-intro banner first line, HoneycombViewModel.swift/.cs</t>
+          <t>Label, HoneycombRulesView.axaml (Windows) — colon variant of opponentPickerLabel</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>First Move: Player!</t>
+          <t>Opponent:</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>¡Primer Movimiento: Jugador!</t>
+          <t>Oponente:</t>
         </is>
       </c>
       <c r="F571" t="b">
@@ -17679,27 +17679,27 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>PreferencesThemes</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>first_move_opponent_fmt</t>
+          <t>save_new_theme_ellipsis_win</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Match-intro banner first line, %@/{0} = opponent difficulty display name</t>
+          <t>Button, PreferencesView.axaml (Windows) — different wording from Mac's "Save as New Theme"</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>First Move: %@!</t>
+          <t>Save New Theme…</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>¡Primer Movimiento: %@!</t>
+          <t>Guardar Nuevo Tema…</t>
         </is>
       </c>
       <c r="F572" t="b">
@@ -17709,27 +17709,27 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>help_no_stress_mode_title</t>
+          <t>first_move_player</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>RuleSection title, shared across all 7 Help views</t>
+          <t>Match-intro banner first line, HoneycombViewModel.swift/.cs</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>🧘 No Stress Mode</t>
+          <t>First Move: Player!</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>🧘 Modo Sin Estrés</t>
+          <t>¡Primer Movimiento: Jugador!</t>
         </is>
       </c>
       <c r="F573" t="b">
@@ -17739,27 +17739,27 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>HelpGuideCommon</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>help_guide_contents_header</t>
+          <t>first_move_opponent_fmt</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Index header, HelpWindow.axaml (Windows)</t>
+          <t>Match-intro banner first line, %@/{0} = opponent difficulty display name</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>CONTENTS</t>
+          <t>First Move: %@!</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>CONTENIDO</t>
+          <t>¡Primer Movimiento: %@!</t>
         </is>
       </c>
       <c r="F574" t="b">
@@ -17774,22 +17774,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>help_guide_window_title</t>
+          <t>help_no_stress_mode_title</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Title bar text, HelpWindow.axaml (Windows) — distinct from per-game Help titles</t>
+          <t>RuleSection title, shared across all 7 Help views</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Help Guide</t>
+          <t>🧘 No Stress Mode</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Guía de Ayuda</t>
+          <t>🧘 Modo Sin Estrés</t>
         </is>
       </c>
       <c r="F575" t="b">
@@ -17804,22 +17804,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>help_themes_settings_index_label</t>
+          <t>help_guide_contents_header</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Index button label, HelpWindow.axaml (Windows) — shorter than helpThemesTitle</t>
+          <t>Index header, HelpWindow.axaml (Windows)</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Themes &amp; Settings</t>
+          <t>CONTENTS</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Temas y Configuración</t>
+          <t>CONTENIDO</t>
         </is>
       </c>
       <c r="F576" t="b">
@@ -17829,27 +17829,27 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>HelpGuideVideoPoker</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>help_shortcut_clear_all_holds</t>
+          <t>help_guide_window_title</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>ShortcutRow action, Video Poker (Windows uses this phrasing; Mac shortens to Clear/C-Q)</t>
+          <t>Title bar text, HelpWindow.axaml (Windows) — distinct from per-game Help titles</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Clear All Holds</t>
+          <t>Help Guide</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Soltar Todas las Cartas</t>
+          <t>Guía de Ayuda</t>
         </is>
       </c>
       <c r="F577" t="b">
@@ -17859,57 +17859,57 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>iOSVideoPoker</t>
+          <t>HelpGuideCommon</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>settings_header_videopoker</t>
+          <t>help_themes_settings_index_label</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Settings section header (uppercase), VideoPokerTouchView.swift</t>
+          <t>Index button label, HelpWindow.axaml (Windows) — shorter than helpThemesTitle</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>VIDEO POKER</t>
+          <t>Themes &amp; Settings</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>VIDEO POKER</t>
+          <t>Temas y Configuración</t>
         </is>
       </c>
       <c r="F578" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>PokerHands</t>
+          <t>HelpGuideVideoPoker</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>hand_royal_flush</t>
+          <t>help_shortcut_clear_all_holds</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Pay table row / result banner, standard (non-Deuces-Wild) tables — VideoPokerViewModel.swift/.cs handName (display-only, stored value stays English)</t>
+          <t>ShortcutRow action, Video Poker (Windows uses this phrasing; Mac shortens to Clear/C-Q)</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Royal Flush</t>
+          <t>Clear All Holds</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Escalera Real</t>
+          <t>Soltar Todas las Cartas</t>
         </is>
       </c>
       <c r="F579" t="b">
@@ -17919,57 +17919,57 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Honeycomb Swarm</t>
+          <t>iOSVideoPoker</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_hive_swarm</t>
+          <t>settings_header_videopoker</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Random banner phrase when the player triggers a Hive Swarm reveal</t>
+          <t>Settings section header (uppercase), VideoPokerTouchView.swift</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Your Hive Swarm</t>
+          <t>VIDEO POKER</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Tu Enjambre de Colmena</t>
+          <t>VIDEO POKER</t>
         </is>
       </c>
       <c r="F580" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Honeycomb Swarm</t>
+          <t>PokerHands</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_unleashed</t>
+          <t>hand_royal_flush</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Random banner phrase when the player triggers a Hive Swarm reveal</t>
+          <t>Pay table row / result banner, standard (non-Deuces-Wild) tables — VideoPokerViewModel.swift/.cs handName (display-only, stored value stays English)</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Your Swarm is Unleashed!</t>
+          <t>Royal Flush</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>¡Tu Enjambre se Desata!</t>
+          <t>Escalera Real</t>
         </is>
       </c>
       <c r="F581" t="b">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_awakens</t>
+          <t>swarm_reveal_player_hive_swarm</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -17994,12 +17994,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Your Swarm Awakens!</t>
+          <t>Your Hive Swarm</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>¡Tu Enjambre Despierta!</t>
+          <t>Tu Enjambre de Colmena</t>
         </is>
       </c>
       <c r="F582" t="b">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_buzzing</t>
+          <t>swarm_reveal_player_unleashed</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Your Hive is Buzzing into Action!</t>
+          <t>Your Swarm is Unleashed!</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>¡Tu Colmena Zumba en Acción!</t>
+          <t>¡Tu Enjambre se Desata!</t>
         </is>
       </c>
       <c r="F583" t="b">
@@ -18044,22 +18044,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_hive_swarm_fmt</t>
+          <t>swarm_reveal_player_awakens</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Random banner phrase when the opponent triggers a Hive Swarm reveal; %@ is the opponent/difficulty name</t>
+          <t>Random banner phrase when the player triggers a Hive Swarm reveal</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>%@'s Hive Swarm</t>
+          <t>Your Swarm Awakens!</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Enjambre de Colmena de %@</t>
+          <t>¡Tu Enjambre Despierta!</t>
         </is>
       </c>
       <c r="F584" t="b">
@@ -18074,22 +18074,22 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_unleashed_fmt</t>
+          <t>swarm_reveal_player_buzzing</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Random banner phrase when the opponent triggers a Hive Swarm reveal; %@ is the opponent/difficulty name</t>
+          <t>Random banner phrase when the player triggers a Hive Swarm reveal</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>%@'s Swarm is Unleashed!</t>
+          <t>Your Hive is Buzzing into Action!</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>¡El Enjambre de %@ se Desata!</t>
+          <t>¡Tu Colmena Zumba en Acción!</t>
         </is>
       </c>
       <c r="F585" t="b">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_awakens_fmt</t>
+          <t>swarm_reveal_opponent_hive_swarm_fmt</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -18114,12 +18114,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>%@'s Swarm Awakens!</t>
+          <t>%@'s Hive Swarm</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>¡El Enjambre de %@ Despierta!</t>
+          <t>Enjambre de Colmena de %@</t>
         </is>
       </c>
       <c r="F586" t="b">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_buzzing_fmt</t>
+          <t>swarm_reveal_opponent_unleashed_fmt</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -18144,12 +18144,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>%@'s Hive is Buzzing into Action!</t>
+          <t>%@'s Swarm is Unleashed!</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>¡La Colmena de %@ Zumba en Acción!</t>
+          <t>¡El Enjambre de %@ se Desata!</t>
         </is>
       </c>
       <c r="F587" t="b">
@@ -18164,22 +18164,22 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>banner_hive_mind_fmt</t>
+          <t>swarm_reveal_opponent_awakens_fmt</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Chain-reaction capture combo banner; %d is the flip count (2+)</t>
+          <t>Random banner phrase when the opponent triggers a Hive Swarm reveal; %@ is the opponent/difficulty name</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>HIVE MIND x%d!</t>
+          <t>%@'s Swarm Awakens!</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>¡MENTE COLMENA x%d!</t>
+          <t>¡El Enjambre de %@ Despierta!</t>
         </is>
       </c>
       <c r="F588" t="b">
@@ -18189,27 +18189,27 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>PreferencesWin</t>
+          <t>Honeycomb Swarm</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>game_mode_section_header</t>
+          <t>swarm_reveal_opponent_buzzing_fmt</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Windows Options page: Game Mode section header above the draw-mode/suit-count/deck-count picker</t>
+          <t>Random banner phrase when the opponent triggers a Hive Swarm reveal; %@ is the opponent/difficulty name</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Game Mode</t>
+          <t>%@'s Hive is Buzzing into Action!</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Modo de Juego</t>
+          <t>¡La Colmena de %@ Zumba en Acción!</t>
         </is>
       </c>
       <c r="F589" t="b">
@@ -18219,27 +18219,27 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>PreferencesWin</t>
+          <t>Honeycomb Swarm</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>saved_themes_header</t>
+          <t>banner_hive_mind_fmt</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Windows Options page: Themes sub-panel sidebar header</t>
+          <t>Chain-reaction capture combo banner; %d is the flip count (2+)</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Saved Themes</t>
+          <t>HIVE MIND x%d!</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Temas Guardados</t>
+          <t>¡MENTE COLMENA x%d!</t>
         </is>
       </c>
       <c r="F590" t="b">
@@ -18254,22 +18254,22 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>double_click_card_or_background_tooltip</t>
+          <t>game_mode_section_header</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Windows Options page: hero preview tooltip (combined card+background, unlike Mac which has separate tooltips)</t>
+          <t>Windows Options page: Game Mode section header above the draw-mode/suit-count/deck-count picker</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Double-click the card or the background to adjust it</t>
+          <t>Game Mode</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Haz doble clic en la carta o el fondo para ajustarlo</t>
+          <t>Modo de Juego</t>
         </is>
       </c>
       <c r="F591" t="b">
@@ -18284,22 +18284,22 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>delete_background_confirm_body</t>
+          <t>saved_themes_header</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Windows Options page: Delete Background confirmation dialog body</t>
+          <t>Windows Options page: Themes sub-panel sidebar header</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Are you sure you want to delete this custom background? This cannot be undone.</t>
+          <t>Saved Themes</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>¿Seguro que quieres eliminar este fondo personalizado? Esto no se puede deshacer.</t>
+          <t>Temas Guardados</t>
         </is>
       </c>
       <c r="F592" t="b">
@@ -18314,22 +18314,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>save_new_theme_title</t>
+          <t>double_click_card_or_background_tooltip</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Windows Options page: Save New Theme dialog title (distinct from the button which has an ellipsis)</t>
+          <t>Windows Options page: hero preview tooltip (combined card+background, unlike Mac which has separate tooltips)</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Save New Theme</t>
+          <t>Double-click the card or the background to adjust it</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Guardar Nuevo Tema</t>
+          <t>Haz doble clic en la carta o el fondo para ajustarlo</t>
         </is>
       </c>
       <c r="F593" t="b">
@@ -18344,22 +18344,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>enter_theme_name_prompt</t>
+          <t>delete_background_confirm_body</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Windows Options page: Save New Theme dialog prompt text</t>
+          <t>Windows Options page: Delete Background confirmation dialog body</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Enter a name for this theme:</t>
+          <t>Are you sure you want to delete this custom background? This cannot be undone.</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Introduce un nombre para este tema:</t>
+          <t>¿Seguro que quieres eliminar este fondo personalizado? Esto no se puede deshacer.</t>
         </is>
       </c>
       <c r="F594" t="b">
@@ -18374,22 +18374,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>tap_tile_upload_art_hint</t>
+          <t>save_new_theme_title</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Windows Options page: Face Cards sub-panel instructional hint</t>
+          <t>Windows Options page: Save New Theme dialog title (distinct from the button which has an ellipsis)</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Tap a tile to upload art. Tap again to adjust.</t>
+          <t>Save New Theme</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Toca un mosaico para subir arte. Toca de nuevo para ajustar.</t>
+          <t>Guardar Nuevo Tema</t>
         </is>
       </c>
       <c r="F595" t="b">
@@ -18399,27 +18399,27 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>PreferencesWin</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>suit_name_spades_plain</t>
+          <t>enter_theme_name_prompt</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list, e.g. "Ascension: Spades, Hearts"</t>
+          <t>Windows Options page: Save New Theme dialog prompt text</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Spades</t>
+          <t>Enter a name for this theme:</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Picas</t>
+          <t>Introduce un nombre para este tema:</t>
         </is>
       </c>
       <c r="F596" t="b">
@@ -18429,27 +18429,27 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>PreferencesWin</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>suit_name_hearts_plain</t>
+          <t>tap_tile_upload_art_hint</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
+          <t>Windows Options page: Face Cards sub-panel instructional hint</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Tap a tile to upload art. Tap again to adjust.</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Corazones</t>
+          <t>Toca un mosaico para subir arte. Toca de nuevo para ajustar.</t>
         </is>
       </c>
       <c r="F597" t="b">
@@ -18464,22 +18464,22 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>suit_name_diamonds_plain</t>
+          <t>suit_name_spades_plain</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list, e.g. "Ascension: Spades, Hearts"</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Diamonds</t>
+          <t>Spades</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Diamantes</t>
+          <t>Picas</t>
         </is>
       </c>
       <c r="F598" t="b">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>suit_name_clubs_plain</t>
+          <t>suit_name_hearts_plain</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -18504,12 +18504,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Clubs</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Tréboles</t>
+          <t>Corazones</t>
         </is>
       </c>
       <c r="F599" t="b">
@@ -18519,27 +18519,27 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>AboutWin</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>about_downloading_update</t>
+          <t>suit_name_diamonds_plain</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Windows About window: update download in progress</t>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Downloading update…</t>
+          <t>Diamonds</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Descargando actualización…</t>
+          <t>Diamantes</t>
         </is>
       </c>
       <c r="F600" t="b">
@@ -18549,27 +18549,27 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>AboutWin</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>about_downloading_update_pct_fmt</t>
+          <t>suit_name_clubs_plain</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Windows About window: update download progress with percentage</t>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Downloading update… %d%%</t>
+          <t>Clubs</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Descargando actualización… %d%%</t>
+          <t>Tréboles</t>
         </is>
       </c>
       <c r="F601" t="b">
@@ -18584,22 +18584,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>about_update_download_failed</t>
+          <t>about_downloading_update</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Windows About window: update download failure message</t>
+          <t>Windows About window: update download in progress</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Failed to download the update.</t>
+          <t>Downloading update…</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>No se pudo descargar la actualización.</t>
+          <t>Descargando actualización…</t>
         </is>
       </c>
       <c r="F602" t="b">
@@ -18614,22 +18614,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>install_and_restart</t>
+          <t>about_downloading_update_pct_fmt</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Windows About window: button to install a downloaded update and restart</t>
+          <t>Windows About window: update download progress with percentage</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Install &amp; Restart</t>
+          <t>Downloading update… %d%%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Instalar y Reiniciar</t>
+          <t>Descargando actualización… %d%%</t>
         </is>
       </c>
       <c r="F603" t="b">
@@ -18639,27 +18639,27 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>BackgroundEditorWin</t>
+          <t>AboutWin</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>add_background_title</t>
+          <t>about_update_download_failed</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Windows Background editor window title when adding a new background</t>
+          <t>Windows About window: update download failure message</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Add Background</t>
+          <t>Failed to download the update.</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Añadir Fondo</t>
+          <t>No se pudo descargar la actualización.</t>
         </is>
       </c>
       <c r="F604" t="b">
@@ -18669,27 +18669,27 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>BackgroundEditorWin</t>
+          <t>AboutWin</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>edit_background_title</t>
+          <t>install_and_restart</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Windows Background editor window title when editing an existing background</t>
+          <t>Windows About window: button to install a downloaded update and restart</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Edit Background</t>
+          <t>Install &amp; Restart</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Editar Fondo</t>
+          <t>Instalar y Reiniciar</t>
         </is>
       </c>
       <c r="F605" t="b">
@@ -18699,91 +18699,91 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
+          <t>BackgroundEditorWin</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>add_background_title</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Windows Background editor window title when adding a new background</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Add Background</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Añadir Fondo</t>
+        </is>
+      </c>
+      <c r="F606" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>BackgroundEditorWin</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>edit_background_title</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Windows Background editor window title when editing an existing background</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Edit Background</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Editar Fondo</t>
+        </is>
+      </c>
+      <c r="F607" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
           <t>CardBackEditorWin</t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>card_back_fill_note</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>Windows Card Back editor: note shown instead of position sliders for fill-type card backs</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr">
+      <c r="D608" t="inlineStr">
         <is>
           <t>This card back fills the card automatically
 and doesn't use position adjustments.</t>
         </is>
       </c>
-      <c r="E606" t="inlineStr">
+      <c r="E608" t="inlineStr">
         <is>
           <t>Este reverso de carta llena la carta automáticamente
 y no usa ajustes de posición.</t>
         </is>
       </c>
-      <c r="F606" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>VideoPokerWin</t>
-        </is>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>btn_deal_d_hotkey</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>Windows Video Poker Deal/Draw toggle button, Deal state (D hotkey)</t>
-        </is>
-      </c>
-      <c r="D607" t="inlineStr">
-        <is>
-          <t>Deal  [D]</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr">
-        <is>
-          <t>Repartir  [D]</t>
-        </is>
-      </c>
-      <c r="F607" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>VideoPokerWin</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>btn_draw_d_hotkey</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>Windows Video Poker Deal/Draw toggle button, Draw state (D hotkey)</t>
-        </is>
-      </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>Draw  [D]</t>
-        </is>
-      </c>
-      <c r="E608" t="inlineStr">
-        <is>
-          <t>Robar  [D]</t>
-        </is>
-      </c>
       <c r="F608" t="b">
         <v>1</v>
       </c>
@@ -18791,27 +18791,27 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>DeckBuilderWin</t>
+          <t>VideoPokerWin</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>remove_from_deck_context_menu</t>
+          <t>btn_deal_d_hotkey</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Windows Deck Builder: right-click context menu item on a deck card</t>
+          <t>Windows Video Poker Deal/Draw toggle button, Deal state (D hotkey)</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Remove from deck?</t>
+          <t>Deal  [D]</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>¿Quitar del mazo?</t>
+          <t>Repartir  [D]</t>
         </is>
       </c>
       <c r="F609" t="b">
@@ -18821,27 +18821,27 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>ManageDecksWin</t>
+          <t>VideoPokerWin</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>star_count_filter_fmt</t>
+          <t>btn_draw_d_hotkey</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: star-count filter dropdown item, e.g. "1 Star"/"3 Stars"</t>
+          <t>Windows Video Poker Deal/Draw toggle button, Draw state (D hotkey)</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>%d Star%@</t>
+          <t>Draw  [D]</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>%d Estrella%@</t>
+          <t>Robar  [D]</t>
         </is>
       </c>
       <c r="F610" t="b">
@@ -18851,27 +18851,27 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>ManageDecksWin</t>
+          <t>DeckBuilderWin</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>no_cards_match_filter</t>
+          <t>remove_from_deck_context_menu</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: empty state when the current filter selection matches no cards</t>
+          <t>Windows Deck Builder: right-click context menu item on a deck card</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>No cards match this filter.</t>
+          <t>Remove from deck?</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Ninguna carta coincide con este filtro.</t>
+          <t>¿Quitar del mazo?</t>
         </is>
       </c>
       <c r="F611" t="b">
@@ -18881,27 +18881,27 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>ManageDecksWin</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>you_lose</t>
+          <t>star_count_filter_fmt</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Match-result overlay title on a loss (Honeycomb)</t>
+          <t>Windows Manage Decks: star-count filter dropdown item, e.g. "1 Star"/"3 Stars"</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>You Lose</t>
+          <t>%d Star%@</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Perdiste</t>
+          <t>%d Estrella%@</t>
         </is>
       </c>
       <c r="F612" t="b">
@@ -18911,27 +18911,27 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>ManageDecksWin</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>draw_sudden_death_fmt</t>
+          <t>no_cards_match_filter</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Match-result overlay title when a tied match enters Sudden Death; %@ is the localized Sudden Death rule name</t>
+          <t>Windows Manage Decks: empty state when the current filter selection matches no cards</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Draw - %@!</t>
+          <t>No cards match this filter.</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>¡Empate - %@!</t>
+          <t>Ninguna carta coincide con este filtro.</t>
         </is>
       </c>
       <c r="F613" t="b">
@@ -18941,27 +18941,27 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>result_dealer_wins</t>
+          <t>you_lose</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Result summary label, single-hand loss (iOS visible text)</t>
+          <t>Match-result overlay title on a loss (Honeycomb)</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Dealer Wins</t>
+          <t>You Lose</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Gana el Repartidor</t>
+          <t>Perdiste</t>
         </is>
       </c>
       <c r="F614" t="b">
@@ -18971,27 +18971,27 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>result_hand_win_fmt</t>
+          <t>draw_sudden_death_fmt</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) win — %d is the hand number</t>
+          <t>Match-result overlay title when a tied match enters Sudden Death; %@ is the localized Sudden Death rule name</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Hand %d: Win</t>
+          <t>Draw - %@!</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Mano %d: Gana</t>
+          <t>¡Empate - %@!</t>
         </is>
       </c>
       <c r="F615" t="b">
@@ -19006,22 +19006,22 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>result_hand_loss_fmt</t>
+          <t>result_dealer_wins</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) loss — %d is the hand number</t>
+          <t>Result summary label, single-hand loss (iOS visible text)</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Hand %d: Loss</t>
+          <t>Dealer Wins</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Mano %d: Pierde</t>
+          <t>Gana el Repartidor</t>
         </is>
       </c>
       <c r="F616" t="b">
@@ -19036,22 +19036,22 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>result_hand_push_fmt</t>
+          <t>result_hand_win_fmt</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) push — %d is the hand number</t>
+          <t>Result summary label, multi-hand (split) win — %d is the hand number</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Hand %d: Push</t>
+          <t>Hand %d: Win</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Mano %d: Empate</t>
+          <t>Mano %d: Gana</t>
         </is>
       </c>
       <c r="F617" t="b">
@@ -19066,22 +19066,22 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>result_hand_bust_fmt</t>
+          <t>result_hand_loss_fmt</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) bust — %d is the hand number</t>
+          <t>Result summary label, multi-hand (split) loss — %d is the hand number</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Hand %d: Bust</t>
+          <t>Hand %d: Loss</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Mano %d: Se pasó</t>
+          <t>Mano %d: Pierde</t>
         </is>
       </c>
       <c r="F618" t="b">
@@ -19091,27 +19091,27 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>new_match_confirm_title</t>
+          <t>result_hand_push_fmt</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Confirmation dialog when starting a new match mid-match</t>
+          <t>Result summary label, multi-hand (split) push — %d is the hand number</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Start a new match? Your current match will end.</t>
+          <t>Hand %d: Push</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>¿Empezar un nuevo partido? Tu partido actual terminará.</t>
+          <t>Mano %d: Empate</t>
         </is>
       </c>
       <c r="F619" t="b">
@@ -19121,27 +19121,27 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>rematch_confirm_title</t>
+          <t>result_hand_bust_fmt</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Confirmation dialog when requesting a rematch mid-match</t>
+          <t>Result summary label, multi-hand (split) bust — %d is the hand number</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Rematch? Your current match will end.</t>
+          <t>Hand %d: Bust</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>¿Revancha? Tu partido actual terminará.</t>
+          <t>Mano %d: Se pasó</t>
         </is>
       </c>
       <c r="F620" t="b">
@@ -19151,27 +19151,27 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>SlideDownMenuIOS</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>menu_tab_game_selection</t>
+          <t>new_match_confirm_title</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>iOS slide-down menu segmented tab</t>
+          <t>Confirmation dialog when starting a new match mid-match</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Game Selection</t>
+          <t>Start a new match? Your current match will end.</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>Selección de Juego</t>
+          <t>¿Empezar un nuevo partido? Tu partido actual terminará.</t>
         </is>
       </c>
       <c r="F621" t="b">
@@ -19181,27 +19181,27 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>SlideDownMenuIOS</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>menu_header_title</t>
+          <t>rematch_confirm_title</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>iOS slide-down menu header title</t>
+          <t>Confirmation dialog when requesting a rematch mid-match</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Menu</t>
+          <t>Rematch? Your current match will end.</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Menú</t>
+          <t>¿Revancha? Tu partido actual terminará.</t>
         </is>
       </c>
       <c r="F622" t="b">
@@ -19216,22 +19216,22 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>close_menu_a11y</t>
+          <t>menu_tab_game_selection</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>iOS slide-down menu close-button accessibility label</t>
+          <t>iOS slide-down menu segmented tab</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Close menu</t>
+          <t>Game Selection</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Cerrar menú</t>
+          <t>Selección de Juego</t>
         </is>
       </c>
       <c r="F623" t="b">
@@ -19246,22 +19246,22 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>menu_section_game</t>
+          <t>menu_header_title</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Game Selection tab section header</t>
+          <t>iOS slide-down menu header title</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Juego</t>
+          <t>Menú</t>
         </is>
       </c>
       <c r="F624" t="b">
@@ -19276,22 +19276,22 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>menu_section_theme</t>
+          <t>close_menu_a11y</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab felt-color section header</t>
+          <t>iOS slide-down menu close-button accessibility label</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Close menu</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Tema</t>
+          <t>Cerrar menú</t>
         </is>
       </c>
       <c r="F625" t="b">
@@ -19306,22 +19306,22 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>menu_section_card_back</t>
+          <t>menu_section_game</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab card-back section header</t>
+          <t>iOS slide-down menu Game Selection tab section header</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Card Back</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Reverso de Carta</t>
+          <t>Juego</t>
         </is>
       </c>
       <c r="F626" t="b">
@@ -19336,22 +19336,22 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>menu_section_background</t>
+          <t>menu_section_theme</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab background section header</t>
+          <t>iOS slide-down menu Themes tab felt-color section header</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Fondo</t>
+          <t>Tema</t>
         </is>
       </c>
       <c r="F627" t="b">
@@ -19366,22 +19366,22 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>background_none_option</t>
+          <t>menu_section_card_back</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: clears the custom background back to felt color</t>
+          <t>iOS slide-down menu Themes tab card-back section header</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Card Back</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Reverso de Carta</t>
         </is>
       </c>
       <c r="F628" t="b">
@@ -19396,22 +19396,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>remove_card_back_alert_title</t>
+          <t>menu_section_background</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom card back</t>
+          <t>iOS slide-down menu Themes tab background section header</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Remove Card Back?</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>¿Quitar Reverso de Carta?</t>
+          <t>Fondo</t>
         </is>
       </c>
       <c r="F629" t="b">
@@ -19426,22 +19426,22 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>remove_background_alert_title</t>
+          <t>background_none_option</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom background</t>
+          <t>iOS slide-down menu: clears the custom background back to felt color</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Remove Background?</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>¿Quitar Fondo?</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="F630" t="b">
@@ -19456,22 +19456,22 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>remove_imported_image_body</t>
+          <t>remove_card_back_alert_title</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
+          <t>iOS slide-down menu: confirm removing a custom card back</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>This removes the imported image. It can't be undone.</t>
+          <t>Remove Card Back?</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
+          <t>¿Quitar Reverso de Carta?</t>
         </is>
       </c>
       <c r="F631" t="b">
@@ -19486,22 +19486,22 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>statistics_nav_row</t>
+          <t>remove_background_alert_title</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Statistics destination row</t>
+          <t>iOS slide-down menu: confirm removing a custom background</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Remove Background?</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Estadísticas</t>
+          <t>¿Quitar Fondo?</t>
         </is>
       </c>
       <c r="F632" t="b">
@@ -19516,22 +19516,22 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>how_to_play_nav_row</t>
+          <t>remove_imported_image_body</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Help destination row</t>
+          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>How to Play</t>
+          <t>This removes the imported image. It can't be undone.</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Cómo Jugar</t>
+          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
         </is>
       </c>
       <c r="F633" t="b">
@@ -19546,22 +19546,22 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>face_card_art_nav_row</t>
+          <t>statistics_nav_row</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Face Card Art destination row</t>
+          <t>iOS slide-down menu: Statistics destination row</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Face Card Art</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Arte de Carta</t>
+          <t>Estadísticas</t>
         </is>
       </c>
       <c r="F634" t="b">
@@ -19571,27 +19571,27 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>SlideDownMenuIOS</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>touch_new_deal_label</t>
+          <t>how_to_play_nav_row</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS slide-down menu: Help destination row</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>How to Play</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Cómo Jugar</t>
         </is>
       </c>
       <c r="F635" t="b">
@@ -19601,27 +19601,27 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>SlideDownMenuIOS</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>touch_undo_last_move_label</t>
+          <t>face_card_art_nav_row</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS slide-down menu: Face Card Art destination row</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Undo Last Move</t>
+          <t>Face Card Art</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Deshacer Última Jugada</t>
+          <t>Arte de Carta</t>
         </is>
       </c>
       <c r="F636" t="b">
@@ -19636,22 +19636,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>touch_deal_a11y</t>
+          <t>touch_new_deal_label</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: stock pile accessibility label</t>
+          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Deal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Repartir</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F637" t="b">
@@ -19666,22 +19666,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>touch_completed_runs_a11y</t>
+          <t>touch_undo_last_move_label</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
+          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Completed runs</t>
+          <t>Undo Last Move</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Series completadas</t>
+          <t>Deshacer Última Jugada</t>
         </is>
       </c>
       <c r="F638" t="b">
@@ -19696,22 +19696,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>touch_decks_picker_label</t>
+          <t>touch_deal_a11y</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker label</t>
+          <t>iOS Spider touch view: stock pile accessibility label</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Decks</t>
+          <t>Deal</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Mazos</t>
+          <t>Repartir</t>
         </is>
       </c>
       <c r="F639" t="b">
@@ -19726,22 +19726,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>touch_single_deck_option</t>
+          <t>touch_completed_runs_a11y</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker option</t>
+          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Single Deck</t>
+          <t>Completed runs</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Mazo Sencillo</t>
+          <t>Series completadas</t>
         </is>
       </c>
       <c r="F640" t="b">
@@ -19756,22 +19756,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>touch_double_deck_option</t>
+          <t>touch_decks_picker_label</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker option</t>
+          <t>iOS Beecell touch view: deck-count Picker label</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Double Deck</t>
+          <t>Decks</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Doble Mazo</t>
+          <t>Mazos</t>
         </is>
       </c>
       <c r="F641" t="b">
@@ -19786,22 +19786,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>touch_suits_picker_label</t>
+          <t>touch_single_deck_option</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
+          <t>iOS Beecell touch view: deck-count Picker option</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Suits</t>
+          <t>Single Deck</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Palos</t>
+          <t>Mazo Sencillo</t>
         </is>
       </c>
       <c r="F642" t="b">
@@ -19816,22 +19816,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>touch_bet_max_button</t>
+          <t>touch_double_deck_option</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: Max bet button</t>
+          <t>iOS Beecell touch view: deck-count Picker option</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Double Deck</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Máx</t>
+          <t>Doble Mazo</t>
         </is>
       </c>
       <c r="F643" t="b">
@@ -19846,22 +19846,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_between_hands</t>
+          <t>touch_suits_picker_label</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
+          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Settings unlock between hands.</t>
+          <t>Suits</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea entre manos.</t>
+          <t>Palos</t>
         </is>
       </c>
       <c r="F644" t="b">
@@ -19876,22 +19876,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_hand_ends</t>
+          <t>touch_bet_max_button</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
+          <t>iOS Video Poker touch view: Max bet button</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Settings unlock when the hand ends.</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea cuando termina la mano.</t>
+          <t>Máx</t>
         </is>
       </c>
       <c r="F645" t="b">
@@ -19906,22 +19906,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>touch_hands_dealt_stat</t>
+          <t>touch_settings_unlock_between_hands</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
+          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Hands Dealt</t>
+          <t>Settings unlock between hands.</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Manos Repartidas</t>
+          <t>La configuración se desbloquea entre manos.</t>
         </is>
       </c>
       <c r="F646" t="b">
@@ -19936,22 +19936,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>touch_session_credits_stat</t>
+          <t>touch_settings_unlock_hand_ends</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
+          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Session Credits</t>
+          <t>Settings unlock when the hand ends.</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Créditos de Sesión</t>
+          <t>La configuración se desbloquea cuando termina la mano.</t>
         </is>
       </c>
       <c r="F647" t="b">
@@ -19966,22 +19966,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>touch_hand_label_fmt</t>
+          <t>touch_hands_dealt_stat</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
+          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>HAND %d</t>
+          <t>Hands Dealt</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>MANO %d</t>
+          <t>Manos Repartidas</t>
         </is>
       </c>
       <c r="F648" t="b">
@@ -19996,22 +19996,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>touch_you_label</t>
+          <t>touch_session_credits_stat</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
+          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>YOU</t>
+          <t>Session Credits</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>TÚ</t>
+          <t>Créditos de Sesión</t>
         </is>
       </c>
       <c r="F649" t="b">
@@ -20026,22 +20026,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>touch_bust_suffix</t>
+          <t>touch_hand_label_fmt</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
+          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BUST</t>
+          <t>HAND %d</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SE PASÓ</t>
+          <t>MANO %d</t>
         </is>
       </c>
       <c r="F650" t="b">
@@ -20056,22 +20056,22 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>touch_result_win</t>
+          <t>touch_you_label</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand result badge</t>
+          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>YOU</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>GANA</t>
+          <t>TÚ</t>
         </is>
       </c>
       <c r="F651" t="b">
@@ -20086,22 +20086,22 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>touch_result_loss</t>
+          <t>touch_bust_suffix</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand result badge</t>
+          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t xml:space="preserve"> BUST</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>PIERDE</t>
+          <t xml:space="preserve"> SE PASÓ</t>
         </is>
       </c>
       <c r="F652" t="b">
@@ -20116,7 +20116,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>touch_result_push</t>
+          <t>touch_result_win</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -20126,12 +20126,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>PUSH</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>EMPATE</t>
+          <t>GANA</t>
         </is>
       </c>
       <c r="F653" t="b">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>touch_result_blackjack</t>
+          <t>touch_result_loss</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -20156,12 +20156,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>BLACKJACK!</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>¡BLACKJACK!</t>
+          <t>PIERDE</t>
         </is>
       </c>
       <c r="F654" t="b">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>touch_result_bust</t>
+          <t>touch_result_push</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -20186,12 +20186,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>BUST</t>
+          <t>PUSH</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>SE PASÓ</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="F655" t="b">
@@ -20206,22 +20206,22 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>touch_action_hit</t>
+          <t>touch_result_blackjack</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: action button</t>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>BLACKJACK!</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Pedir</t>
+          <t>¡BLACKJACK!</t>
         </is>
       </c>
       <c r="F656" t="b">
@@ -20236,22 +20236,22 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>touch_action_stand</t>
+          <t>touch_result_bust</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: action button</t>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>BUST</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Plantarse</t>
+          <t>SE PASÓ</t>
         </is>
       </c>
       <c r="F657" t="b">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>touch_action_double</t>
+          <t>touch_action_hit</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -20276,12 +20276,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Hit</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Doblar</t>
+          <t>Pedir</t>
         </is>
       </c>
       <c r="F658" t="b">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>touch_action_split</t>
+          <t>touch_action_stand</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -20306,12 +20306,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Dividir</t>
+          <t>Plantarse</t>
         </is>
       </c>
       <c r="F659" t="b">
@@ -20326,22 +20326,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>touch_reset_position_button</t>
+          <t>touch_action_double</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: Reset Position button</t>
+          <t>iOS Blackjack touch view: action button</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Reset Position</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Restablecer Posición</t>
+          <t>Doblar</t>
         </is>
       </c>
       <c r="F660" t="b">
@@ -20356,22 +20356,22 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>touch_add_card_back_title</t>
+          <t>touch_action_split</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>iOS custom card-back import sheet nav title</t>
+          <t>iOS Blackjack touch view: action button</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Add Card Back</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Añadir Reverso de Carta</t>
+          <t>Dividir</t>
         </is>
       </c>
       <c r="F661" t="b">
@@ -20381,32 +20381,92 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>touch_reset_position_button</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: Reset Position button</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Reset Position</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Restablecer Posición</t>
+        </is>
+      </c>
+      <c r="F662" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>touch_add_card_back_title</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>iOS custom card-back import sheet nav title</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Add Card Back</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Añadir Reverso de Carta</t>
+        </is>
+      </c>
+      <c r="F663" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
           <t>Honeycomb</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>steal_instruction_tap</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>Steal-mode instructional hint, iOS (touch wording — Mac/Windows use the click-based steal_instruction key)</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr">
+      <c r="D664" t="inlineStr">
         <is>
           <t>Double-tap a captured opponent's card
 on the board to steal it.</t>
         </is>
       </c>
-      <c r="E662" t="inlineStr">
+      <c r="E664" t="inlineStr">
         <is>
           <t>Toca dos veces la carta capturada de un oponente
 en el tablero para robarla.</t>
         </is>
       </c>
-      <c r="F662" t="b">
+      <c r="F664" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BannerFlavorText" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,11 +56,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20473,4 +20475,9234 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F288"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nectar Exchange swaps away the player's 5-star card.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{OpponentName} snatched your prize honey!</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>¡{OpponentName} robó tu mejor miel!</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nectar Exchange trades the player's worst card for the opponent's best.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>You’ve traded up!</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>¡Has hecho un buen cambio!</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Roulette rolls zero extra rules.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A classic match — just bees and honey, no gimmicks.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Una partida clásica — solo abejas y miel, sin trucos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Game loads on May 20th (World Bee Day).</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Happy World Bee Day! The comb is buzzing with excitement.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>¡Feliz Día Mundial de las Abejas! La colmena zumba de emoción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Game loads on New Year's Day (Jan 1).</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Blessed bee your new year!</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Game loads on Halloween (Oct 31).</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A spooky swarm gathers!</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>¡Un enjambre espeluznante se reúne!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Every heart in the hive beats for you.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cada corazón en la colmena late por ti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>First launch after playing for one year.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>One year in the hive. Thank you for playing!</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Un año en la colmena. ¡Gracias por jugar!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The bees are feeling mischievous today.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Las abejas se sienten traviesas hoy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>The midnight shift in the hive.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>El turno de medianoche en la colmena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The early bee catches the nectar.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>One more match before the hive turns in...</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Una partida más antes de que la colmena se vaya a dormir...</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Match starts within a minute of local noon.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>It’s Hive Noon!</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Burning the midnight beeswax.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Who needs sleep when there's honey on the line?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>¿Quién necesita dormir cuando hay miel en juego?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>The hive is quiet, but the night shift keeps buzzing.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>La colmena está en silencio, pero el turno de noche sigue zumbando.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Only the most dedicated bees are awake at this hour.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Solo las abejas más dedicadas están despiertas a esta hora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Up with the sun! The morning dew is fresh on the comb.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>¡Arriba con el sol! El rocío matutino está fresco en el panal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>First flight of the day.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Primer vuelo del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Coffee and cards — a bee's favorite morning routine.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Café y cartas — la rutina matutina favorita de una abeja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rise and buzz! Time for morning cards.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>¡Arriba y a zumbar! Hora de las cartas matutinas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Night falls over the hive.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Cae la noche sobre la colmena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>The comb quietens as the stars come out.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>El panal se silencia a medida que salen las estrellas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Just one more game... famous last words in the hive.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Solo una partida más... las famosas últimas palabras en la colmena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Morning in the comb — the day's first harvest begins!</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mañana en el panal — ¡comienza la primera cosecha del día!</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Peak pollen-gathering hours!</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>¡Horas pico de recolección de polen!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The hive is buzzing with morning energy.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>La colmena zumba con energía matutina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>High noon in the hive — time for a honey break!</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mediodía en la colmena — ¡hora de un descanso para tomar miel!</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>The sun is high, and the nectar is sweet.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>El sol está alto, y el néctar es dulce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Midday match! A quick break between flights.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>¡Partida de mediodía! Un rápido descanso entre vuelos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Golden afternoon light fills the comb.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>La luz dorada de la tarde llena el panal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>The afternoon warmth has the bees buzzing lively.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>El calor de la tarde tiene a las abejas zumbando animadamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Basking in the warm afternoon sun.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Disfrutando del cálido sol de la tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>The sun sets over the hive — time for evening games.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>El sol se pone sobre la colmena — hora de las partidas nocturnas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Workers return home after a full day's buzz.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Las obreras regresan a casa después de un largo día de zumbidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Golden hour in the honeycomb.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Hora dorada en el panal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Warming up flights muscles…</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Calentando los músculos de vuelo…</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pollinating the processors…</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Polinizando los procesadores…</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Untangling waggle-dance choreography…</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Desemredando la coreografía del baile de meneo…</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Generating royal jelly…</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Generando jalea real…</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sealing the honeycomb…</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sellando el panal…</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Consulting the Queen Bee…</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Consultando a la Abeja Reina…</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Calibrating stingers…</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Calibrando aguijones…</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Deploying scout bees…</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Desplegando abejas exploradoras…</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Counting the worker bees…</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Contando a las abejas obreras…</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Preparing a sticky situation…</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Preparando una situación pegajosa…</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>The swarm is gathering…</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>El enjambre se está reuniendo…</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sweeping the hive…</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Limpiando la colmena…</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Gathering nectar from local memory…</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Recolectando néctar de la memoria local…</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Guarding the entrance from wasps…</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vigilando la entrada de las avispas…</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Feeding the larvae bits and bytes…</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Alimentando a las larvas con bits y bytes…</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Orienting new forager bees…</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Orientando a las nuevas abejas recolectoras…</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cross-referencing pollen routes…</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Comprobando las rutas del polen…</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Recruiting nurse bees…</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Reclutando abejas nodrizas…</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Loading nectar reserves…</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Cargando reservas de néctar…</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Synchronizing with the hive mind…</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sincronizando con la mente colmena…</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tuning antennae for reception…</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Afinando antenas para recepción…</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Propolis-sealing the cracks…</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sellando grietas con propóleo…</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Rousing drones from their nap…</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Despertando a los zánganos de su siesta…</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>The hive hums quietly, waiting for your next move.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>La colmena zumba en silencio, esperando tu siguiente movimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A stray bee drifts across the board...</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Una abeja perdida se desplaza por el tablero...</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>It’s when you can’t hear the bees, that’s when the bees are coming.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Es cuando no puedes escuchar a las abejas, ahí es cuando vienen las abejas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Somewhere, honey is dripping.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>En algún lugar, está goteando miel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>The comb creaks softly under the weight of gathered honey.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>El panal cruje suavemente bajo el peso de la miel recolectada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A distant hum grows louder... or is that just the board?</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Un zumbido distante se hace más fuerte... ¿o es solo el tablero?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Pollen settles on the board like fine snow.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>El polen se asienta sobre el tablero como nieve fina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Somewhere, a queen bee hums a low, satisfied note.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>En algún lugar, una abeja reina tararea una nota baja y satisfecha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>The board glows faintly gold in the afternoon light.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>El tablero brilla tenuemente en oro bajo la luz de la tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A single petal drifts down onto the comb.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Un solo pétalo cae sobre el panal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>The hive never truly sleeps.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>La colmena nunca duerme realmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>The swarm is silently judging your strategy.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>El enjambre está juzgando silenciosamente tu estrategia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A worker bee pauses mid-flight, unsure why.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Una abeja obrera se detiene en pleno vuelo, sin saber por qué.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Somewhere, a bee is telling the others where you’ve been.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>En algún lugar, una abeja le dice a las demás dónde has estado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>The hive remembers every card you’ve touched.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>La colmena recuerda cada carta que has tocado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Nothing moves. Everything hums.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Nada se mueve. Todo zumba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>The edges of the cards are getting a little sticky.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Los bordes de las cartas se están poniendo un poco pegajosos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>The bees are keeping score. They always do.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Las abejas llevan la cuenta. Siempre lo hacen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A bee lands, looks around, and leaves again.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Una abeja aterriza, mira alrededor, y se va de nuevo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>The hum has changed pitch. Did you notice?</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>El zumbido ha cambiado de tono. ¿Lo notaste?</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Time moves differently inside the comb.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>El tiempo pasa de manera diferente dentro del panal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Somewhere, wax is being warmed by tiny bodies.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>En algún lugar, cuerpos diminutos están calentando cera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Even idle hands make honey eventually.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Incluso las manos ociosas hacen miel eventualmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>The bees are patient. Are you?</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Las abejas son pacientes. ¿Lo eres tú?</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>The hive keeps its own time.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>La colmena marca su propio tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Need a little help? The scout bees are buzzing suggestions.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>¿Necesitas un poco de ayuda? Las abejas exploradoras zumban sugerencias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Waggle dance activated!</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>¡Baile de meneo activado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>The bees checked every flower!</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>¡Las abejas revisaron cada flor!</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>The hive mind is thinking...</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>La mente colmena está pensando...</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The hive has reached a consensus.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>La colmena ha llegado a un consenso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Even the busiest bees ask the Queen for directions sometimes.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Incluso las abejas más ocupadas piden direcciones a la Reina a veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>A drop of honey marks a sweet path forward.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Una gota de miel marca un dulce camino a seguir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Nectar trail spotted! Follow this lead.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>¡Rastro de néctar detectado! Sigue esta pista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>A little bee whispered a suggestion in your ear.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Una pequeña abeja te susurró una sugerencia al oído.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Undo used immediately after a placement.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Wise bees always double-check.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Las abejas sabias siempre comprueban dos veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Undo used immediately after a placement.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Re-charting the swarm!</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>¡Trazando de nuevo el enjambre!</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Undo used immediately after a placement.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mid-air flight recalculation!</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>¡Recálculo de vuelo en el aire!</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Undo used immediately after a placement.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Hovering backwards...</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Volando hacia atrás...</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Undo used immediately after a placement.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Plucking that card right back out of the wax.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Sacando esa carta directamente de la cera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Undo used immediately after a placement.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Unsticking that card from the comb.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Despegando esa carta del panal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Player wins a match with 4 rules active at once.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Four rules, one victory. Chaos bends to you.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Cuatro reglas, una victoria. El caos se inclina ante ti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Opponent is winning by two cards and is about to place the last card on the board.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>{OpponentName} prepares a final sting!</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>¡{OpponentName} prepara un aguijonazo final!</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Player flips 3+ cards in a single turn.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>A massive swarm!</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>¡Un enjambre masivo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Opponent flips 3+ of the player's cards in a single turn (not a Combo).</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>{OpponentName} unleashes an angry swarm!</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>¡{OpponentName} desata un enjambre furioso!</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Combo x4 or higher.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SWARM FRENZY — the whole hive is buzzing!</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>FRENESÍ DE ENJAMBRE — ¡toda la colmena está zumbando!</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>The hive is nearly overrun... is there any hope left?</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>La colmena está casi invadida... ¿queda alguna esperanza?</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>A placed card captures on all 4 sides at once.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Four-way sting!</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>¡Aguijonazo de cuatro frentes!</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>{OpponentName} is starting to sweat.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>{OpponentName} está empezando a sudar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>{OpponentName} has your number. Time for a new strategy?</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>{OpponentName} ya te tiene calado. ¿Hora de una nueva estrategia?</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>The weakest bee just took down half the hive!</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>¡La abeja más débil acaba de derribar a media colmena!</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>A worker bee just humbled royalty.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Una abeja obrera acaba de humillar a la realeza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Second thoughts... wait, never mind, let's stick to the plan.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Pensándolo bien... no importa, sigamos con el plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>A worker bee never doubts their instincts... twice!</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Una abeja obrera nunca duda de sus instintos... ¡dos veces!</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Just testing the Undo button, right?</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Solo estabas probando el botón de Deshacer, ¿verdad?</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>You just wanted to see that card flip again!</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>¡Solo querías ver cómo se volteaba esa carta otra vez!</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>A plot twist... that went absolutely nowhere!</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Un giro en la trama... ¡que no llevó absolutamente a ninguna parte!</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Taking the scenic route to the exact same move!</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>¡Tomando la ruta panorámica hacia el mismo movimiento exacto!</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>A true rivalry is forming in the comb.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Se está formando una verdadera rivalidad en el panal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Player wins by the maximum possible margin.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Nothing left to sting!</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>¡No queda nada a qué picar!</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>First launch ever</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Welcome to the colony! Time to make some honey.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>¡Bienvenido a la colonia! Hora de hacer un poco de miel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Player reaches 10 total wins.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10 wins. The hive takes notice.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>10 victorias. La colmena toma nota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Player reaches 100 total wins.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>100 wins. The colony sings your name.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>100 victorias. La colonia canta tu nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Player reaches 1000 total wins.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1000 wins. A millennium of triumph. The Queen herself applauds.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1000 victorias. Un milenio de triunfos. La mismísima Reina aplaude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Fallen Ace triggers (a '1' captures a '10').</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>The drone takes down the Queen!</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>¡El zángano derrota a la Reina!</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Fallen Ace triggers (a '1' captures a '10').</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>A lucky sting! The mighty have fallen.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>¡Un aguijonazo de suerte! Los poderosos han caído.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>The pollen's thick today — {AscensionSuit} is in full bloom!</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>El polen está espeso hoy — ¡{AscensionSuit} está en plena floración!</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Smoked Out drops a card's effective stat to 1.</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Smoked out — that card can barely buzz anymore.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ahuevada por el humo — esa carta apenas puede zumbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>The math checks out!</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>¡Las matemáticas son correctas!</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Player wins flawless (opponent score = 0).</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Flawless victory!</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Win Banner</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>¡Victoria perfecta!</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Player wins flawless (opponent score = 0).</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hive domination!</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Win Banner</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>¡Dominio de la colmena!</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Player wins flawless (opponent score = 0).</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>The colony reigns supreme..</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Win Banner</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>La colonia reina supremamente...</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Player loses flawless (0 captures).</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Every card fell. The hive lies in ruins.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>You Lose Banner</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Todas las cartas cayeron. La colmena yace en ruinas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Player loses flawless (0 captures).</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>{OpponentName} didn't leave you a single card standing.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>You Lose Banner</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>{OpponentName} no te dejó ni una sola carta en pie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Player loses flawless (0 captures).</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>There are no bees left in your bonnet.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>You Lose Banner</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Roulette rolls Pollination.</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Pollen is in the air!</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>¡Hay polen en el aire!</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Roulette rolls Smoked Out.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>A haze covers the comb!</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>¡Una niebla cubre el panal!</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Addition is key!</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>¡La suma es clave!</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Roulette rolls Inversion</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Everything is upside down!</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>¡Todo está de cabeza!</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Roulette rolls clear skies</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>The hive is exposed!</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>¡La colmena está expuesta!</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>The drones are out!</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>¡Los zánganos están fuera!</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Roulette rolls Frenzy</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Chaos takes over!</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>¡El caos toma el control!</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Roulette rolls Symmetry</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Patterns Align!</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>¡Los patrones se alinean!</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Roulette rolls Nectar Exchange</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>A trade before the swarm!</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>¡Un intercambio antes del enjambre!</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Roulette rolls Hierarchy</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Order above all!</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>¡El orden ante todo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Moonlight glints off the wax.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>La luz de la luna brilla en la cera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>The dew hasn't dried and the bees are already at it.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>El rocío no se ha secado y las abejas ya están en ello.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>The hive hums with a fresh day's plans.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>La colmena zumba con los planes de un nuevo día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Even bees pause to enjoy the sunshine.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Incluso las abejas se detienen a disfrutar del sol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Half the day's pollen is already in.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>La mitad del polen del día ya está adentro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>The hive settles into its afternoon rhythm.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>La colmena se asienta en su ritmo vespertino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Long shadows, long odds — let's play.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Sombras largas, bajas probabilidades — a jugar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>The last foragers are heading home.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Las últimas recolectoras van de regreso a casa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Lantern-bugs light the way to the hive.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Las luciérnagas iluminan el camino a la colmena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>The Queen's chambers go quiet, but not this table.</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Las cámaras de la Reina quedan en silencio, pero no esta mesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>A nightcap of nectar before bed.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Un último sorbo de néctar antes de dormir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Cornered in the comb... can you pull off a miracle?</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Acorralado en el panal... ¿podrás hacer un milagro?</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Down to your final stand! The hive needs a hero.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>¡Hasta tu último aliento! La colmena necesita un héroe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Only a few cells left! Can a single sting turn the tide?</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>¡Solo quedan unas cuantas celdas! ¿Podrá un solo aguijonazo cambiar el rumbo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Trapped in the comb... one last chance to strike back.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Atrapado en el panal... una última oportunidad de contraatacar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Well... this is getting uncomfortable.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Bueno... esto se está poniendo incómodo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Don't panic! ...Okay, maybe panic just a little.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>¡No entres en pánico! ...Bueno, tal vez entra un poco en pánico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Backed into a corner — just where we want 'em?</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Acorralados en un rincón — ¿justo donde los queríamos?</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Player wins a match with 4 rules active at once.</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>The odds were quadrupled, and so was your glory!</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>¡Las probabilidades se cuadriplicaron, y también tu gloria!</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Player wins a match with 4 rules active at once.</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Four rules? Just four more reasons to win.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>¿Cuatro reglas? Solo cuatro razones más para ganar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Player flips 3+ cards in a single turn.</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Sting 'em all!</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>¡Pícalos a todos!</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Player flips 3+ cards in a single turn.</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Raking in the honey!</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>¡Acumulando la miel!</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Player flips 3+ cards in a single turn.</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>A sweeping sting!</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>¡Un aguijonazo arrasador!</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Opponent flips 3+ of the player's cards in a single turn (not a Combo).</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>{OpponentName} shows no mercy!</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>¡{OpponentName} no muestra piedad!</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Opponent flips 3+ of the player's cards in a single turn (not a Combo).</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>{OpponentName} didn't hold back!</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>¡{OpponentName} no se contuvo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Combo x4 or higher.</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MEGA CASCADE — absolute hive pandemonium!</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>MEGA CASCADA — ¡pandemónium absoluto en la colmena!</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Combo x4 or higher.</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>HIVE SUPERNOVA — a four-fold combo explosion!</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>SUPERNOVA DE COLMENA — ¡una explosión de combo cuádruple!</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Combo x4 or higher.</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ULTIMATE SWARM — cards flipping in every direction!</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ENJAMBRE DEFINITIVO — ¡cartas volteándose en todas direcciones!</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>A placed card captures on all 4 sides at once.</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Omnidirectional sting — nothing on that board was safe!</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Aguijonazo omnidireccional — ¡nada en el tablero estaba a salvo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>A placed card captures on all 4 sides at once.</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Royal center sting!</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>¡Aguijonazo real al centro!</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>A placed card captures on all 4 sides at once.</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Bullseye in the comb!</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>¡En el blanco del panal!</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>{OpponentName}'s wings are getting tired!</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>¡Las alas de {OpponentName} se están cansando!</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>{OpponentName} is losing their buzz!</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>¡{OpponentName} está perdiendo su zumbido!</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>You're ruling this hive!</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>¡Tú gobiernas esta colmena!</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>{OpponentName} can't catch a break.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>{OpponentName} no tiene un momento de respiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>{OpponentName} might need a quick coffee break.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Puede que {OpponentName} necesite un rápido descanso para tomar café.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>{OpponentName} is on a roll… time to shake up your deck!</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>{OpponentName} está en racha… ¡hora de agitar tu mazo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Smoked out by {OpponentName} 3 times in a row!</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>¡Ahuevado con humo por {OpponentName} 3 veces seguidas!</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>The swarm is favoring {OpponentName}… for now!</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>El enjambre está a favor de {OpponentName}… ¡por ahora!</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Got caught in {OpponentName}'s honey trap again!</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>¡Atrapado en la trampa de miel de {OpponentName} otra vez!</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>A humble worker bee just staged a revolution!</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>¡Una humilde abeja obrera acaba de hacer una revolución!</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Smallest bee, ENORMOUS sting!</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>¡Abeja más pequeña, ENORME aguijonazo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Don't judge a bee by its stars!</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>¡No juzgues a una abeja por sus estrellas!</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Small card, big moves!</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>¡Carta pequeña, grandes movimientos!</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>The ultimate rarity mismatch!</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>¡El desajuste de rareza definitivo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Rank means nothing to a sharp stinger!</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>¡El rango no significa nada para un aguijón afilado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Royalty is expensive — tactics are free!</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>La realeza es cara — ¡las tácticas son gratis!</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Big stars fall hard!</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>¡Las grandes estrellas caen fuerte!</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Neither bee backs down — 5 matches and counting!</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Ninguna abeja se rinde — ¡5 partidas y contando!</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Five battles in the same comb! The bees are watching closely.</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>¡Cinco batallas en el mismo panal! Las abejas observan de cerca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Deep in the hive, a classic matchup unfolds.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>En lo profundo de la colmena, se desarrolla un clásico enfrentamiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Player wins by the maximum possible margin.</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Absolute hive takeover!</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>¡Toma de control absoluta de la colmena!</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Player wins by the maximum possible margin.</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>All the honey is yours!</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>¡Toda la miel es tuya!</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Player wins by the maximum possible margin.</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Not even a drone left standing!</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>¡Ni un zángano ha quedado en pie!</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Nectar Exchange swaps away the player's 5-star card.</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>{OpponentName} just flew off with your Royal Jelly!</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>¡{OpponentName} acaba de salir volando con tu Jalea Real!</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Nectar Exchange swaps away the player's 5-star card.</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Highway robbery in the hive! {OpponentName} stole your 5-star!</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>¡Robo a plena luz en la colmena! ¡{OpponentName} robó tu carta de 5 estrellas!</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Nectar Exchange trades the player's worst card for the opponent's best.</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>The nectar favors you.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>El néctar te favorece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Nectar Exchange trades the player's worst card for the opponent's best.</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>A golden exchange.</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Un intercambio dorado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Roulette rolls zero extra rules.</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Pure, unadulterated honey — standard rules apply!</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Miel pura y sin adulterar — ¡se aplican reglas estándar!</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Roulette rolls zero extra rules.</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Back to basics for the bees!</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>¡De vuelta a lo básico para las abejas!</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Roulette rolls zero extra rules.</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Clean comb, clean rules — just you and the cards.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Panal limpio, reglas limpias — solo tú y las cartas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Roulette rolls Pollination.</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Flowers are blooming!</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>¡Las flores están floreciendo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Roulette rolls Pollination.</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Pollen. Everywhere.</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Polen. Por todas partes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Roulette rolls Smoked Out.</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Smoke fills the hive…</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>El humo llena la colmena…</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Do the math!</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>¡Haz los cálculos!</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Sum it up!</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>¡Súmalo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Calculate carefully!</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>¡Calcula con cuidado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Class is in session!</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>¡La clase está en sesión!</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Roulette rolls Inversion</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Flying backwards — low beats high!</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Volando hacia atrás — ¡lo bajo vence a lo alto!</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Roulette rolls clear skies</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Clear Skies overheard.</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Cielos Despejados por encima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Roulette rolls clear skies</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>No shade on the hive today.</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Hoy no hay sombra sobre la colmena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Scout bees have reported back!</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>¡Las abejas exploradoras han regresado con información!</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Reconnaissance in progress!</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>¡Reconocimiento en progreso!</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Intel gathered!</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>¡Información recopilada!</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Roulette rolls Frenzy</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>The bees are out of control!</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>¡Las abejas están fuera de control!</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Roulette rolls Frenzy</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Those bees are wild!</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>¡Esas abejas son salvajes!</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Roulette rolls Symmetry</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Geometric precision required.</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Se requiere precisión geométrica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Roulette rolls Nectar Exchange</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Pre-game trading post open!</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>¡Puesto de intercambio previo a la partida abierto!</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Roulette rolls Nectar Exchange</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Nectar bartering begins!</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>¡Comienza el trueque de néctar!</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Roulette rolls Hierarchy</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Obey the Queen!</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>¡Obedece a la Reina!</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Roulette rolls Hierarchy</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Royal decree issued!</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>¡Decreto real emitido!</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Hearts flutter through the hive today.</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Corazones revolotean por la colmena hoy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Every heart in the comb beats a little louder.</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Cada corazón en el panal late un poco más fuerte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>The hive is full of hearts, and yours is winning.</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>La colmena está llena de corazones, y el tuyo está ganando.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Diamonds sparkle brighter on Valentine's Day.</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Los diamantes brillan más fuerte en el Día de San Valentín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>The bees traded honey for diamonds today.</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Las abejas intercambiaron miel por diamantes hoy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>A diamond in the rough, sweeter than honey.</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Un diamante en bruto, más dulce que la miel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Clover and clubs bloom together this Valentine's.</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Los tréboles florecen juntos este San Valentín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Even the clubs are feeling the love today.</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Incluso los tréboles sienten el amor hoy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Cupid's arrow struck the spades first.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>La flecha de Cupido golpeó a las picas primero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>The spades soften their edges for Valentine's Day.</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Las picas suavizan sus bordes por el Día de San Valentín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Even spades dig deep for love today.</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Incluso las picas cavan profundo por amor hoy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Game loads on Earth Day (Apr 22).</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Protect the flowers, save the bees! Happy Earth Day!</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>¡Protege las flores, salva a las abejas! ¡Feliz Día de la Tierra!</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Game loads on National Honey Day (Aug 15).</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>A golden celebration in the comb — Happy Honey Day!</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Una celebración dorada en el panal — ¡Feliz Día de la Miel!</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Is that card really what it seems… or an April Fools' trick?</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>¿Es esa carta realmente lo que parece… o una broma del Día de los Inocentes?</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Game loads on Pi Day (Mar 14).</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>The math in the comb is extra precise today!</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>¡Las matemáticas en el panal son extra precisas hoy!</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Game loads on New Year's Eve (Dec 31).</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Counting down the final buzz of the year!</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>¡Contando el último zumbido del año!</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Game loads on Christmas (Dec 25).</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Peace, warmth, and sweetness to all in the hive this Christmas!</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>¡Paz, calidez y dulzura a todos en la colmena en esta Navidad!</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Is that a 5-star card, or just a worker bee in a fake crown?</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>¿Es una carta de 5 estrellas, o solo una abeja obrera con una corona falsa?</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Maybe it's time for a wasp theme…</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Tal vez sea hora de un tema de avispas…</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Pranksters in the hive! Trust your cards, not the drones.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>¡Bromistas en la colmena! Confía en tus cartas, no en los zánganos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Game loads on Holi.</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Vibrant colors bloom across the comb! Happy Holi!</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>¡Colores vibrantes florecen en el panal! ¡Feliz Holi!</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Game loads on Rosh Hashanah.</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Wishing you a sweet and fruitful new year — Shanah Tovah from the hive!</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Deseándote un dulce y fructífero año nuevo — ¡Shaná Tová desde la colmena!</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Game loads on Diwali.</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Wishing you a season of light, sweetness, and harmony in the hive.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Deseándote una temporada de luz, dulzura y armonía en la colmena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Game loads on Eid al-Fitr.</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>A season of gratitude, sweetness, and joy. Eid Mubarak from the hive!</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Una temporada de gratitud, dulzura y alegría. ¡Eid Mubarak desde la colmena!</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Game loads on Hanukkah.</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>May your home bee filled with light, peace, and joy this Hanukkah.</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Is that diamond or a rhinestone?</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>¿Es un diamante o un diamante de imitación?</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Calculating 475 moves ahead, or taking a snack break?</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>¿Calculando 475 movimientos por adelantado, o tomando un descanso para merendar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>The cards aren't going to play themselves… though that would be a neat.</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Las cartas no se van a jugar solas… aunque eso sería genial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Checking your hand twice? Santa Bee would be proud.</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>¿Revisando tu mano dos veces? Santa Abeja estaría orgulloso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>No pressure, it's only the entire match on the line.</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Sin presión, es solo la partida entera la que está en juego.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>A masterclass in the dramatic pause.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Una clase magistral de la pausa dramática.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Shuffling your thoughts? We've got time.</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>¿Barajando tus pensamientos? Tenemos tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Brain.exe is processing the optimal placement…</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Brain.exe está procesando la ubicación óptima…</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Calculated to perfection!</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>¡Calculado a la perfección!</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>{AscensionSuit} is drowning in nectar!</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>¡{AscensionSuit} se está ahogando en néctar!</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>A massive harvest! {AscensionSuit} thrives.</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>¡Una cosecha masiva! {AscensionSuit} prospera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Smoked Out drops a card's effective stat to 1.</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Lethargic and grounded.</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Letárgico y en tierra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Has science gone too far? Click here to see this 10-star card.</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>¿Ha ido demasiado lejos la ciencia? Haz clic aquí para ver esta carta de 10 estrellas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Local worker bee discovers secret to endless nectar...</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Abeja obrera local descubre el secreto del néctar infinito...</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Top 10 cards to steal from the Queen. Number 4 will sting you!</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Top 10 de cartas para robar a la Reina. ¡El número 4 te picará!</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Beekeepers will hate you! Win every match with this one simple trick!</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>¡Los apicultores te odiarán! ¡Gana cada partida con este simple truco!</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Get rich or buzz trying.</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>To bee, or not to bee... wait, whose turn is it?</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>May the swarm be with you.</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Que el enjambre te acompañe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Live, Laugh, Pollinate.</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Vive, Ríe, Poliniza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Keep calm and buzz on.</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Home is where the hive is.</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>El hogar está donde está la colmena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Just a worker bee looking for my queen.</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Solo una abeja obrera buscando a mi reina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Are you gonna play a card, or just sit there looking sweet?</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>¿Vas a jugar una carta, o solo te vas a sentar ahí luciendo dulce?</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Frankly, my dear, I don't give a buzz.</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>We're gonna need a bigger hive.</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Vamos a necesitar una colmena más grande.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Show me the honey!</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>¡Muéstrame la miel!</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>I'll bee back.</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Nobody puts Baby Bee in a corner.</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Nadie pone a Abeja Bebé en un rincón.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Sweet dreams are made of bees.</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Bee yourself; everyone else is already taken.</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Mind your own beeswax!</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>This one weird trick captures 4 cards at once — dealers don't want you to know it.</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Este extraño truco captura 4 cartas a la vez — los repartidores no quieren que lo sepas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>You won't believe what happened when a worker bee met a Fallen Ace.</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>No vas a creer lo que pasó cuando una abeja obrera conoció a un As Caído.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>She said yes to Symmetry. He said yes to Math Bee. Chaos ensued.</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Ella dijo sí a la Simetría. Él dijo sí a Abeja Matemática. Se desató el caos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Busy as a bee, broke as a beekeeper.</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Ocupado como una abeja, arruinado como un apicultor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Absence makes the heart grow fonder — and the hive grow louder.</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>La ausencia hace que el corazón se encariñe — y la colmena suene más fuerte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Two bees or not two bees — that's a math problem, not a question.</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>No Translation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F664"/>
+  <dimension ref="A1:F672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20469,6 +20469,246 @@
         </is>
       </c>
       <c r="F664" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>touch_layout_coming_soon</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Placeholder/fallback text</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Touch layout coming soon</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Diseño táctil próximamente</t>
+        </is>
+      </c>
+      <c r="F665" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>touch_blackjack_title</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Title-case game label</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="F666" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>touch_blackjack_banner</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>All-caps banner/header label</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>BLACKJACK</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>BLACKJACK</t>
+        </is>
+      </c>
+      <c r="F667" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>touch_spider_banner</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>All-caps banner/header label</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>SPIDER</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>SPIDER</t>
+        </is>
+      </c>
+      <c r="F668" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>touch_klondike_banner</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>All-caps banner/header label</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>KLONDIKE</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>KLONDIKE</t>
+        </is>
+      </c>
+      <c r="F669" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>touch_beecell_banner</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>All-caps banner/header label</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>BEECELL</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>BEECELL</t>
+        </is>
+      </c>
+      <c r="F670" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Chrome</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>debug_banners_menu</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Mac-only dev menu title</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Banners</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Anuncios</t>
+        </is>
+      </c>
+      <c r="F671" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>ManageDecksWin</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>deck_default_name</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Predeterminado</t>
+        </is>
+      </c>
+      <c r="F672" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F672"/>
+  <dimension ref="A1:F679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20709,6 +20709,216 @@
         </is>
       </c>
       <c r="F672" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>free_play_label</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Free Play</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Juego Libre</t>
+        </is>
+      </c>
+      <c r="F673" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>touch_choose_photo</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Choose Photo</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Elegir Foto</t>
+        </is>
+      </c>
+      <c r="F674" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>touch_choose_different_photo</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Choose a Different Photo</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Elegir Otra Foto</t>
+        </is>
+      </c>
+      <c r="F675" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>touch_pinch_zoom_reposition</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: crop editor section header</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Pinch to zoom, drag to reposition</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
+        </is>
+      </c>
+      <c r="F676" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>touch_name_field_placeholder</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: name TextField placeholder</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="F677" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>touch_name_already_taken_error</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: duplicate-name validation error</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>That name is already taken — pick another.</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Ese nombre ya está en uso — elige otro.</t>
+        </is>
+      </c>
+      <c r="F678" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>touch_enabled_toggle</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>iOS custom face-card-art import sheet: Enabled toggle label</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Activado</t>
+        </is>
+      </c>
+      <c r="F679" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F679"/>
+  <dimension ref="A1:F680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17981,27 +17981,27 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Honeycomb Swarm</t>
+          <t>PokerHands</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_hive_swarm</t>
+          <t>hand_jacks_or_better</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Random banner phrase when the player triggers a Hive Swarm reveal</t>
+          <t>Pay table row / result banner, standard (non-Deuces-Wild, non-Bonus) tables base qualifying win — VideoPokerViewModel.swift/.cs handName</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Your Hive Swarm</t>
+          <t>Jacks or Better</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Tu Enjambre de Colmena</t>
+          <t>Jotas o Mejor</t>
         </is>
       </c>
       <c r="F582" t="b">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_unleashed</t>
+          <t>swarm_reveal_player_hive_swarm</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -18026,12 +18026,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Your Swarm is Unleashed!</t>
+          <t>Your Hive Swarm</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>¡Tu Enjambre se Desata!</t>
+          <t>Tu Enjambre de Colmena</t>
         </is>
       </c>
       <c r="F583" t="b">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_awakens</t>
+          <t>swarm_reveal_player_unleashed</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -18056,12 +18056,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Your Swarm Awakens!</t>
+          <t>Your Swarm is Unleashed!</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>¡Tu Enjambre Despierta!</t>
+          <t>¡Tu Enjambre se Desata!</t>
         </is>
       </c>
       <c r="F584" t="b">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>swarm_reveal_player_buzzing</t>
+          <t>swarm_reveal_player_awakens</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -18086,12 +18086,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Your Hive is Buzzing into Action!</t>
+          <t>Your Swarm Awakens!</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>¡Tu Colmena Zumba en Acción!</t>
+          <t>¡Tu Enjambre Despierta!</t>
         </is>
       </c>
       <c r="F585" t="b">
@@ -18106,22 +18106,22 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_hive_swarm_fmt</t>
+          <t>swarm_reveal_player_buzzing</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Random banner phrase when the opponent triggers a Hive Swarm reveal; %@ is the opponent/difficulty name</t>
+          <t>Random banner phrase when the player triggers a Hive Swarm reveal</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>%@'s Hive Swarm</t>
+          <t>Your Hive is Buzzing into Action!</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Enjambre de Colmena de %@</t>
+          <t>¡Tu Colmena Zumba en Acción!</t>
         </is>
       </c>
       <c r="F586" t="b">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_unleashed_fmt</t>
+          <t>swarm_reveal_opponent_hive_swarm_fmt</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -18146,12 +18146,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>%@'s Swarm is Unleashed!</t>
+          <t>%@'s Hive Swarm</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>¡El Enjambre de %@ se Desata!</t>
+          <t>Enjambre de Colmena de %@</t>
         </is>
       </c>
       <c r="F587" t="b">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_awakens_fmt</t>
+          <t>swarm_reveal_opponent_unleashed_fmt</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -18176,12 +18176,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>%@'s Swarm Awakens!</t>
+          <t>%@'s Swarm is Unleashed!</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>¡El Enjambre de %@ Despierta!</t>
+          <t>¡El Enjambre de %@ se Desata!</t>
         </is>
       </c>
       <c r="F588" t="b">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>swarm_reveal_opponent_buzzing_fmt</t>
+          <t>swarm_reveal_opponent_awakens_fmt</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -18206,12 +18206,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>%@'s Hive is Buzzing into Action!</t>
+          <t>%@'s Swarm Awakens!</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>¡La Colmena de %@ Zumba en Acción!</t>
+          <t>¡El Enjambre de %@ Despierta!</t>
         </is>
       </c>
       <c r="F589" t="b">
@@ -18226,22 +18226,22 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>banner_hive_mind_fmt</t>
+          <t>swarm_reveal_opponent_buzzing_fmt</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Chain-reaction capture combo banner; %d is the flip count (2+)</t>
+          <t>Random banner phrase when the opponent triggers a Hive Swarm reveal; %@ is the opponent/difficulty name</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>HIVE MIND x%d!</t>
+          <t>%@'s Hive is Buzzing into Action!</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>¡MENTE COLMENA x%d!</t>
+          <t>¡La Colmena de %@ Zumba en Acción!</t>
         </is>
       </c>
       <c r="F590" t="b">
@@ -18251,27 +18251,27 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>PreferencesWin</t>
+          <t>Honeycomb Swarm</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>game_mode_section_header</t>
+          <t>banner_hive_mind_fmt</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Windows Options page: Game Mode section header above the draw-mode/suit-count/deck-count picker</t>
+          <t>Chain-reaction capture combo banner; %d is the flip count (2+)</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Game Mode</t>
+          <t>HIVE MIND x%d!</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Modo de Juego</t>
+          <t>¡MENTE COLMENA x%d!</t>
         </is>
       </c>
       <c r="F591" t="b">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>saved_themes_header</t>
+          <t>game_mode_section_header</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Windows Options page: Themes sub-panel sidebar header</t>
+          <t>Windows Options page: Game Mode section header above the draw-mode/suit-count/deck-count picker</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Saved Themes</t>
+          <t>Game Mode</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Temas Guardados</t>
+          <t>Modo de Juego</t>
         </is>
       </c>
       <c r="F592" t="b">
@@ -18316,22 +18316,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>double_click_card_or_background_tooltip</t>
+          <t>saved_themes_header</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Windows Options page: hero preview tooltip (combined card+background, unlike Mac which has separate tooltips)</t>
+          <t>Windows Options page: Themes sub-panel sidebar header</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Double-click the card or the background to adjust it</t>
+          <t>Saved Themes</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Haz doble clic en la carta o el fondo para ajustarlo</t>
+          <t>Temas Guardados</t>
         </is>
       </c>
       <c r="F593" t="b">
@@ -18346,22 +18346,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>delete_background_confirm_body</t>
+          <t>double_click_card_or_background_tooltip</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Windows Options page: Delete Background confirmation dialog body</t>
+          <t>Windows Options page: hero preview tooltip (combined card+background, unlike Mac which has separate tooltips)</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Are you sure you want to delete this custom background? This cannot be undone.</t>
+          <t>Double-click the card or the background to adjust it</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>¿Seguro que quieres eliminar este fondo personalizado? Esto no se puede deshacer.</t>
+          <t>Haz doble clic en la carta o el fondo para ajustarlo</t>
         </is>
       </c>
       <c r="F594" t="b">
@@ -18376,22 +18376,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>save_new_theme_title</t>
+          <t>delete_background_confirm_body</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Windows Options page: Save New Theme dialog title (distinct from the button which has an ellipsis)</t>
+          <t>Windows Options page: Delete Background confirmation dialog body</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Save New Theme</t>
+          <t>Are you sure you want to delete this custom background? This cannot be undone.</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Guardar Nuevo Tema</t>
+          <t>¿Seguro que quieres eliminar este fondo personalizado? Esto no se puede deshacer.</t>
         </is>
       </c>
       <c r="F595" t="b">
@@ -18406,22 +18406,22 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>enter_theme_name_prompt</t>
+          <t>save_new_theme_title</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Windows Options page: Save New Theme dialog prompt text</t>
+          <t>Windows Options page: Save New Theme dialog title (distinct from the button which has an ellipsis)</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Enter a name for this theme:</t>
+          <t>Save New Theme</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Introduce un nombre para este tema:</t>
+          <t>Guardar Nuevo Tema</t>
         </is>
       </c>
       <c r="F596" t="b">
@@ -18436,22 +18436,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>tap_tile_upload_art_hint</t>
+          <t>enter_theme_name_prompt</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Windows Options page: Face Cards sub-panel instructional hint</t>
+          <t>Windows Options page: Save New Theme dialog prompt text</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Tap a tile to upload art. Tap again to adjust.</t>
+          <t>Enter a name for this theme:</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Toca un mosaico para subir arte. Toca de nuevo para ajustar.</t>
+          <t>Introduce un nombre para este tema:</t>
         </is>
       </c>
       <c r="F597" t="b">
@@ -18461,27 +18461,27 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>PreferencesWin</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>suit_name_spades_plain</t>
+          <t>tap_tile_upload_art_hint</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list, e.g. "Ascension: Spades, Hearts"</t>
+          <t>Windows Options page: Face Cards sub-panel instructional hint</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Spades</t>
+          <t>Tap a tile to upload art. Tap again to adjust.</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Picas</t>
+          <t>Toca un mosaico para subir arte. Toca de nuevo para ajustar.</t>
         </is>
       </c>
       <c r="F598" t="b">
@@ -18496,22 +18496,22 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>suit_name_hearts_plain</t>
+          <t>suit_name_spades_plain</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list, e.g. "Ascension: Spades, Hearts"</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Spades</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Corazones</t>
+          <t>Picas</t>
         </is>
       </c>
       <c r="F599" t="b">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>suit_name_diamonds_plain</t>
+          <t>suit_name_hearts_plain</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -18536,12 +18536,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Diamonds</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Diamantes</t>
+          <t>Corazones</t>
         </is>
       </c>
       <c r="F600" t="b">
@@ -18556,7 +18556,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>suit_name_clubs_plain</t>
+          <t>suit_name_diamonds_plain</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Clubs</t>
+          <t>Diamonds</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Tréboles</t>
+          <t>Diamantes</t>
         </is>
       </c>
       <c r="F601" t="b">
@@ -18581,27 +18581,27 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>AboutWin</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>about_downloading_update</t>
+          <t>suit_name_clubs_plain</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Windows About window: update download in progress</t>
+          <t>Plain suit name (no symbol prefix) — Ascension/Descension rule-bar suit list</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Downloading update…</t>
+          <t>Clubs</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Descargando actualización…</t>
+          <t>Tréboles</t>
         </is>
       </c>
       <c r="F602" t="b">
@@ -18616,22 +18616,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>about_downloading_update_pct_fmt</t>
+          <t>about_downloading_update</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Windows About window: update download progress with percentage</t>
+          <t>Windows About window: update download in progress</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Downloading update… %d%%</t>
+          <t>Downloading update…</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Descargando actualización… %d%%</t>
+          <t>Descargando actualización…</t>
         </is>
       </c>
       <c r="F603" t="b">
@@ -18646,22 +18646,22 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>about_update_download_failed</t>
+          <t>about_downloading_update_pct_fmt</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Windows About window: update download failure message</t>
+          <t>Windows About window: update download progress with percentage</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Failed to download the update.</t>
+          <t>Downloading update… %d%%</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>No se pudo descargar la actualización.</t>
+          <t>Descargando actualización… %d%%</t>
         </is>
       </c>
       <c r="F604" t="b">
@@ -18676,22 +18676,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>install_and_restart</t>
+          <t>about_update_download_failed</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Windows About window: button to install a downloaded update and restart</t>
+          <t>Windows About window: update download failure message</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Install &amp; Restart</t>
+          <t>Failed to download the update.</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Instalar y Reiniciar</t>
+          <t>No se pudo descargar la actualización.</t>
         </is>
       </c>
       <c r="F605" t="b">
@@ -18701,27 +18701,27 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>BackgroundEditorWin</t>
+          <t>AboutWin</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>add_background_title</t>
+          <t>install_and_restart</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Windows Background editor window title when adding a new background</t>
+          <t>Windows About window: button to install a downloaded update and restart</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Add Background</t>
+          <t>Install &amp; Restart</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Añadir Fondo</t>
+          <t>Instalar y Reiniciar</t>
         </is>
       </c>
       <c r="F606" t="b">
@@ -18736,22 +18736,22 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>edit_background_title</t>
+          <t>add_background_title</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Windows Background editor window title when editing an existing background</t>
+          <t>Windows Background editor window title when adding a new background</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Edit Background</t>
+          <t>Add Background</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Editar Fondo</t>
+          <t>Añadir Fondo</t>
         </is>
       </c>
       <c r="F607" t="b">
@@ -18761,61 +18761,61 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
+          <t>BackgroundEditorWin</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>edit_background_title</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Windows Background editor window title when editing an existing background</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Edit Background</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Editar Fondo</t>
+        </is>
+      </c>
+      <c r="F608" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
           <t>CardBackEditorWin</t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>card_back_fill_note</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>Windows Card Back editor: note shown instead of position sliders for fill-type card backs</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr">
+      <c r="D609" t="inlineStr">
         <is>
           <t>This card back fills the card automatically
 and doesn't use position adjustments.</t>
         </is>
       </c>
-      <c r="E608" t="inlineStr">
+      <c r="E609" t="inlineStr">
         <is>
           <t>Este reverso de carta llena la carta automáticamente
 y no usa ajustes de posición.</t>
         </is>
       </c>
-      <c r="F608" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>VideoPokerWin</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>btn_deal_d_hotkey</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>Windows Video Poker Deal/Draw toggle button, Deal state (D hotkey)</t>
-        </is>
-      </c>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>Deal  [D]</t>
-        </is>
-      </c>
-      <c r="E609" t="inlineStr">
-        <is>
-          <t>Repartir  [D]</t>
-        </is>
-      </c>
       <c r="F609" t="b">
         <v>1</v>
       </c>
@@ -18828,22 +18828,22 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>btn_draw_d_hotkey</t>
+          <t>btn_deal_d_hotkey</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Windows Video Poker Deal/Draw toggle button, Draw state (D hotkey)</t>
+          <t>Windows Video Poker Deal/Draw toggle button, Deal state (D hotkey)</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Draw  [D]</t>
+          <t>Deal  [D]</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Robar  [D]</t>
+          <t>Repartir  [D]</t>
         </is>
       </c>
       <c r="F610" t="b">
@@ -18853,27 +18853,27 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>DeckBuilderWin</t>
+          <t>VideoPokerWin</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>remove_from_deck_context_menu</t>
+          <t>btn_draw_d_hotkey</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Windows Deck Builder: right-click context menu item on a deck card</t>
+          <t>Windows Video Poker Deal/Draw toggle button, Draw state (D hotkey)</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Remove from deck?</t>
+          <t>Draw  [D]</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>¿Quitar del mazo?</t>
+          <t>Robar  [D]</t>
         </is>
       </c>
       <c r="F611" t="b">
@@ -18883,27 +18883,27 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>ManageDecksWin</t>
+          <t>DeckBuilderWin</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>star_count_filter_fmt</t>
+          <t>remove_from_deck_context_menu</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: star-count filter dropdown item, e.g. "1 Star"/"3 Stars"</t>
+          <t>Windows Deck Builder: right-click context menu item on a deck card</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>%d Star%@</t>
+          <t>Remove from deck?</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>%d Estrella%@</t>
+          <t>¿Quitar del mazo?</t>
         </is>
       </c>
       <c r="F612" t="b">
@@ -18918,22 +18918,22 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>no_cards_match_filter</t>
+          <t>star_count_filter_fmt</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: empty state when the current filter selection matches no cards</t>
+          <t>Windows Manage Decks: star-count filter dropdown item, e.g. "1 Star"/"3 Stars"</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>No cards match this filter.</t>
+          <t>%d Star%@</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Ninguna carta coincide con este filtro.</t>
+          <t>%d Estrella%@</t>
         </is>
       </c>
       <c r="F613" t="b">
@@ -18943,27 +18943,27 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>ManageDecksWin</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>you_lose</t>
+          <t>no_cards_match_filter</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Match-result overlay title on a loss (Honeycomb)</t>
+          <t>Windows Manage Decks: empty state when the current filter selection matches no cards</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>You Lose</t>
+          <t>No cards match this filter.</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Perdiste</t>
+          <t>Ninguna carta coincide con este filtro.</t>
         </is>
       </c>
       <c r="F614" t="b">
@@ -18978,22 +18978,22 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>draw_sudden_death_fmt</t>
+          <t>you_lose</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Match-result overlay title when a tied match enters Sudden Death; %@ is the localized Sudden Death rule name</t>
+          <t>Match-result overlay title on a loss (Honeycomb)</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Draw - %@!</t>
+          <t>You Lose</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>¡Empate - %@!</t>
+          <t>Perdiste</t>
         </is>
       </c>
       <c r="F615" t="b">
@@ -19003,27 +19003,27 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>result_dealer_wins</t>
+          <t>draw_sudden_death_fmt</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Result summary label, single-hand loss (iOS visible text)</t>
+          <t>Match-result overlay title when a tied match enters Sudden Death; %@ is the localized Sudden Death rule name</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Dealer Wins</t>
+          <t>Draw - %@!</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Gana el Repartidor</t>
+          <t>¡Empate - %@!</t>
         </is>
       </c>
       <c r="F616" t="b">
@@ -19038,22 +19038,22 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>result_hand_win_fmt</t>
+          <t>result_dealer_wins</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) win — %d is the hand number</t>
+          <t>Result summary label, single-hand loss (iOS visible text)</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Hand %d: Win</t>
+          <t>Dealer Wins</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Mano %d: Gana</t>
+          <t>Gana el Repartidor</t>
         </is>
       </c>
       <c r="F617" t="b">
@@ -19068,22 +19068,22 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>result_hand_loss_fmt</t>
+          <t>result_hand_win_fmt</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) loss — %d is the hand number</t>
+          <t>Result summary label, multi-hand (split) win — %d is the hand number</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Hand %d: Loss</t>
+          <t>Hand %d: Win</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Mano %d: Pierde</t>
+          <t>Mano %d: Gana</t>
         </is>
       </c>
       <c r="F618" t="b">
@@ -19098,22 +19098,22 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>result_hand_push_fmt</t>
+          <t>result_hand_loss_fmt</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) push — %d is the hand number</t>
+          <t>Result summary label, multi-hand (split) loss — %d is the hand number</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Hand %d: Push</t>
+          <t>Hand %d: Loss</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Mano %d: Empate</t>
+          <t>Mano %d: Pierde</t>
         </is>
       </c>
       <c r="F619" t="b">
@@ -19128,22 +19128,22 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>result_hand_bust_fmt</t>
+          <t>result_hand_push_fmt</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Result summary label, multi-hand (split) bust — %d is the hand number</t>
+          <t>Result summary label, multi-hand (split) push — %d is the hand number</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Hand %d: Bust</t>
+          <t>Hand %d: Push</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Mano %d: Se pasó</t>
+          <t>Mano %d: Empate</t>
         </is>
       </c>
       <c r="F620" t="b">
@@ -19153,27 +19153,27 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>new_match_confirm_title</t>
+          <t>result_hand_bust_fmt</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Confirmation dialog when starting a new match mid-match</t>
+          <t>Result summary label, multi-hand (split) bust — %d is the hand number</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Start a new match? Your current match will end.</t>
+          <t>Hand %d: Bust</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>¿Empezar un nuevo partido? Tu partido actual terminará.</t>
+          <t>Mano %d: Se pasó</t>
         </is>
       </c>
       <c r="F621" t="b">
@@ -19188,22 +19188,22 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>rematch_confirm_title</t>
+          <t>new_match_confirm_title</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Confirmation dialog when requesting a rematch mid-match</t>
+          <t>Confirmation dialog when starting a new match mid-match</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Rematch? Your current match will end.</t>
+          <t>Start a new match? Your current match will end.</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>¿Revancha? Tu partido actual terminará.</t>
+          <t>¿Empezar un nuevo partido? Tu partido actual terminará.</t>
         </is>
       </c>
       <c r="F622" t="b">
@@ -19213,27 +19213,27 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>SlideDownMenuIOS</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>menu_tab_game_selection</t>
+          <t>rematch_confirm_title</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>iOS slide-down menu segmented tab</t>
+          <t>Confirmation dialog when requesting a rematch mid-match</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Game Selection</t>
+          <t>Rematch? Your current match will end.</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Selección de Juego</t>
+          <t>¿Revancha? Tu partido actual terminará.</t>
         </is>
       </c>
       <c r="F623" t="b">
@@ -19248,22 +19248,22 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>menu_header_title</t>
+          <t>menu_tab_game_selection</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>iOS slide-down menu header title</t>
+          <t>iOS slide-down menu segmented tab</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Menu</t>
+          <t>Game Selection</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Menú</t>
+          <t>Selección de Juego</t>
         </is>
       </c>
       <c r="F624" t="b">
@@ -19278,22 +19278,22 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>close_menu_a11y</t>
+          <t>menu_header_title</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>iOS slide-down menu close-button accessibility label</t>
+          <t>iOS slide-down menu header title</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Close menu</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Cerrar menú</t>
+          <t>Menú</t>
         </is>
       </c>
       <c r="F625" t="b">
@@ -19308,22 +19308,22 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>menu_section_game</t>
+          <t>close_menu_a11y</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Game Selection tab section header</t>
+          <t>iOS slide-down menu close-button accessibility label</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>Close menu</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Juego</t>
+          <t>Cerrar menú</t>
         </is>
       </c>
       <c r="F626" t="b">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>menu_section_theme</t>
+          <t>menu_section_game</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab felt-color section header</t>
+          <t>iOS slide-down menu Game Selection tab section header</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Tema</t>
+          <t>Juego</t>
         </is>
       </c>
       <c r="F627" t="b">
@@ -19368,22 +19368,22 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>menu_section_card_back</t>
+          <t>menu_section_theme</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab card-back section header</t>
+          <t>iOS slide-down menu Themes tab felt-color section header</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Card Back</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Reverso de Carta</t>
+          <t>Tema</t>
         </is>
       </c>
       <c r="F628" t="b">
@@ -19398,22 +19398,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>menu_section_background</t>
+          <t>menu_section_card_back</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab background section header</t>
+          <t>iOS slide-down menu Themes tab card-back section header</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Card Back</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Fondo</t>
+          <t>Reverso de Carta</t>
         </is>
       </c>
       <c r="F629" t="b">
@@ -19428,22 +19428,22 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>background_none_option</t>
+          <t>menu_section_background</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: clears the custom background back to felt color</t>
+          <t>iOS slide-down menu Themes tab background section header</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Fondo</t>
         </is>
       </c>
       <c r="F630" t="b">
@@ -19458,22 +19458,22 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>remove_card_back_alert_title</t>
+          <t>background_none_option</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom card back</t>
+          <t>iOS slide-down menu: clears the custom background back to felt color</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Remove Card Back?</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>¿Quitar Reverso de Carta?</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="F631" t="b">
@@ -19488,22 +19488,22 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>remove_background_alert_title</t>
+          <t>remove_card_back_alert_title</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom background</t>
+          <t>iOS slide-down menu: confirm removing a custom card back</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Remove Background?</t>
+          <t>Remove Card Back?</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>¿Quitar Fondo?</t>
+          <t>¿Quitar Reverso de Carta?</t>
         </is>
       </c>
       <c r="F632" t="b">
@@ -19518,22 +19518,22 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>remove_imported_image_body</t>
+          <t>remove_background_alert_title</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
+          <t>iOS slide-down menu: confirm removing a custom background</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>This removes the imported image. It can't be undone.</t>
+          <t>Remove Background?</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
+          <t>¿Quitar Fondo?</t>
         </is>
       </c>
       <c r="F633" t="b">
@@ -19548,22 +19548,22 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>statistics_nav_row</t>
+          <t>remove_imported_image_body</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Statistics destination row</t>
+          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>This removes the imported image. It can't be undone.</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Estadísticas</t>
+          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
         </is>
       </c>
       <c r="F634" t="b">
@@ -19578,22 +19578,22 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>how_to_play_nav_row</t>
+          <t>statistics_nav_row</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Help destination row</t>
+          <t>iOS slide-down menu: Statistics destination row</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>How to Play</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Cómo Jugar</t>
+          <t>Estadísticas</t>
         </is>
       </c>
       <c r="F635" t="b">
@@ -19608,22 +19608,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>face_card_art_nav_row</t>
+          <t>how_to_play_nav_row</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Face Card Art destination row</t>
+          <t>iOS slide-down menu: Help destination row</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Face Card Art</t>
+          <t>How to Play</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Arte de Carta</t>
+          <t>Cómo Jugar</t>
         </is>
       </c>
       <c r="F636" t="b">
@@ -19633,27 +19633,27 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>SlideDownMenuIOS</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>touch_new_deal_label</t>
+          <t>face_card_art_nav_row</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS slide-down menu: Face Card Art destination row</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Face Card Art</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Arte de Carta</t>
         </is>
       </c>
       <c r="F637" t="b">
@@ -19668,22 +19668,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>touch_undo_last_move_label</t>
+          <t>touch_new_deal_label</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Undo Last Move</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Deshacer Última Jugada</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F638" t="b">
@@ -19698,22 +19698,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>touch_deal_a11y</t>
+          <t>touch_undo_last_move_label</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: stock pile accessibility label</t>
+          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Deal</t>
+          <t>Undo Last Move</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Repartir</t>
+          <t>Deshacer Última Jugada</t>
         </is>
       </c>
       <c r="F639" t="b">
@@ -19728,22 +19728,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>touch_completed_runs_a11y</t>
+          <t>touch_deal_a11y</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
+          <t>iOS Spider touch view: stock pile accessibility label</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Completed runs</t>
+          <t>Deal</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Series completadas</t>
+          <t>Repartir</t>
         </is>
       </c>
       <c r="F640" t="b">
@@ -19758,22 +19758,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>touch_decks_picker_label</t>
+          <t>touch_completed_runs_a11y</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker label</t>
+          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Decks</t>
+          <t>Completed runs</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Mazos</t>
+          <t>Series completadas</t>
         </is>
       </c>
       <c r="F641" t="b">
@@ -19788,22 +19788,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>touch_single_deck_option</t>
+          <t>touch_decks_picker_label</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker option</t>
+          <t>iOS Beecell touch view: deck-count Picker label</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Single Deck</t>
+          <t>Decks</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Mazo Sencillo</t>
+          <t>Mazos</t>
         </is>
       </c>
       <c r="F642" t="b">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>touch_double_deck_option</t>
+          <t>touch_single_deck_option</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -19828,12 +19828,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Double Deck</t>
+          <t>Single Deck</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Doble Mazo</t>
+          <t>Mazo Sencillo</t>
         </is>
       </c>
       <c r="F643" t="b">
@@ -19848,22 +19848,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>touch_suits_picker_label</t>
+          <t>touch_double_deck_option</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
+          <t>iOS Beecell touch view: deck-count Picker option</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Suits</t>
+          <t>Double Deck</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Palos</t>
+          <t>Doble Mazo</t>
         </is>
       </c>
       <c r="F644" t="b">
@@ -19878,22 +19878,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>touch_bet_max_button</t>
+          <t>touch_suits_picker_label</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: Max bet button</t>
+          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Suits</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Máx</t>
+          <t>Palos</t>
         </is>
       </c>
       <c r="F645" t="b">
@@ -19908,22 +19908,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_between_hands</t>
+          <t>touch_bet_max_button</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
+          <t>iOS Video Poker touch view: Max bet button</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Settings unlock between hands.</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea entre manos.</t>
+          <t>Máx</t>
         </is>
       </c>
       <c r="F646" t="b">
@@ -19938,22 +19938,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_hand_ends</t>
+          <t>touch_settings_unlock_between_hands</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
+          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Settings unlock when the hand ends.</t>
+          <t>Settings unlock between hands.</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea cuando termina la mano.</t>
+          <t>La configuración se desbloquea entre manos.</t>
         </is>
       </c>
       <c r="F647" t="b">
@@ -19968,22 +19968,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>touch_hands_dealt_stat</t>
+          <t>touch_settings_unlock_hand_ends</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
+          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Hands Dealt</t>
+          <t>Settings unlock when the hand ends.</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Manos Repartidas</t>
+          <t>La configuración se desbloquea cuando termina la mano.</t>
         </is>
       </c>
       <c r="F648" t="b">
@@ -19998,22 +19998,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>touch_session_credits_stat</t>
+          <t>touch_hands_dealt_stat</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
+          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Session Credits</t>
+          <t>Hands Dealt</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Créditos de Sesión</t>
+          <t>Manos Repartidas</t>
         </is>
       </c>
       <c r="F649" t="b">
@@ -20028,22 +20028,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>touch_hand_label_fmt</t>
+          <t>touch_session_credits_stat</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
+          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>HAND %d</t>
+          <t>Session Credits</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>MANO %d</t>
+          <t>Créditos de Sesión</t>
         </is>
       </c>
       <c r="F650" t="b">
@@ -20058,22 +20058,22 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>touch_you_label</t>
+          <t>touch_hand_label_fmt</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
+          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>YOU</t>
+          <t>HAND %d</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>TÚ</t>
+          <t>MANO %d</t>
         </is>
       </c>
       <c r="F651" t="b">
@@ -20088,22 +20088,22 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>touch_bust_suffix</t>
+          <t>touch_you_label</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
+          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BUST</t>
+          <t>YOU</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SE PASÓ</t>
+          <t>TÚ</t>
         </is>
       </c>
       <c r="F652" t="b">
@@ -20118,22 +20118,22 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>touch_result_win</t>
+          <t>touch_bust_suffix</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand result badge</t>
+          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t xml:space="preserve"> BUST</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>GANA</t>
+          <t xml:space="preserve"> SE PASÓ</t>
         </is>
       </c>
       <c r="F653" t="b">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>touch_result_loss</t>
+          <t>touch_result_win</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -20158,12 +20158,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>PIERDE</t>
+          <t>GANA</t>
         </is>
       </c>
       <c r="F654" t="b">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>touch_result_push</t>
+          <t>touch_result_loss</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -20188,12 +20188,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>PUSH</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>EMPATE</t>
+          <t>PIERDE</t>
         </is>
       </c>
       <c r="F655" t="b">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>touch_result_blackjack</t>
+          <t>touch_result_push</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -20218,12 +20218,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>BLACKJACK!</t>
+          <t>PUSH</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>¡BLACKJACK!</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="F656" t="b">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>touch_result_bust</t>
+          <t>touch_result_blackjack</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -20248,12 +20248,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>BUST</t>
+          <t>BLACKJACK!</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>SE PASÓ</t>
+          <t>¡BLACKJACK!</t>
         </is>
       </c>
       <c r="F657" t="b">
@@ -20268,22 +20268,22 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>touch_action_hit</t>
+          <t>touch_result_bust</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: action button</t>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>BUST</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Pedir</t>
+          <t>SE PASÓ</t>
         </is>
       </c>
       <c r="F658" t="b">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>touch_action_stand</t>
+          <t>touch_action_hit</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -20308,12 +20308,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Hit</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Plantarse</t>
+          <t>Pedir</t>
         </is>
       </c>
       <c r="F659" t="b">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>touch_action_double</t>
+          <t>touch_action_stand</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -20338,12 +20338,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Doblar</t>
+          <t>Plantarse</t>
         </is>
       </c>
       <c r="F660" t="b">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>touch_action_split</t>
+          <t>touch_action_double</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -20368,12 +20368,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Dividir</t>
+          <t>Doblar</t>
         </is>
       </c>
       <c r="F661" t="b">
@@ -20388,22 +20388,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>touch_reset_position_button</t>
+          <t>touch_action_split</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: Reset Position button</t>
+          <t>iOS Blackjack touch view: action button</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Reset Position</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Restablecer Posición</t>
+          <t>Dividir</t>
         </is>
       </c>
       <c r="F662" t="b">
@@ -20418,22 +20418,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>touch_add_card_back_title</t>
+          <t>touch_reset_position_button</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>iOS custom card-back import sheet nav title</t>
+          <t>iOS custom-art import sheets: Reset Position button</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Add Card Back</t>
+          <t>Reset Position</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Añadir Reverso de Carta</t>
+          <t>Restablecer Posición</t>
         </is>
       </c>
       <c r="F663" t="b">
@@ -20443,61 +20443,61 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>touch_add_card_back_title</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>iOS custom card-back import sheet nav title</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Add Card Back</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Añadir Reverso de Carta</t>
+        </is>
+      </c>
+      <c r="F664" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
           <t>Honeycomb</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>steal_instruction_tap</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>Steal-mode instructional hint, iOS (touch wording — Mac/Windows use the click-based steal_instruction key)</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr">
+      <c r="D665" t="inlineStr">
         <is>
           <t>Double-tap a captured opponent's card
 on the board to steal it.</t>
         </is>
       </c>
-      <c r="E664" t="inlineStr">
+      <c r="E665" t="inlineStr">
         <is>
           <t>Toca dos veces la carta capturada de un oponente
 en el tablero para robarla.</t>
         </is>
       </c>
-      <c r="F664" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>TouchViewsIOS</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>touch_layout_coming_soon</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>Placeholder/fallback text</t>
-        </is>
-      </c>
-      <c r="D665" t="inlineStr">
-        <is>
-          <t>Touch layout coming soon</t>
-        </is>
-      </c>
-      <c r="E665" t="inlineStr">
-        <is>
-          <t>Diseño táctil próximamente</t>
-        </is>
-      </c>
       <c r="F665" t="b">
         <v>1</v>
       </c>
@@ -20510,26 +20510,26 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>touch_blackjack_title</t>
+          <t>touch_layout_coming_soon</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Title-case game label</t>
+          <t>Placeholder/fallback text</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Touch layout coming soon</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Diseño táctil próximamente</t>
         </is>
       </c>
       <c r="F666" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="667">
@@ -20540,22 +20540,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>touch_blackjack_banner</t>
+          <t>touch_blackjack_title</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>All-caps banner/header label</t>
+          <t>Title-case game label</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="F667" t="b">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>touch_spider_banner</t>
+          <t>touch_blackjack_banner</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="F668" t="b">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>touch_klondike_banner</t>
+          <t>touch_spider_banner</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -20610,12 +20610,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="F669" t="b">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>touch_beecell_banner</t>
+          <t>touch_klondike_banner</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -20640,12 +20640,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="F670" t="b">
@@ -20655,57 +20655,57 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Chrome</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>debug_banners_menu</t>
+          <t>touch_beecell_banner</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Mac-only dev menu title</t>
+          <t>All-caps banner/header label</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Banners</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Anuncios</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="F671" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>ManageDecksWin</t>
+          <t>Chrome</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>deck_default_name</t>
+          <t>debug_banners_menu</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
+          <t>Mac-only dev menu title</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Banners</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Predeterminado</t>
+          <t>Anuncios</t>
         </is>
       </c>
       <c r="F672" t="b">
@@ -20715,27 +20715,27 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>ManageDecksWin</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>free_play_label</t>
+          <t>deck_default_name</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
+          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Free Play</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Juego Libre</t>
+          <t>Predeterminado</t>
         </is>
       </c>
       <c r="F673" t="b">
@@ -20750,22 +20750,22 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>touch_choose_photo</t>
+          <t>free_play_label</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
+          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Choose Photo</t>
+          <t>Free Play</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Elegir Foto</t>
+          <t>Juego Libre</t>
         </is>
       </c>
       <c r="F674" t="b">
@@ -20780,22 +20780,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>touch_choose_different_photo</t>
+          <t>touch_choose_photo</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
+          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Choose a Different Photo</t>
+          <t>Choose Photo</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Elegir Otra Foto</t>
+          <t>Elegir Foto</t>
         </is>
       </c>
       <c r="F675" t="b">
@@ -20810,22 +20810,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>touch_pinch_zoom_reposition</t>
+          <t>touch_choose_different_photo</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: crop editor section header</t>
+          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Pinch to zoom, drag to reposition</t>
+          <t>Choose a Different Photo</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
+          <t>Elegir Otra Foto</t>
         </is>
       </c>
       <c r="F676" t="b">
@@ -20840,22 +20840,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>touch_name_field_placeholder</t>
+          <t>touch_pinch_zoom_reposition</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: name TextField placeholder</t>
+          <t>iOS custom-art import sheets: crop editor section header</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Pinch to zoom, drag to reposition</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
         </is>
       </c>
       <c r="F677" t="b">
@@ -20870,22 +20870,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>touch_name_already_taken_error</t>
+          <t>touch_name_field_placeholder</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: duplicate-name validation error</t>
+          <t>iOS custom-art import sheets: name TextField placeholder</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>That name is already taken — pick another.</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Ese nombre ya está en uso — elige otro.</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F678" t="b">
@@ -20900,25 +20900,55 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
+          <t>touch_name_already_taken_error</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: duplicate-name validation error</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>That name is already taken — pick another.</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Ese nombre ya está en uso — elige otro.</t>
+        </is>
+      </c>
+      <c r="F679" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
           <t>touch_enabled_toggle</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>iOS custom face-card-art import sheet: Enabled toggle label</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr">
+      <c r="D680" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="E679" t="inlineStr">
+      <c r="E680" t="inlineStr">
         <is>
           <t>Activado</t>
         </is>
       </c>
-      <c r="F679" t="b">
+      <c r="F680" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F680"/>
+  <dimension ref="A1:F681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19303,27 +19303,27 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>SlideDownMenuIOS</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>close_menu_a11y</t>
+          <t>search_a11y</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>iOS slide-down menu close-button accessibility label</t>
+          <t>Accessibility label for the search icon in the iOS Themes full-screen sheet toolbar</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Close menu</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Cerrar menú</t>
+          <t>Buscar</t>
         </is>
       </c>
       <c r="F626" t="b">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>menu_section_game</t>
+          <t>close_menu_a11y</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Game Selection tab section header</t>
+          <t>iOS slide-down menu close-button accessibility label</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>Close menu</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Juego</t>
+          <t>Cerrar menú</t>
         </is>
       </c>
       <c r="F627" t="b">
@@ -19368,22 +19368,22 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>menu_section_theme</t>
+          <t>menu_section_game</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab felt-color section header</t>
+          <t>iOS slide-down menu Game Selection tab section header</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Tema</t>
+          <t>Juego</t>
         </is>
       </c>
       <c r="F628" t="b">
@@ -19398,22 +19398,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>menu_section_card_back</t>
+          <t>menu_section_theme</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab card-back section header</t>
+          <t>iOS slide-down menu Themes tab felt-color section header</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Card Back</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Reverso de Carta</t>
+          <t>Tema</t>
         </is>
       </c>
       <c r="F629" t="b">
@@ -19428,22 +19428,22 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>menu_section_background</t>
+          <t>menu_section_card_back</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab background section header</t>
+          <t>iOS slide-down menu Themes tab card-back section header</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Card Back</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Fondo</t>
+          <t>Reverso de Carta</t>
         </is>
       </c>
       <c r="F630" t="b">
@@ -19458,22 +19458,22 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>background_none_option</t>
+          <t>menu_section_background</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: clears the custom background back to felt color</t>
+          <t>iOS slide-down menu Themes tab background section header</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Fondo</t>
         </is>
       </c>
       <c r="F631" t="b">
@@ -19488,22 +19488,22 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>remove_card_back_alert_title</t>
+          <t>background_none_option</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom card back</t>
+          <t>iOS slide-down menu: clears the custom background back to felt color</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Remove Card Back?</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>¿Quitar Reverso de Carta?</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="F632" t="b">
@@ -19518,22 +19518,22 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>remove_background_alert_title</t>
+          <t>remove_card_back_alert_title</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom background</t>
+          <t>iOS slide-down menu: confirm removing a custom card back</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Remove Background?</t>
+          <t>Remove Card Back?</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>¿Quitar Fondo?</t>
+          <t>¿Quitar Reverso de Carta?</t>
         </is>
       </c>
       <c r="F633" t="b">
@@ -19548,22 +19548,22 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>remove_imported_image_body</t>
+          <t>remove_background_alert_title</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
+          <t>iOS slide-down menu: confirm removing a custom background</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>This removes the imported image. It can't be undone.</t>
+          <t>Remove Background?</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
+          <t>¿Quitar Fondo?</t>
         </is>
       </c>
       <c r="F634" t="b">
@@ -19578,22 +19578,22 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>statistics_nav_row</t>
+          <t>remove_imported_image_body</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Statistics destination row</t>
+          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>This removes the imported image. It can't be undone.</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Estadísticas</t>
+          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
         </is>
       </c>
       <c r="F635" t="b">
@@ -19608,22 +19608,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>how_to_play_nav_row</t>
+          <t>statistics_nav_row</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Help destination row</t>
+          <t>iOS slide-down menu: Statistics destination row</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>How to Play</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Cómo Jugar</t>
+          <t>Estadísticas</t>
         </is>
       </c>
       <c r="F636" t="b">
@@ -19638,22 +19638,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>face_card_art_nav_row</t>
+          <t>how_to_play_nav_row</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Face Card Art destination row</t>
+          <t>iOS slide-down menu: Help destination row</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Face Card Art</t>
+          <t>How to Play</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Arte de Carta</t>
+          <t>Cómo Jugar</t>
         </is>
       </c>
       <c r="F637" t="b">
@@ -19663,27 +19663,27 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>SlideDownMenuIOS</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>touch_new_deal_label</t>
+          <t>face_card_art_nav_row</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS slide-down menu: Face Card Art destination row</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Face Card Art</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Arte de Carta</t>
         </is>
       </c>
       <c r="F638" t="b">
@@ -19698,22 +19698,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>touch_undo_last_move_label</t>
+          <t>touch_new_deal_label</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Undo Last Move</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Deshacer Última Jugada</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F639" t="b">
@@ -19728,22 +19728,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>touch_deal_a11y</t>
+          <t>touch_undo_last_move_label</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: stock pile accessibility label</t>
+          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Deal</t>
+          <t>Undo Last Move</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Repartir</t>
+          <t>Deshacer Última Jugada</t>
         </is>
       </c>
       <c r="F640" t="b">
@@ -19758,22 +19758,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>touch_completed_runs_a11y</t>
+          <t>touch_deal_a11y</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
+          <t>iOS Spider touch view: stock pile accessibility label</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Completed runs</t>
+          <t>Deal</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Series completadas</t>
+          <t>Repartir</t>
         </is>
       </c>
       <c r="F641" t="b">
@@ -19788,22 +19788,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>touch_decks_picker_label</t>
+          <t>touch_completed_runs_a11y</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker label</t>
+          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Decks</t>
+          <t>Completed runs</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Mazos</t>
+          <t>Series completadas</t>
         </is>
       </c>
       <c r="F642" t="b">
@@ -19818,22 +19818,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>touch_single_deck_option</t>
+          <t>touch_decks_picker_label</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker option</t>
+          <t>iOS Beecell touch view: deck-count Picker label</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Single Deck</t>
+          <t>Decks</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Mazo Sencillo</t>
+          <t>Mazos</t>
         </is>
       </c>
       <c r="F643" t="b">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>touch_double_deck_option</t>
+          <t>touch_single_deck_option</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -19858,12 +19858,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Double Deck</t>
+          <t>Single Deck</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Doble Mazo</t>
+          <t>Mazo Sencillo</t>
         </is>
       </c>
       <c r="F644" t="b">
@@ -19878,22 +19878,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>touch_suits_picker_label</t>
+          <t>touch_double_deck_option</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
+          <t>iOS Beecell touch view: deck-count Picker option</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Suits</t>
+          <t>Double Deck</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Palos</t>
+          <t>Doble Mazo</t>
         </is>
       </c>
       <c r="F645" t="b">
@@ -19908,22 +19908,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>touch_bet_max_button</t>
+          <t>touch_suits_picker_label</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: Max bet button</t>
+          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Suits</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Máx</t>
+          <t>Palos</t>
         </is>
       </c>
       <c r="F646" t="b">
@@ -19938,22 +19938,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_between_hands</t>
+          <t>touch_bet_max_button</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
+          <t>iOS Video Poker touch view: Max bet button</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Settings unlock between hands.</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea entre manos.</t>
+          <t>Máx</t>
         </is>
       </c>
       <c r="F647" t="b">
@@ -19968,22 +19968,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_hand_ends</t>
+          <t>touch_settings_unlock_between_hands</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
+          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Settings unlock when the hand ends.</t>
+          <t>Settings unlock between hands.</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea cuando termina la mano.</t>
+          <t>La configuración se desbloquea entre manos.</t>
         </is>
       </c>
       <c r="F648" t="b">
@@ -19998,22 +19998,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>touch_hands_dealt_stat</t>
+          <t>touch_settings_unlock_hand_ends</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
+          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Hands Dealt</t>
+          <t>Settings unlock when the hand ends.</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Manos Repartidas</t>
+          <t>La configuración se desbloquea cuando termina la mano.</t>
         </is>
       </c>
       <c r="F649" t="b">
@@ -20028,22 +20028,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>touch_session_credits_stat</t>
+          <t>touch_hands_dealt_stat</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
+          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Session Credits</t>
+          <t>Hands Dealt</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Créditos de Sesión</t>
+          <t>Manos Repartidas</t>
         </is>
       </c>
       <c r="F650" t="b">
@@ -20058,22 +20058,22 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>touch_hand_label_fmt</t>
+          <t>touch_session_credits_stat</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
+          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>HAND %d</t>
+          <t>Session Credits</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>MANO %d</t>
+          <t>Créditos de Sesión</t>
         </is>
       </c>
       <c r="F651" t="b">
@@ -20088,22 +20088,22 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>touch_you_label</t>
+          <t>touch_hand_label_fmt</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
+          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>YOU</t>
+          <t>HAND %d</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>TÚ</t>
+          <t>MANO %d</t>
         </is>
       </c>
       <c r="F652" t="b">
@@ -20118,22 +20118,22 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>touch_bust_suffix</t>
+          <t>touch_you_label</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
+          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BUST</t>
+          <t>YOU</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SE PASÓ</t>
+          <t>TÚ</t>
         </is>
       </c>
       <c r="F653" t="b">
@@ -20148,22 +20148,22 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>touch_result_win</t>
+          <t>touch_bust_suffix</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand result badge</t>
+          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t xml:space="preserve"> BUST</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>GANA</t>
+          <t xml:space="preserve"> SE PASÓ</t>
         </is>
       </c>
       <c r="F654" t="b">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>touch_result_loss</t>
+          <t>touch_result_win</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -20188,12 +20188,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>PIERDE</t>
+          <t>GANA</t>
         </is>
       </c>
       <c r="F655" t="b">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>touch_result_push</t>
+          <t>touch_result_loss</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -20218,12 +20218,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>PUSH</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>EMPATE</t>
+          <t>PIERDE</t>
         </is>
       </c>
       <c r="F656" t="b">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>touch_result_blackjack</t>
+          <t>touch_result_push</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -20248,12 +20248,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>BLACKJACK!</t>
+          <t>PUSH</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>¡BLACKJACK!</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="F657" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>touch_result_bust</t>
+          <t>touch_result_blackjack</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -20278,12 +20278,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>BUST</t>
+          <t>BLACKJACK!</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>SE PASÓ</t>
+          <t>¡BLACKJACK!</t>
         </is>
       </c>
       <c r="F658" t="b">
@@ -20298,22 +20298,22 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>touch_action_hit</t>
+          <t>touch_result_bust</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: action button</t>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>BUST</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Pedir</t>
+          <t>SE PASÓ</t>
         </is>
       </c>
       <c r="F659" t="b">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>touch_action_stand</t>
+          <t>touch_action_hit</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -20338,12 +20338,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Hit</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Plantarse</t>
+          <t>Pedir</t>
         </is>
       </c>
       <c r="F660" t="b">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>touch_action_double</t>
+          <t>touch_action_stand</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -20368,12 +20368,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Doblar</t>
+          <t>Plantarse</t>
         </is>
       </c>
       <c r="F661" t="b">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>touch_action_split</t>
+          <t>touch_action_double</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -20398,12 +20398,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Dividir</t>
+          <t>Doblar</t>
         </is>
       </c>
       <c r="F662" t="b">
@@ -20418,22 +20418,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>touch_reset_position_button</t>
+          <t>touch_action_split</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: Reset Position button</t>
+          <t>iOS Blackjack touch view: action button</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Reset Position</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Restablecer Posición</t>
+          <t>Dividir</t>
         </is>
       </c>
       <c r="F663" t="b">
@@ -20448,22 +20448,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>touch_add_card_back_title</t>
+          <t>touch_reset_position_button</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>iOS custom card-back import sheet nav title</t>
+          <t>iOS custom-art import sheets: Reset Position button</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Add Card Back</t>
+          <t>Reset Position</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Añadir Reverso de Carta</t>
+          <t>Restablecer Posición</t>
         </is>
       </c>
       <c r="F664" t="b">
@@ -20473,61 +20473,61 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>touch_add_card_back_title</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>iOS custom card-back import sheet nav title</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Add Card Back</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Añadir Reverso de Carta</t>
+        </is>
+      </c>
+      <c r="F665" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
           <t>Honeycomb</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>steal_instruction_tap</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>Steal-mode instructional hint, iOS (touch wording — Mac/Windows use the click-based steal_instruction key)</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr">
+      <c r="D666" t="inlineStr">
         <is>
           <t>Double-tap a captured opponent's card
 on the board to steal it.</t>
         </is>
       </c>
-      <c r="E665" t="inlineStr">
+      <c r="E666" t="inlineStr">
         <is>
           <t>Toca dos veces la carta capturada de un oponente
 en el tablero para robarla.</t>
         </is>
       </c>
-      <c r="F665" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>TouchViewsIOS</t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>touch_layout_coming_soon</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
-        <is>
-          <t>Placeholder/fallback text</t>
-        </is>
-      </c>
-      <c r="D666" t="inlineStr">
-        <is>
-          <t>Touch layout coming soon</t>
-        </is>
-      </c>
-      <c r="E666" t="inlineStr">
-        <is>
-          <t>Diseño táctil próximamente</t>
-        </is>
-      </c>
       <c r="F666" t="b">
         <v>1</v>
       </c>
@@ -20540,26 +20540,26 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>touch_blackjack_title</t>
+          <t>touch_layout_coming_soon</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Title-case game label</t>
+          <t>Placeholder/fallback text</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Touch layout coming soon</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Diseño táctil próximamente</t>
         </is>
       </c>
       <c r="F667" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
@@ -20570,22 +20570,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>touch_blackjack_banner</t>
+          <t>touch_blackjack_title</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>All-caps banner/header label</t>
+          <t>Title-case game label</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="F668" t="b">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>touch_spider_banner</t>
+          <t>touch_blackjack_banner</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -20610,12 +20610,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="F669" t="b">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>touch_klondike_banner</t>
+          <t>touch_spider_banner</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -20640,12 +20640,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="F670" t="b">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>touch_beecell_banner</t>
+          <t>touch_klondike_banner</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -20670,12 +20670,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="F671" t="b">
@@ -20685,57 +20685,57 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Chrome</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>debug_banners_menu</t>
+          <t>touch_beecell_banner</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Mac-only dev menu title</t>
+          <t>All-caps banner/header label</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Banners</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Anuncios</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="F672" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>ManageDecksWin</t>
+          <t>Chrome</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>deck_default_name</t>
+          <t>debug_banners_menu</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
+          <t>Mac-only dev menu title</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Banners</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Predeterminado</t>
+          <t>Anuncios</t>
         </is>
       </c>
       <c r="F673" t="b">
@@ -20745,27 +20745,27 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>ManageDecksWin</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>free_play_label</t>
+          <t>deck_default_name</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
+          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Free Play</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Juego Libre</t>
+          <t>Predeterminado</t>
         </is>
       </c>
       <c r="F674" t="b">
@@ -20780,22 +20780,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>touch_choose_photo</t>
+          <t>free_play_label</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
+          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Choose Photo</t>
+          <t>Free Play</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Elegir Foto</t>
+          <t>Juego Libre</t>
         </is>
       </c>
       <c r="F675" t="b">
@@ -20810,22 +20810,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>touch_choose_different_photo</t>
+          <t>touch_choose_photo</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
+          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Choose a Different Photo</t>
+          <t>Choose Photo</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Elegir Otra Foto</t>
+          <t>Elegir Foto</t>
         </is>
       </c>
       <c r="F676" t="b">
@@ -20840,22 +20840,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>touch_pinch_zoom_reposition</t>
+          <t>touch_choose_different_photo</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: crop editor section header</t>
+          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Pinch to zoom, drag to reposition</t>
+          <t>Choose a Different Photo</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
+          <t>Elegir Otra Foto</t>
         </is>
       </c>
       <c r="F677" t="b">
@@ -20870,22 +20870,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>touch_name_field_placeholder</t>
+          <t>touch_pinch_zoom_reposition</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: name TextField placeholder</t>
+          <t>iOS custom-art import sheets: crop editor section header</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Pinch to zoom, drag to reposition</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
         </is>
       </c>
       <c r="F678" t="b">
@@ -20900,22 +20900,22 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>touch_name_already_taken_error</t>
+          <t>touch_name_field_placeholder</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: duplicate-name validation error</t>
+          <t>iOS custom-art import sheets: name TextField placeholder</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>That name is already taken — pick another.</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Ese nombre ya está en uso — elige otro.</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F679" t="b">
@@ -20930,25 +20930,55 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
+          <t>touch_name_already_taken_error</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>iOS custom-art import sheets: duplicate-name validation error</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>That name is already taken — pick another.</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Ese nombre ya está en uso — elige otro.</t>
+        </is>
+      </c>
+      <c r="F680" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
           <t>touch_enabled_toggle</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>iOS custom face-card-art import sheet: Enabled toggle label</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr">
+      <c r="D681" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="E680" t="inlineStr">
+      <c r="E681" t="inlineStr">
         <is>
           <t>Activado</t>
         </is>
       </c>
-      <c r="F680" t="b">
+      <c r="F681" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F681"/>
+  <dimension ref="A1:F680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19303,27 +19303,27 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>SlideDownMenuIOS</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>search_a11y</t>
+          <t>close_menu_a11y</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Accessibility label for the search icon in the iOS Themes full-screen sheet toolbar</t>
+          <t>iOS slide-down menu close-button accessibility label</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Close menu</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Buscar</t>
+          <t>Cerrar menú</t>
         </is>
       </c>
       <c r="F626" t="b">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>close_menu_a11y</t>
+          <t>menu_section_game</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>iOS slide-down menu close-button accessibility label</t>
+          <t>iOS slide-down menu Game Selection tab section header</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Close menu</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Cerrar menú</t>
+          <t>Juego</t>
         </is>
       </c>
       <c r="F627" t="b">
@@ -19368,22 +19368,22 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>menu_section_game</t>
+          <t>menu_section_theme</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Game Selection tab section header</t>
+          <t>iOS slide-down menu Themes tab felt-color section header</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Juego</t>
+          <t>Tema</t>
         </is>
       </c>
       <c r="F628" t="b">
@@ -19398,22 +19398,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>menu_section_theme</t>
+          <t>menu_section_card_back</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab felt-color section header</t>
+          <t>iOS slide-down menu Themes tab card-back section header</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Card Back</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Tema</t>
+          <t>Reverso de Carta</t>
         </is>
       </c>
       <c r="F629" t="b">
@@ -19428,22 +19428,22 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>menu_section_card_back</t>
+          <t>menu_section_background</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab card-back section header</t>
+          <t>iOS slide-down menu Themes tab background section header</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Card Back</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Reverso de Carta</t>
+          <t>Fondo</t>
         </is>
       </c>
       <c r="F630" t="b">
@@ -19458,22 +19458,22 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>menu_section_background</t>
+          <t>background_none_option</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>iOS slide-down menu Themes tab background section header</t>
+          <t>iOS slide-down menu: clears the custom background back to felt color</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Fondo</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="F631" t="b">
@@ -19488,22 +19488,22 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>background_none_option</t>
+          <t>remove_card_back_alert_title</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: clears the custom background back to felt color</t>
+          <t>iOS slide-down menu: confirm removing a custom card back</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Remove Card Back?</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>¿Quitar Reverso de Carta?</t>
         </is>
       </c>
       <c r="F632" t="b">
@@ -19518,22 +19518,22 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>remove_card_back_alert_title</t>
+          <t>remove_background_alert_title</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom card back</t>
+          <t>iOS slide-down menu: confirm removing a custom background</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Remove Card Back?</t>
+          <t>Remove Background?</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>¿Quitar Reverso de Carta?</t>
+          <t>¿Quitar Fondo?</t>
         </is>
       </c>
       <c r="F633" t="b">
@@ -19548,22 +19548,22 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>remove_background_alert_title</t>
+          <t>remove_imported_image_body</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: confirm removing a custom background</t>
+          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Remove Background?</t>
+          <t>This removes the imported image. It can't be undone.</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>¿Quitar Fondo?</t>
+          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
         </is>
       </c>
       <c r="F634" t="b">
@@ -19578,22 +19578,22 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>remove_imported_image_body</t>
+          <t>statistics_nav_row</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: alert body, reused for both card-back and background removal</t>
+          <t>iOS slide-down menu: Statistics destination row</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>This removes the imported image. It can't be undone.</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Esto elimina la imagen importada. No se puede deshacer.</t>
+          <t>Estadísticas</t>
         </is>
       </c>
       <c r="F635" t="b">
@@ -19608,22 +19608,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>statistics_nav_row</t>
+          <t>how_to_play_nav_row</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Statistics destination row</t>
+          <t>iOS slide-down menu: Help destination row</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>How to Play</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Estadísticas</t>
+          <t>Cómo Jugar</t>
         </is>
       </c>
       <c r="F636" t="b">
@@ -19638,22 +19638,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>how_to_play_nav_row</t>
+          <t>face_card_art_nav_row</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Help destination row</t>
+          <t>iOS slide-down menu: Face Card Art destination row</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>How to Play</t>
+          <t>Face Card Art</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Cómo Jugar</t>
+          <t>Arte de Carta</t>
         </is>
       </c>
       <c r="F637" t="b">
@@ -19663,27 +19663,27 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>SlideDownMenuIOS</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>face_card_art_nav_row</t>
+          <t>touch_new_deal_label</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>iOS slide-down menu: Face Card Art destination row</t>
+          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Face Card Art</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Arte de Carta</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F638" t="b">
@@ -19698,22 +19698,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>touch_new_deal_label</t>
+          <t>touch_undo_last_move_label</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>iOS touch game views: New (deal) toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Undo Last Move</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Deshacer Última Jugada</t>
         </is>
       </c>
       <c r="F639" t="b">
@@ -19728,22 +19728,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>touch_undo_last_move_label</t>
+          <t>touch_deal_a11y</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>iOS touch game views: Undo Last Move toolbar Label, Klondike/Spider/Beecell</t>
+          <t>iOS Spider touch view: stock pile accessibility label</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Undo Last Move</t>
+          <t>Deal</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Deshacer Última Jugada</t>
+          <t>Repartir</t>
         </is>
       </c>
       <c r="F640" t="b">
@@ -19758,22 +19758,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>touch_deal_a11y</t>
+          <t>touch_completed_runs_a11y</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: stock pile accessibility label</t>
+          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Deal</t>
+          <t>Completed runs</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Repartir</t>
+          <t>Series completadas</t>
         </is>
       </c>
       <c r="F641" t="b">
@@ -19788,22 +19788,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>touch_completed_runs_a11y</t>
+          <t>touch_decks_picker_label</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: completed-runs tray accessibility label</t>
+          <t>iOS Beecell touch view: deck-count Picker label</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Completed runs</t>
+          <t>Decks</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Series completadas</t>
+          <t>Mazos</t>
         </is>
       </c>
       <c r="F642" t="b">
@@ -19818,22 +19818,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>touch_decks_picker_label</t>
+          <t>touch_single_deck_option</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker label</t>
+          <t>iOS Beecell touch view: deck-count Picker option</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Decks</t>
+          <t>Single Deck</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Mazos</t>
+          <t>Mazo Sencillo</t>
         </is>
       </c>
       <c r="F643" t="b">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>touch_single_deck_option</t>
+          <t>touch_double_deck_option</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -19858,12 +19858,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Single Deck</t>
+          <t>Double Deck</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Mazo Sencillo</t>
+          <t>Doble Mazo</t>
         </is>
       </c>
       <c r="F644" t="b">
@@ -19878,22 +19878,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>touch_double_deck_option</t>
+          <t>touch_suits_picker_label</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>iOS Beecell touch view: deck-count Picker option</t>
+          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Double Deck</t>
+          <t>Suits</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Doble Mazo</t>
+          <t>Palos</t>
         </is>
       </c>
       <c r="F645" t="b">
@@ -19908,22 +19908,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>touch_suits_picker_label</t>
+          <t>touch_bet_max_button</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>iOS Spider touch view: suit-count Picker label (mislabeled "Difficulty" in source, corrected to match Mac's "Suits:")</t>
+          <t>iOS Video Poker touch view: Max bet button</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Suits</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Palos</t>
+          <t>Máx</t>
         </is>
       </c>
       <c r="F646" t="b">
@@ -19938,22 +19938,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>touch_bet_max_button</t>
+          <t>touch_settings_unlock_between_hands</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: Max bet button</t>
+          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Settings unlock between hands.</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Máx</t>
+          <t>La configuración se desbloquea entre manos.</t>
         </is>
       </c>
       <c r="F647" t="b">
@@ -19968,22 +19968,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_between_hands</t>
+          <t>touch_settings_unlock_hand_ends</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: settings-locked notice during a round</t>
+          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Settings unlock between hands.</t>
+          <t>Settings unlock when the hand ends.</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea entre manos.</t>
+          <t>La configuración se desbloquea cuando termina la mano.</t>
         </is>
       </c>
       <c r="F648" t="b">
@@ -19998,22 +19998,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>touch_settings_unlock_hand_ends</t>
+          <t>touch_hands_dealt_stat</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>iOS Video Poker touch view: settings-locked notice during a hand</t>
+          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Settings unlock when the hand ends.</t>
+          <t>Hands Dealt</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>La configuración se desbloquea cuando termina la mano.</t>
+          <t>Manos Repartidas</t>
         </is>
       </c>
       <c r="F649" t="b">
@@ -20028,22 +20028,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>touch_hands_dealt_stat</t>
+          <t>touch_session_credits_stat</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: hands-dealt row label</t>
+          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Hands Dealt</t>
+          <t>Session Credits</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Manos Repartidas</t>
+          <t>Créditos de Sesión</t>
         </is>
       </c>
       <c r="F650" t="b">
@@ -20058,22 +20058,22 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>touch_session_credits_stat</t>
+          <t>touch_hand_label_fmt</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch stats: session-credits row label</t>
+          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Session Credits</t>
+          <t>HAND %d</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Créditos de Sesión</t>
+          <t>MANO %d</t>
         </is>
       </c>
       <c r="F651" t="b">
@@ -20088,22 +20088,22 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>touch_hand_label_fmt</t>
+          <t>touch_you_label</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand label when split (multiple hands), %d is the hand number</t>
+          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>HAND %d</t>
+          <t>YOU</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>MANO %d</t>
+          <t>TÚ</t>
         </is>
       </c>
       <c r="F652" t="b">
@@ -20118,22 +20118,22 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>touch_you_label</t>
+          <t>touch_bust_suffix</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: player hand label when not split (single hand)</t>
+          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>YOU</t>
+          <t xml:space="preserve"> BUST</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>TÚ</t>
+          <t xml:space="preserve"> SE PASÓ</t>
         </is>
       </c>
       <c r="F653" t="b">
@@ -20148,22 +20148,22 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>touch_bust_suffix</t>
+          <t>touch_result_win</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: appended to a hand value when busted (leading space intentional)</t>
+          <t>iOS Blackjack touch view: per-hand result badge</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BUST</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SE PASÓ</t>
+          <t>GANA</t>
         </is>
       </c>
       <c r="F654" t="b">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>touch_result_win</t>
+          <t>touch_result_loss</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -20188,12 +20188,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>GANA</t>
+          <t>PIERDE</t>
         </is>
       </c>
       <c r="F655" t="b">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>touch_result_loss</t>
+          <t>touch_result_push</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -20218,12 +20218,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>PUSH</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>PIERDE</t>
+          <t>EMPATE</t>
         </is>
       </c>
       <c r="F656" t="b">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>touch_result_push</t>
+          <t>touch_result_blackjack</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -20248,12 +20248,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>PUSH</t>
+          <t>BLACKJACK!</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>EMPATE</t>
+          <t>¡BLACKJACK!</t>
         </is>
       </c>
       <c r="F657" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>touch_result_blackjack</t>
+          <t>touch_result_bust</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -20278,12 +20278,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>BLACKJACK!</t>
+          <t>BUST</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>¡BLACKJACK!</t>
+          <t>SE PASÓ</t>
         </is>
       </c>
       <c r="F658" t="b">
@@ -20298,22 +20298,22 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>touch_result_bust</t>
+          <t>touch_action_hit</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: per-hand result badge</t>
+          <t>iOS Blackjack touch view: action button</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>BUST</t>
+          <t>Hit</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>SE PASÓ</t>
+          <t>Pedir</t>
         </is>
       </c>
       <c r="F659" t="b">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>touch_action_hit</t>
+          <t>touch_action_stand</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -20338,12 +20338,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Pedir</t>
+          <t>Plantarse</t>
         </is>
       </c>
       <c r="F660" t="b">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>touch_action_stand</t>
+          <t>touch_action_double</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -20368,12 +20368,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Plantarse</t>
+          <t>Doblar</t>
         </is>
       </c>
       <c r="F661" t="b">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>touch_action_double</t>
+          <t>touch_action_split</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -20398,12 +20398,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Doblar</t>
+          <t>Dividir</t>
         </is>
       </c>
       <c r="F662" t="b">
@@ -20418,22 +20418,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>touch_action_split</t>
+          <t>touch_reset_position_button</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>iOS Blackjack touch view: action button</t>
+          <t>iOS custom-art import sheets: Reset Position button</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Reset Position</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Dividir</t>
+          <t>Restablecer Posición</t>
         </is>
       </c>
       <c r="F663" t="b">
@@ -20448,22 +20448,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>touch_reset_position_button</t>
+          <t>touch_add_card_back_title</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: Reset Position button</t>
+          <t>iOS custom card-back import sheet nav title</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Reset Position</t>
+          <t>Add Card Back</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Restablecer Posición</t>
+          <t>Añadir Reverso de Carta</t>
         </is>
       </c>
       <c r="F664" t="b">
@@ -20473,27 +20473,29 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>touch_add_card_back_title</t>
+          <t>steal_instruction_tap</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>iOS custom card-back import sheet nav title</t>
+          <t>Steal-mode instructional hint, iOS (touch wording — Mac/Windows use the click-based steal_instruction key)</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Add Card Back</t>
+          <t>Double-tap a captured opponent's card
+on the board to steal it.</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Añadir Reverso de Carta</t>
+          <t>Toca dos veces la carta capturada de un oponente
+en el tablero para robarla.</t>
         </is>
       </c>
       <c r="F665" t="b">
@@ -20503,29 +20505,27 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>steal_instruction_tap</t>
+          <t>touch_layout_coming_soon</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Steal-mode instructional hint, iOS (touch wording — Mac/Windows use the click-based steal_instruction key)</t>
+          <t>Placeholder/fallback text</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Double-tap a captured opponent's card
-on the board to steal it.</t>
+          <t>Touch layout coming soon</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Toca dos veces la carta capturada de un oponente
-en el tablero para robarla.</t>
+          <t>Diseño táctil próximamente</t>
         </is>
       </c>
       <c r="F666" t="b">
@@ -20540,26 +20540,26 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>touch_layout_coming_soon</t>
+          <t>touch_blackjack_title</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Placeholder/fallback text</t>
+          <t>Title-case game label</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Touch layout coming soon</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Diseño táctil próximamente</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="F667" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="668">
@@ -20570,22 +20570,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>touch_blackjack_title</t>
+          <t>touch_blackjack_banner</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Title-case game label</t>
+          <t>All-caps banner/header label</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="F668" t="b">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>touch_blackjack_banner</t>
+          <t>touch_spider_banner</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -20610,12 +20610,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="F669" t="b">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>touch_spider_banner</t>
+          <t>touch_klondike_banner</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -20640,12 +20640,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="F670" t="b">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>touch_klondike_banner</t>
+          <t>touch_beecell_banner</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -20670,12 +20670,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="F671" t="b">
@@ -20685,57 +20685,57 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>Chrome</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>touch_beecell_banner</t>
+          <t>debug_banners_menu</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>All-caps banner/header label</t>
+          <t>Mac-only dev menu title</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>Banners</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>Anuncios</t>
         </is>
       </c>
       <c r="F672" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Chrome</t>
+          <t>ManageDecksWin</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>debug_banners_menu</t>
+          <t>deck_default_name</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Mac-only dev menu title</t>
+          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Banners</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Anuncios</t>
+          <t>Predeterminado</t>
         </is>
       </c>
       <c r="F673" t="b">
@@ -20745,27 +20745,27 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>ManageDecksWin</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>deck_default_name</t>
+          <t>free_play_label</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
+          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Free Play</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Predeterminado</t>
+          <t>Juego Libre</t>
         </is>
       </c>
       <c r="F674" t="b">
@@ -20780,22 +20780,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>free_play_label</t>
+          <t>touch_choose_photo</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
+          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Free Play</t>
+          <t>Choose Photo</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Juego Libre</t>
+          <t>Elegir Foto</t>
         </is>
       </c>
       <c r="F675" t="b">
@@ -20810,22 +20810,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>touch_choose_photo</t>
+          <t>touch_choose_different_photo</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
+          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Choose Photo</t>
+          <t>Choose a Different Photo</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Elegir Foto</t>
+          <t>Elegir Otra Foto</t>
         </is>
       </c>
       <c r="F676" t="b">
@@ -20840,22 +20840,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>touch_choose_different_photo</t>
+          <t>touch_pinch_zoom_reposition</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
+          <t>iOS custom-art import sheets: crop editor section header</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Choose a Different Photo</t>
+          <t>Pinch to zoom, drag to reposition</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Elegir Otra Foto</t>
+          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
         </is>
       </c>
       <c r="F677" t="b">
@@ -20870,22 +20870,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>touch_pinch_zoom_reposition</t>
+          <t>touch_name_field_placeholder</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: crop editor section header</t>
+          <t>iOS custom-art import sheets: name TextField placeholder</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Pinch to zoom, drag to reposition</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F678" t="b">
@@ -20900,22 +20900,22 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>touch_name_field_placeholder</t>
+          <t>touch_name_already_taken_error</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: name TextField placeholder</t>
+          <t>iOS custom-art import sheets: duplicate-name validation error</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>That name is already taken — pick another.</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Ese nombre ya está en uso — elige otro.</t>
         </is>
       </c>
       <c r="F679" t="b">
@@ -20930,55 +20930,25 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>touch_name_already_taken_error</t>
+          <t>touch_enabled_toggle</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: duplicate-name validation error</t>
+          <t>iOS custom face-card-art import sheet: Enabled toggle label</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>That name is already taken — pick another.</t>
+          <t>Enabled</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Ese nombre ya está en uso — elige otro.</t>
+          <t>Activado</t>
         </is>
       </c>
       <c r="F680" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>TouchViewsIOS</t>
-        </is>
-      </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>touch_enabled_toggle</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
-        <is>
-          <t>iOS custom face-card-art import sheet: Enabled toggle label</t>
-        </is>
-      </c>
-      <c r="D681" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>Activado</t>
-        </is>
-      </c>
-      <c r="F681" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F680"/>
+  <dimension ref="A1:F681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20949,6 +20949,36 @@
         </is>
       </c>
       <c r="F680" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>card_back_default_name</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Auto-filled base name for a new custom card back before the user renames it (appended with ' N' for the 2nd, 3rd, ... duplicate)</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Predeterminado</t>
+        </is>
+      </c>
+      <c r="F681" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -14139,7 +14139,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>💡 Estrategia y Consejos Pro</t>
+          <t>💡 Estrategia y consejos</t>
         </is>
       </c>
       <c r="F457" t="b">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Teclas de Flecha</t>
+          <t>Flechas del Teclado</t>
         </is>
       </c>
       <c r="F466" t="b">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Espacio / Intro</t>
+          <t>Barra espaciadora / Intro</t>
         </is>
       </c>
       <c r="F468" t="b">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Teclas de Flecha + Espacio / Intro</t>
+          <t>Flechas del Teclado + Barra espaciadora / Intro</t>
         </is>
       </c>
       <c r="F527" t="b">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F681"/>
+  <dimension ref="A1:F683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20979,6 +20979,66 @@
         </is>
       </c>
       <c r="F681" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>add_photo_short</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Caption on the iOS Themes sheet Background grid's Add tile (imports a photo, unlike Card Back/Face Art's plain "Add")</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Add Photo</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Añadir Foto</t>
+        </is>
+      </c>
+      <c r="F682" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>felt_custom_short</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Caption on the iOS Themes sheet Background grid's Custom Felt tile — shorter than feltCustomColor ("Custom Felt Color") so it fits the narrow tile without truncating</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Custom Felt</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Fieltro Personalizado</t>
+        </is>
+      </c>
+      <c r="F683" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F683"/>
+  <dimension ref="A1:F688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21039,6 +21039,156 @@
         </is>
       </c>
       <c r="F683" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>stat_position_top</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's top corner value</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Arriba</t>
+        </is>
+      </c>
+      <c r="F684" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>stat_position_bottom</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's bottom corner value</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Abajo</t>
+        </is>
+      </c>
+      <c r="F685" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>stat_position_left</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's left corner value</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Izquierda</t>
+        </is>
+      </c>
+      <c r="F686" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>stat_position_right</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's right corner value</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Derecha</t>
+        </is>
+      </c>
+      <c r="F687" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>stat_filter_any</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Default/unset option in each iOS Card Bank stat-filter dropdown (matches any value)</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Cualquiera</t>
+        </is>
+      </c>
+      <c r="F688" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F688"/>
+  <dimension ref="A1:F690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21189,6 +21189,66 @@
         </is>
       </c>
       <c r="F688" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>stat_sudden_death_count_ios</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>iOS Honeycomb stats sheet label for suddenDeathCount — plainer than mac's thematic "Most Swarms to the Death", matching iOS's literal stat-label style</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Sudden Deaths</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Muertes Súbitas</t>
+        </is>
+      </c>
+      <c r="F689" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>TouchViewsIOS</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>stat_fallen_aces_ios</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>iOS Honeycomb stats sheet label for fallenAces — plainer than mac's thematic "Queen's Falls", matching iOS's literal stat-label style</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Fallen Aces</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Ases Caídos</t>
+        </is>
+      </c>
+      <c r="F690" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -4317,17 +4317,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Score badge, %d = dealer score — Honeycomb touch view</t>
+          <t>Score badge, Honeycomb touch view — %d = opponent score, %@/{1} = opponent's difficulty name (e.g. Baby Bee)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>%d DEALER</t>
+          <t>%d %@</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>%d REPARTIDOR</t>
+          <t>%d %@</t>
         </is>
       </c>
       <c r="F130" t="b">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -4292,12 +4292,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>YOU %d</t>
+          <t>You %d</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TÚ %d</t>
+          <t>Tú %d</t>
         </is>
       </c>
       <c r="F129" t="b">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F682"/>
+  <dimension ref="A1:F685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21009,6 +21009,96 @@
         </is>
       </c>
       <c r="F682" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>out_of_credits_toast</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Toast shown when the player runs out of credits, reused Blackjack/Video Poker</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Out of Credits!</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>¡Sin créditos!</t>
+        </is>
+      </c>
+      <c r="F683" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Blackjack</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>btn_clear_short</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Short "Clear" label for Blackjack landscape betting grid (fits one line at that button width)</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Borrar</t>
+        </is>
+      </c>
+      <c r="F684" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>global_options_section</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>iOS Options sheet section header — groups Sound/No Stress Mode/Honey Mode/Hide Hint/Manually Dismiss Banners, separate from the per-game settings section below it</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F685" t="b">
         <v>1</v>
       </c>
     </row>
@@ -30149,12 +30239,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Idle Action</t>
+          <t>Gameplay</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>No action taken for one minute.</t>
+          <t>Player runs out of credits (Video Poker/Blackjack).</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -30164,7 +30254,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Ambiance</t>
+          <t>Repeatable Flavor</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -22313,7 +22313,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Warming up flights muscles…</t>
+          <t>Warming up flight muscles…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -4317,17 +4317,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Score badge, Honeycomb touch view — %d = opponent score, %@/{1} = opponent's difficulty name (e.g. Baby Bee)</t>
+          <t>Score badge, Honeycomb touch view — %@/{0} = opponent's difficulty name (e.g. Baby Bee), %d = opponent score</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>%d %@</t>
+          <t>%@ %d</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>%d %@</t>
+          <t>%@ %d</t>
         </is>
       </c>
       <c r="F130" t="b">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F684"/>
+  <dimension ref="A1:F685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21069,6 +21069,36 @@
         </is>
       </c>
       <c r="F684" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>hide_bee</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Toggle label, reused across every game's Options on Mac/iOS/Windows</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Hide the Bee</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Ocultar la Abeja</t>
+        </is>
+      </c>
+      <c r="F685" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -1500,12 +1500,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Honey Mode (Flavor)</t>
+          <t>Enable Banners</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Modo Miel (Sabor)</t>
+          <t>Activar Anuncios</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -15142,14 +15142,14 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>• Honey Mode (Flavor): Global toggle across all 6 games — controls the "+N"/"-N" score popups and whether flavor/ambiance banners appear. Turn it off for a quieter, more minimal play experience.
+          <t>• Enable Banners: Global toggle across all 6 games — controls the "+N"/"-N" score popups and whether flavor/ambiance banners appear. Turn it off for a quieter, more minimal play experience.
 • Stay on Top: Keeps the game window pinned above your other windows (View menu).
 • Sound Effects, Vegas Scoring, and Hide Hint Button are also available here per-game.</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>• Modo Miel (Sabor): Interruptor global en los 6 juegos — controla las ventanas emergentes de puntuación "+N"/"-N" y si aparecen los carteles de sabor/ambiente. Desactívalo para una experiencia de juego más silenciosa y minimalista.
+          <t>• Activar Anuncios: Interruptor global en los 6 juegos — controla las ventanas emergentes de puntuación "+N"/"-N" y si aparecen los carteles de sabor/ambiente. Desactívalo para una experiencia de juego más silenciosa y minimalista.
 • Siempre Encima: Mantiene la ventana del juego anclada sobre tus otras ventanas (Menú Vista).
 • Efectos de Sonido, Puntuación Vegas, y Ocultar Botón de Pistas también están disponibles aquí por juego.</t>
         </is>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F685"/>
+  <dimension ref="A1:F697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Enable Banners</t>
+          <t>Honey Mode</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Activar Anuncios</t>
+          <t>Modo Miel</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>YOU</t>
+          <t>You</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -15142,14 +15142,14 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>• Enable Banners: Global toggle across all 6 games — controls the "+N"/"-N" score popups and whether flavor/ambiance banners appear. Turn it off for a quieter, more minimal play experience.
+          <t>• Honey Mode: Global toggle across all 6 games — controls the "+N"/"-N" score popups and whether flavor/ambiance banners appear. Turn it off for a quieter, more minimal play experience.
 • Stay on Top: Keeps the game window pinned above your other windows (View menu).
 • Sound Effects, Vegas Scoring, and Hide Hint Button are also available here per-game.</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>• Activar Anuncios: Interruptor global en los 6 juegos — controla las ventanas emergentes de puntuación "+N"/"-N" y si aparecen los carteles de sabor/ambiente. Desactívalo para una experiencia de juego más silenciosa y minimalista.
+          <t>• Modo Miel: Interruptor global en los 6 juegos — controla las ventanas emergentes de puntuación "+N"/"-N" y si aparecen los carteles de sabor/ambiente. Desactívalo para una experiencia de juego más silenciosa y minimalista.
 • Siempre Encima: Mantiene la ventana del juego anclada sobre tus otras ventanas (Menú Vista).
 • Efectos de Sonido, Puntuación Vegas, y Ocultar Botón de Pistas también están disponibles aquí por juego.</t>
         </is>
@@ -21099,6 +21099,366 @@
         </is>
       </c>
       <c r="F685" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>honey_mode_tooltip</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Tooltip for the Honey Mode toggle</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Enables banners and solitaire point animations.</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Habilita los anuncios y las animaciones de puntos en los solitarios.</t>
+        </is>
+      </c>
+      <c r="F686" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>no_stress_mode_tooltip</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Tooltip for the No Stress Mode toggle</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Pressure-free! No timers, no betting, and Honeycomb chooses your deck for you at random.</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>¡Sin presión! Sin temporizadores, sin apuestas, y Honeycomb elige tu mazo al azar.</t>
+        </is>
+      </c>
+      <c r="F687" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>rank_nurse_bee</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Player rank, 10-19 cards collected</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Nurse Bee</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Abeja Nodriza</t>
+        </is>
+      </c>
+      <c r="F688" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>rank_scout_bee</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Player rank, 20-49 cards collected</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Scout Bee</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Abeja Exploradora</t>
+        </is>
+      </c>
+      <c r="F689" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>rank_worker_bee</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Player rank, 50-99 cards collected</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Worker Bee</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Abeja Obrera</t>
+        </is>
+      </c>
+      <c r="F690" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>rank_guard_bee</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Player rank, 100-149 cards collected</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Guard Bee</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Abeja Guardiana</t>
+        </is>
+      </c>
+      <c r="F691" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>rank_waggle_dancer</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Player rank, 150-199 cards collected</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Waggle Dancer</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Abeja Bailarina</t>
+        </is>
+      </c>
+      <c r="F692" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>rank_comb_architect</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Player rank, 200-299 cards collected</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Comb Architect</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Arquitecta del Panal</t>
+        </is>
+      </c>
+      <c r="F693" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>rank_royal_attendant</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Player rank, 300-399 cards collected</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Royal Attendant</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Asistente Real</t>
+        </is>
+      </c>
+      <c r="F694" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>rank_swarm_leader</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Player rank, 400-499 cards collected</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Swarm Leader</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Líder del Enjambre</t>
+        </is>
+      </c>
+      <c r="F695" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>rank_hive_monarch</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Player rank, 500+ cards collected but not the full set</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Hive Monarch</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Monarca de la Colmena</t>
+        </is>
+      </c>
+      <c r="F696" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>rank_apiarist</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Player rank, every card in the collection unlocked</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Apiarist</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Apicultor</t>
+        </is>
+      </c>
+      <c r="F697" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F697"/>
+  <dimension ref="A1:F698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1. Mismo Palo Antes que Palos Mixtos: Siempre prefiere construir rachas del mismo palo. Las pilas de palos mixtos bloquean tus cartas y no pueden moverse juntas.
+          <t>1. Mismo Palo Antes que Palos Mixtos: Siempre prioriza construir rachas del mismo palo. Las pilas de palos mixtos bloquean tus cartas y no pueden moverse juntas.
 2. Columnas Vacías Primero: Las columnas vacías te permiten aislar pilas de palos mixtos y reorganizarlas en limpias rachas del mismo palo.
 3. Retrasa el Reparto: Agota cada movimiento posible en el tablero antes de hacer clic en la pila.</t>
         </is>
@@ -21459,6 +21459,36 @@
         </is>
       </c>
       <c r="F697" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>global_settings_header</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Section header, Windows Preferences panel — global (cross-game) settings group</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Global Settings</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Configuración Global</t>
+        </is>
+      </c>
+      <c r="F698" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -15051,7 +15051,7 @@
           <t>• Mecánica de Robo: Después de ganar una partida, ¡haz doble clic en una carta elegible del repartidor para robarla permanentemente hacia tu Banco de Cartas! Solo se permite un robo por partida.
 • Límites de Rareza de Mazo: Los mazos personalizados están limitados a: como máximo una carta de 5★, y como máximo una carta de 4★ si hay una de 5★ presente (o hasta dos cartas de 4★ sin una de 5★).
 • Mazos de Oponente Inteligentes: La IA selecciona automáticamente mazos que contienen cartas que aún no tienes para maximizar las recompensas de robo.
-• Protección Anti-Robo: ¿Atrapado en una cadena de Revanchas contra un oponente cuyas cartas parece que no puedes capturar? Gana dos Revanchas seguidas contra el mismo oponente sin que haya nada elegible para robar, y cualquier carta aún no desbloqueada que quede en el tablero se vuelve robable en esa segunda victoria — capturada o no. Una vez activada, se mantiene activa para el resto de esa cadena de Revanchas, para que cada victoria futura siga ofreciendo un robo — no tendrás que volver a ganarlo. Comenzar una Nueva Partida (un nuevo oponente) es lo que la desactiva.</t>
+• Protección Anti-Robo: ¿Atrapado en una cadena de Revanchas contra un oponente cuyas cartas parece que no puedes capturar? Gana dos Revanchas seguidas contra el mismo oponente sin que haya nada elegible para robar, y cualquier carta aún no desbloqueada que quede en el tablero se vuelve robable en esa segunda victoria — capturada o no. Una vez activada, se mantiene activa para el resto de esa cadena de Revanchas, para que cada victoria futura siga ofreciendo un robo — no tendrás que volver a ganarlo. Esto se desactiva al comenzar una Nueva Partida (contra un nuevo oponente).</t>
         </is>
       </c>
       <c r="F484" t="b">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -2250,12 +2250,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Win Percentage</t>
+          <t>Win Rate</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Porcentaje de Victorias</t>
+          <t>Tasa de Victorias</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Rebuy</t>
+          <t>Buy In</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recomprar</t>
+          <t>Comprar Fichas</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Background, outline, text, hint highlight</t>
+          <t>Background, outline, suit text, hint highlight</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Fondo, contorno, texto, resaltado de pista</t>
+          <t>Fondo, contorno, texto de palo, resaltado de pista</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Win Percentage:</t>
+          <t>Win Rate:</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Porcentaje de Victorias:</t>
+          <t>Tasa de Victorias:</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>REBUY</t>
+          <t>BUY IN</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>RECOMPRAR</t>
+          <t>COMPRAR FICHAS</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Clear  [Q]</t>
+          <t>Clear  [C]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Borrar  [Q]</t>
+          <t>Borrar  [C]</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Force Normal Rules</t>
+          <t>Normal Mode (Force Zero Rules)</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Forzar Reglas Normales</t>
+          <t>Modo Normal (Forzar Cero Reglas)</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Honeycomb Statistics</t>
+          <t>Honeycomb Stats</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Matches Played</t>
+          <t>Games Played</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -11554,12 +11554,12 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Flawless Victories (10-0 Sweep)</t>
+          <t>Flawless Victories</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Victorias Perfectas (Barrida 10-0)</t>
+          <t>Victorias Perfectas</t>
         </is>
       </c>
       <c r="F371" t="b">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Same/Plus Triggers</t>
+          <t>Symmetry/Math Bee Hive Minds Triggered</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Activaciones Same/Plus</t>
+          <t>Mentes Colmena Simetría/Abeja Matemática Activadas</t>
         </is>
       </c>
       <c r="F372" t="b">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Saved Decks &amp; Card Bank</t>
+          <t>Manage Decks</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Mazos Guardados y Banco de Cartas</t>
+          <t>Administrar Mazos</t>
         </is>
       </c>
       <c r="F393" t="b">
@@ -20880,12 +20880,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Sudden Deaths</t>
+          <t>Most Swarms to the Death</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Muertes Súbitas</t>
+          <t>Más Enjambres a Muerte</t>
         </is>
       </c>
       <c r="F678" t="b">
@@ -20910,12 +20910,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Fallen Aces</t>
+          <t>Queen's Falls</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Ases Caídos</t>
+          <t>Caídas de la Reina</t>
         </is>
       </c>
       <c r="F679" t="b">

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F700"/>
+  <dimension ref="A1:F703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21549,6 +21549,96 @@
         </is>
       </c>
       <c r="F700" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>stat_shortest_win_time</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Stat row label, Klondike/Spider/Beecell — shortest winning-game time</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Shortest Win Time</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Tiempo Más Corto de Victoria</t>
+        </is>
+      </c>
+      <c r="F701" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>stat_total_paid_out</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Stat row label, Blackjack/Video Poker</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Total Paid Out</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Total Pagado</t>
+        </is>
+      </c>
+      <c r="F702" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>stat_biggest_payout</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Stat row label, Blackjack/Video Poker</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Biggest Payout</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Mayor Pago</t>
+        </is>
+      </c>
+      <c r="F703" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F703"/>
+  <dimension ref="A1:F704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21639,6 +21639,36 @@
         </is>
       </c>
       <c r="F703" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>beecell_statistics_title</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Stats screen title for Beecell</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Beecell Statistics</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Estadísticas de Beecell</t>
+        </is>
+      </c>
+      <c r="F704" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F704"/>
+  <dimension ref="A1:F707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21669,6 +21669,96 @@
         </is>
       </c>
       <c r="F704" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Casino</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>btn_new_bet</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Blackjack action button</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>New Bet</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Nueva Apuesta</t>
+        </is>
+      </c>
+      <c r="F705" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Casino</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>btn_rebuy</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Casino action button to rebuy chips</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Rebuy</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Recomprar</t>
+        </is>
+      </c>
+      <c r="F706" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Casino</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>btn_re_deal</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Blackjack action button to deal again</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Re-Deal</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Repartir</t>
+        </is>
+      </c>
+      <c r="F707" t="b">
         <v>1</v>
       </c>
     </row>
